--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -626,11 +626,7 @@
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Alderwood”.</t>
-        </is>
-      </c>
+      <c r="J5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -663,11 +659,7 @@
         <f>H6/$D$6</f>
         <v/>
       </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Armani”.</t>
-        </is>
-      </c>
+      <c r="J6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -700,11 +692,7 @@
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Harmoni Indah”.</t>
-        </is>
-      </c>
+      <c r="J7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -766,11 +754,7 @@
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Armani Hallson Klcc”.</t>
-        </is>
-      </c>
+      <c r="J9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -803,11 +787,7 @@
         <f>H10/$D$10</f>
         <v/>
       </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Armani Kepong”.</t>
-        </is>
-      </c>
+      <c r="J10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -898,11 +878,7 @@
         <f>H13/$D$13</f>
         <v/>
       </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Alam Armani”.</t>
-        </is>
-      </c>
+      <c r="J13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -935,11 +911,7 @@
         <f>H14/$D$14</f>
         <v/>
       </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Armani”.</t>
-        </is>
-      </c>
+      <c r="J14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -966,17 +938,13 @@
       </c>
       <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="I15" s="12">
         <f>H15/$D$15</f>
         <v/>
       </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Lofthill”.</t>
-        </is>
-      </c>
+      <c r="J15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -1075,11 +1043,7 @@
         <f>H18/$D$18</f>
         <v/>
       </c>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Taman Bukit Tualang”.</t>
-        </is>
-      </c>
+      <c r="J18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -1108,11 +1072,7 @@
         <f>H19/$D$19</f>
         <v/>
       </c>
-      <c r="J19" s="8" t="inlineStr">
-        <is>
-          <t>Code not yet confirmed against TEDUH.</t>
-        </is>
-      </c>
+      <c r="J19" s="8" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="7" t="n">
@@ -1141,11 +1101,7 @@
         <f>H20/$D$20</f>
         <v/>
       </c>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>Code not yet confirmed against TEDUH.</t>
-        </is>
-      </c>
+      <c r="J20" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1286,11 +1242,7 @@
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Mh Platinum 3”.</t>
-        </is>
-      </c>
+      <c r="J5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1323,11 +1275,7 @@
         <f>H6/$D$6</f>
         <v/>
       </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Pv 22”.</t>
-        </is>
-      </c>
+      <c r="J6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1360,11 +1308,7 @@
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Platinum Melati”.</t>
-        </is>
-      </c>
+      <c r="J7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1393,11 +1337,7 @@
         <f>H8/$D$8</f>
         <v/>
       </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>Code not yet confirmed against TEDUH.</t>
-        </is>
-      </c>
+      <c r="J8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1428,7 +1368,7 @@
       </c>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>Code not yet confirmed against TEDUH. Latest sales - Block W: 598 units, Block X: 559 units</t>
+          <t>Latest sales - Block W: 598 units, Block X: 559 units</t>
         </is>
       </c>
     </row>
@@ -1459,11 +1399,7 @@
         <f>H10/$D$10</f>
         <v/>
       </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>Code not yet confirmed against TEDUH.</t>
-        </is>
-      </c>
+      <c r="J10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -1653,11 +1589,7 @@
         <f>H6/$D$6</f>
         <v/>
       </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>Code not yet confirmed against TEDUH.</t>
-        </is>
-      </c>
+      <c r="J6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -1686,11 +1618,7 @@
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>Code not yet confirmed against TEDUH.</t>
-        </is>
-      </c>
+      <c r="J7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1713,17 +1641,13 @@
       <c r="F8" s="8" t="inlineStr"/>
       <c r="G8" s="11" t="n"/>
       <c r="H8" s="11" t="n">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="I8" s="12">
         <f>H8/$D$8</f>
         <v/>
       </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>Code not yet confirmed against TEDUH.</t>
-        </is>
-      </c>
+      <c r="J8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -1752,11 +1676,7 @@
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>Code not yet confirmed against TEDUH.</t>
-        </is>
-      </c>
+      <c r="J9" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1897,11 +1817,7 @@
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Pangsapuri Seri Aura”.</t>
-        </is>
-      </c>
+      <c r="J5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1936,7 +1852,7 @@
       </c>
       <c r="J6" s="8" t="inlineStr">
         <is>
-          <t>Filed on TEDUH as “Bayu Ceria”. Latest sales - Block A1: 45 units, Block A2: 202 units, Block B: 100 units</t>
+          <t>Latest sales - Block A1: 45 units, Block A2: 202 units, Block B: 100 units</t>
         </is>
       </c>
     </row>
@@ -2111,11 +2027,7 @@
         <f>H13/$D$13</f>
         <v/>
       </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>Code not yet confirmed against TEDUH.</t>
-        </is>
-      </c>
+      <c r="J13" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2258,7 +2170,7 @@
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>Filed on TEDUH as “Skyline One Sentosa”. Latest sales - Block A: 728 units, Block B: 668 units</t>
+          <t>Latest sales - Block A: 728 units, Block B: 668 units</t>
         </is>
       </c>
     </row>
@@ -2293,11 +2205,7 @@
         <f>H6/$D$6</f>
         <v/>
       </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Skyline Kuchai”.</t>
-        </is>
-      </c>
+      <c r="J6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -2350,11 +2258,7 @@
         <f>H8/$D$8</f>
         <v/>
       </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>Code not yet confirmed against TEDUH.</t>
-        </is>
-      </c>
+      <c r="J8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -2383,11 +2287,7 @@
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>Code not yet confirmed against TEDUH.</t>
-        </is>
-      </c>
+      <c r="J9" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2528,11 +2428,7 @@
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Aetas Seputeh”.</t>
-        </is>
-      </c>
+      <c r="J5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -2594,11 +2490,7 @@
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Amika”.</t>
-        </is>
-      </c>
+      <c r="J7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -2664,11 +2556,7 @@
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Avalon Cybersouth”.</t>
-        </is>
-      </c>
+      <c r="J9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -2701,11 +2589,7 @@
         <f>H10/$D$10</f>
         <v/>
       </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Lakefront Residence”.</t>
-        </is>
-      </c>
+      <c r="J10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -2758,11 +2642,7 @@
         <f>H12/$D$12</f>
         <v/>
       </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>Code not yet confirmed against TEDUH.</t>
-        </is>
-      </c>
+      <c r="J12" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2897,7 +2777,7 @@
       </c>
       <c r="G5" s="11" t="n"/>
       <c r="H5" s="11" t="n">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="I5" s="12">
         <f>H5/$D$5</f>
@@ -3102,7 +2982,7 @@
       </c>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>Filed on TEDUH as “Residensi Ambar Rimba”. Latest sales - Block A: 439 units, Block B: 286 units</t>
+          <t>Latest sales - Block A: 439 units, Block B: 286 units</t>
         </is>
       </c>
     </row>
@@ -3137,11 +3017,7 @@
         <f>H6/$D$6</f>
         <v/>
       </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Aris”.</t>
-        </is>
-      </c>
+      <c r="J6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -3174,11 +3050,7 @@
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Avantro”.</t>
-        </is>
-      </c>
+      <c r="J7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -3211,11 +3083,7 @@
         <f>H8/$D$8</f>
         <v/>
       </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Ayanna”.</t>
-        </is>
-      </c>
+      <c r="J8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -3248,11 +3116,7 @@
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “The Crown”.</t>
-        </is>
-      </c>
+      <c r="J9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -3279,7 +3143,7 @@
       </c>
       <c r="G10" s="11" t="n"/>
       <c r="H10" s="11" t="n">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="I10" s="12">
         <f>H10/$D$10</f>
@@ -3318,11 +3182,7 @@
         <f>H11/$D$11</f>
         <v/>
       </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Simfoni Residensi”.</t>
-        </is>
-      </c>
+      <c r="J11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -3384,11 +3244,7 @@
         <f>H13/$D$13</f>
         <v/>
       </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>Code not yet confirmed against TEDUH.</t>
-        </is>
-      </c>
+      <c r="J13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -3417,11 +3273,7 @@
         <f>H14/$D$14</f>
         <v/>
       </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t>Code not yet confirmed against TEDUH.</t>
-        </is>
-      </c>
+      <c r="J14" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3562,11 +3414,7 @@
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Branniganz Suites @ Bukit Bintang”.</t>
-        </is>
-      </c>
+      <c r="J5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -3599,11 +3447,7 @@
         <f>H6/$D$6</f>
         <v/>
       </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Dataran Sentral (d'clover Residences)”.</t>
-        </is>
-      </c>
+      <c r="J6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -3636,11 +3480,7 @@
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Dataran Sentral (d'terra Residences)”.</t>
-        </is>
-      </c>
+      <c r="J7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -3673,11 +3513,7 @@
         <f>H8/$D$8</f>
         <v/>
       </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Dataran Sentral (d'tessera Residences)”.</t>
-        </is>
-      </c>
+      <c r="J8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -3710,11 +3546,7 @@
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Menara Sutera Indah (hanaz Suites @ Kl City Centre)”.</t>
-        </is>
-      </c>
+      <c r="J9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -3747,11 +3579,7 @@
         <f>H10/$D$10</f>
         <v/>
       </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Menara Sutera Ria (hugoz Suites @ Kl City Centre)”.</t>
-        </is>
-      </c>
+      <c r="J10" s="8" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="7" t="n">
@@ -3784,11 +3612,7 @@
         <f>H11/$D$11</f>
         <v/>
       </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Kyliez Suites @ Kl City Centre”.</t>
-        </is>
-      </c>
+      <c r="J11" s="8" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="7" t="n">
@@ -3821,11 +3645,7 @@
         <f>H12/$D$12</f>
         <v/>
       </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Noordinz Suites @ George Town”.</t>
-        </is>
-      </c>
+      <c r="J12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -3858,11 +3678,7 @@
         <f>H13/$D$13</f>
         <v/>
       </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Menara Kubah (qubaz Suites @ Kuala Terengganu)”.</t>
-        </is>
-      </c>
+      <c r="J13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -3895,11 +3711,7 @@
         <f>H14/$D$14</f>
         <v/>
       </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Sea Crestz @ Kuantan Waterfront Resort City”.</t>
-        </is>
-      </c>
+      <c r="J14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -3926,17 +3738,13 @@
       </c>
       <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="I15" s="12">
         <f>H15/$D$15</f>
         <v/>
       </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Damai Mekar (the Aldenz)”.</t>
-        </is>
-      </c>
+      <c r="J15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -3971,7 +3779,7 @@
       </c>
       <c r="J16" s="8" t="inlineStr">
         <is>
-          <t>Filed on TEDUH as “Residensi Kebun Teh (the Asteriaz @ Kebun Teh)”. -</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -4006,11 +3814,7 @@
         <f>H17/$D$17</f>
         <v/>
       </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “The Fiddlewoodz @ Kl Metropolis”.</t>
-        </is>
-      </c>
+      <c r="J17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -4043,11 +3847,7 @@
         <f>H18/$D$18</f>
         <v/>
       </c>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “The Kingswoodz @ Bukit Jalil”.</t>
-        </is>
-      </c>
+      <c r="J18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -4113,11 +3913,7 @@
         <f>H20/$D$20</f>
         <v/>
       </c>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Mahkota Bukit Jalil”.</t>
-        </is>
-      </c>
+      <c r="J20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -4150,11 +3946,7 @@
         <f>H21/$D$21</f>
         <v/>
       </c>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Seri Lestari (the Vividz @ Bukit Jalil)”.</t>
-        </is>
-      </c>
+      <c r="J21" s="8" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="7" t="n">
@@ -4187,11 +3979,7 @@
         <f>H22/$D$22</f>
         <v/>
       </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Sejahtera Damai (veladaz Residences @ Bukit Jalil)”.</t>
-        </is>
-      </c>
+      <c r="J22" s="8" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="7" t="n">
@@ -4222,7 +4010,7 @@
       </c>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>Code not yet confirmed against TEDUH. Latest sales - Block A: 493 units, Block B: 531 units, Block D: 473 units</t>
+          <t>Latest sales - Block A: 493 units, Block B: 531 units, Block D: 473 units</t>
         </is>
       </c>
     </row>
@@ -4253,11 +4041,7 @@
         <f>H24/$D$24</f>
         <v/>
       </c>
-      <c r="J24" s="8" t="inlineStr">
-        <is>
-          <t>Code not yet confirmed against TEDUH.</t>
-        </is>
-      </c>
+      <c r="J24" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4398,11 +4182,7 @@
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Meridin East”.</t>
-        </is>
-      </c>
+      <c r="J5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -4435,11 +4215,7 @@
         <f>H6/$D$6</f>
         <v/>
       </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Ferringhi Residence”.</t>
-        </is>
-      </c>
+      <c r="J6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">
@@ -4472,11 +4248,7 @@
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Meridin East Jasmine 2”.</t>
-        </is>
-      </c>
+      <c r="J7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -4503,7 +4275,7 @@
       </c>
       <c r="G8" s="11" t="n"/>
       <c r="H8" s="11" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I8" s="12">
         <f>H8/$D$8</f>
@@ -4542,11 +4314,7 @@
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi M Aria”.</t>
-        </is>
-      </c>
+      <c r="J9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -4581,7 +4349,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>Filed on TEDUH as “Residensi M Aspira”. Latest sales - Block A: 460 units, Block B: 549 units</t>
+          <t>Latest sales - Block A: 460 units, Block B: 549 units</t>
         </is>
       </c>
     </row>
@@ -4618,7 +4386,7 @@
       </c>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>Filed on TEDUH as “Residensi M Aurora”. Latest sales - Block A: 51 units, Block B: 304 units</t>
+          <t>Latest sales - Block A: 51 units, Block B: 304 units</t>
         </is>
       </c>
     </row>
@@ -4653,11 +4421,7 @@
         <f>H12/$D$12</f>
         <v/>
       </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi M Azura”.</t>
-        </is>
-      </c>
+      <c r="J12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -4723,11 +4487,7 @@
         <f>H14/$D$14</f>
         <v/>
       </c>
-      <c r="J14" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi M Nova”.</t>
-        </is>
-      </c>
+      <c r="J14" s="8" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="7" t="n">
@@ -4760,11 +4520,7 @@
         <f>H15/$D$15</f>
         <v/>
       </c>
-      <c r="J15" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Panora”.</t>
-        </is>
-      </c>
+      <c r="J15" s="8" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="7" t="n">
@@ -4797,11 +4553,7 @@
         <f>H16/$D$16</f>
         <v/>
       </c>
-      <c r="J16" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “M Sinar”.</t>
-        </is>
-      </c>
+      <c r="J16" s="8" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="7" t="n">
@@ -4828,17 +4580,13 @@
       </c>
       <c r="G17" s="11" t="n"/>
       <c r="H17" s="11" t="n">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="I17" s="12">
         <f>H17/$D$17</f>
         <v/>
       </c>
-      <c r="J17" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi M Terra”.</t>
-        </is>
-      </c>
+      <c r="J17" s="8" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="7" t="n">
@@ -4871,11 +4619,7 @@
         <f>H18/$D$18</f>
         <v/>
       </c>
-      <c r="J18" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Taman Tiara Indah (m Tiara)”.</t>
-        </is>
-      </c>
+      <c r="J18" s="8" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="7" t="n">
@@ -4941,11 +4685,7 @@
         <f>H20/$D$20</f>
         <v/>
       </c>
-      <c r="J20" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi M Zenya”.</t>
-        </is>
-      </c>
+      <c r="J20" s="8" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="7" t="n">
@@ -4968,7 +4708,7 @@
       <c r="F21" s="8" t="inlineStr"/>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="I21" s="12">
         <f>H21/$D$21</f>
@@ -4976,7 +4716,7 @@
       </c>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>Code not yet confirmed against TEDUH. Latest sales - Block A: 499 units, Block B: 257 units</t>
+          <t>Latest sales - Block A: 499 units, Block B: 257 units</t>
         </is>
       </c>
     </row>
@@ -5007,11 +4747,7 @@
         <f>H22/$D$22</f>
         <v/>
       </c>
-      <c r="J22" s="8" t="inlineStr">
-        <is>
-          <t>Code not yet confirmed against TEDUH.</t>
-        </is>
-      </c>
+      <c r="J22" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5152,11 +4888,7 @@
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Gen”.</t>
-        </is>
-      </c>
+      <c r="J5" s="8" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -5226,11 +4958,7 @@
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Gen”.</t>
-        </is>
-      </c>
+      <c r="J7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -5263,11 +4991,7 @@
         <f>H8/$D$8</f>
         <v/>
       </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Majestic”.</t>
-        </is>
-      </c>
+      <c r="J8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -5300,11 +5024,7 @@
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Taman Yu”.</t>
-        </is>
-      </c>
+      <c r="J9" s="8" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="7" t="n">
@@ -5339,7 +5059,7 @@
       </c>
       <c r="J10" s="8" t="inlineStr">
         <is>
-          <t>Filed on TEDUH as “Soho Sunway Majestic”. Latest sales - Block A: 297 units, Block B: 93 units</t>
+          <t>Latest sales - Block A: 297 units, Block B: 93 units</t>
         </is>
       </c>
     </row>
@@ -5394,11 +5114,7 @@
         <f>H12/$D$12</f>
         <v/>
       </c>
-      <c r="J12" s="8" t="inlineStr">
-        <is>
-          <t>Code not yet confirmed against TEDUH.</t>
-        </is>
-      </c>
+      <c r="J12" s="8" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="7" t="n">
@@ -5427,11 +5143,7 @@
         <f>H13/$D$13</f>
         <v/>
       </c>
-      <c r="J13" s="8" t="inlineStr">
-        <is>
-          <t>Code not yet confirmed against TEDUH.</t>
-        </is>
-      </c>
+      <c r="J13" s="8" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="7" t="n">
@@ -5662,11 +5374,7 @@
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Pavilion Bukit Jalil”.</t>
-        </is>
-      </c>
+      <c r="J7" s="8" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -5699,11 +5407,7 @@
         <f>H8/$D$8</f>
         <v/>
       </c>
-      <c r="J8" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Kerinchi Ria”.</t>
-        </is>
-      </c>
+      <c r="J8" s="8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="7" t="n">
@@ -5732,11 +5436,7 @@
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>Code not yet confirmed against TEDUH.</t>
-        </is>
-      </c>
+      <c r="J9" s="8" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5910,11 +5610,7 @@
         <f>H6/$D$6</f>
         <v/>
       </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>Filed on TEDUH as “Residensi Maxim D'parc”.</t>
-        </is>
-      </c>
+      <c r="J6" s="8" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="7" t="n">

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -604,7 +604,9 @@
           <t>Alderwood Residence</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
+      <c r="C5" s="9" t="n">
+        <v>46028</v>
+      </c>
       <c r="D5" s="10" t="n">
         <v>186</v>
       </c>
@@ -637,7 +639,9 @@
           <t>Armani Avani</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n"/>
+      <c r="C6" s="9" t="n">
+        <v>46086</v>
+      </c>
       <c r="D6" s="10" t="n">
         <v>328</v>
       </c>
@@ -670,7 +674,9 @@
           <t>Armani Business Park</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
+      <c r="C7" s="9" t="n">
+        <v>45632</v>
+      </c>
       <c r="D7" s="10" t="n">
         <v>44</v>
       </c>
@@ -703,7 +709,9 @@
           <t>Armani Cameron Residence</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n"/>
+      <c r="C8" s="9" t="n">
+        <v>45790</v>
+      </c>
       <c r="D8" s="10" t="n">
         <v>232</v>
       </c>
@@ -732,7 +740,9 @@
           <t>Armani Hallson KLCC</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n"/>
+      <c r="C9" s="9" t="n">
+        <v>45820</v>
+      </c>
       <c r="D9" s="10" t="n">
         <v>2215</v>
       </c>
@@ -765,7 +775,9 @@
           <t>Armani Residence Kepong</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n"/>
+      <c r="C10" s="9" t="n">
+        <v>45436</v>
+      </c>
       <c r="D10" s="10" t="n">
         <v>306</v>
       </c>
@@ -798,7 +810,9 @@
           <t>Armani Residence Setia Alam</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n"/>
+      <c r="C11" s="9" t="n">
+        <v>45561</v>
+      </c>
       <c r="D11" s="10" t="n">
         <v>648</v>
       </c>
@@ -827,7 +841,9 @@
           <t>Armani Residence Setia Alam 2</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n"/>
+      <c r="C12" s="9" t="n">
+        <v>46162</v>
+      </c>
       <c r="D12" s="10" t="n">
         <v>998</v>
       </c>
@@ -856,7 +872,9 @@
           <t>Armani Residence Shah Alam</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n"/>
+      <c r="C13" s="9" t="n">
+        <v>45303</v>
+      </c>
       <c r="D13" s="10" t="n">
         <v>338</v>
       </c>
@@ -889,7 +907,9 @@
           <t>Armani Signature Residence</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n"/>
+      <c r="C14" s="9" t="n">
+        <v>45252</v>
+      </c>
       <c r="D14" s="10" t="n">
         <v>315</v>
       </c>
@@ -922,7 +942,9 @@
           <t>Lofthill Residence</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n"/>
+      <c r="C15" s="9" t="n">
+        <v>45506</v>
+      </c>
       <c r="D15" s="10" t="n">
         <v>653</v>
       </c>
@@ -955,7 +977,9 @@
           <t>Residensi Armani Kg Baru 1</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n"/>
+      <c r="C16" s="9" t="n">
+        <v>45632</v>
+      </c>
       <c r="D16" s="10" t="n">
         <v>387</v>
       </c>
@@ -988,7 +1012,9 @@
           <t>Residensi Armani Putra</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n"/>
+      <c r="C17" s="9" t="n">
+        <v>46183</v>
+      </c>
       <c r="D17" s="10" t="n">
         <v>984</v>
       </c>
@@ -1021,7 +1047,9 @@
           <t>Taman Bukit Tualang 2</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n"/>
+      <c r="C18" s="9" t="n">
+        <v>46238</v>
+      </c>
       <c r="D18" s="10" t="n">
         <v>30</v>
       </c>
@@ -1054,7 +1082,9 @@
           <t>Armani Prestige</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n"/>
+      <c r="C19" s="9" t="n">
+        <v>45862</v>
+      </c>
       <c r="D19" s="10" t="n">
         <v>280</v>
       </c>
@@ -1083,7 +1113,9 @@
           <t>Taman PMINT Tebing Tembah 2</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n"/>
+      <c r="C20" s="9" t="n">
+        <v>46263</v>
+      </c>
       <c r="D20" s="10" t="n">
         <v>116</v>
       </c>
@@ -1220,7 +1252,9 @@
           <t>MHP3 Residences</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
+      <c r="C5" s="9" t="n">
+        <v>45270</v>
+      </c>
       <c r="D5" s="10" t="n">
         <v>1688</v>
       </c>
@@ -1253,7 +1287,9 @@
           <t>PV22 Residences</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n"/>
+      <c r="C6" s="9" t="n">
+        <v>45334</v>
+      </c>
       <c r="D6" s="10" t="n">
         <v>2082</v>
       </c>
@@ -1286,7 +1322,9 @@
           <t>Platinum Melati Residences</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
+      <c r="C7" s="9" t="n">
+        <v>45827</v>
+      </c>
       <c r="D7" s="10" t="n">
         <v>794</v>
       </c>
@@ -1319,7 +1357,9 @@
           <t>PSV1 Residences</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n"/>
+      <c r="C8" s="9" t="n">
+        <v>45965</v>
+      </c>
       <c r="D8" s="10" t="n">
         <v>500</v>
       </c>
@@ -1348,7 +1388,9 @@
           <t>PSV2 Residences</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n"/>
+      <c r="C9" s="9" t="n">
+        <v>45610</v>
+      </c>
       <c r="D9" s="10" t="n">
         <v>1500</v>
       </c>
@@ -1381,7 +1423,9 @@
           <t>The Maison 23</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n"/>
+      <c r="C10" s="9" t="n">
+        <v>45714</v>
+      </c>
       <c r="D10" s="10" t="n">
         <v>23</v>
       </c>
@@ -1542,7 +1586,9 @@
           <t>SkyAwani PRIMA Residences</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
+      <c r="C5" s="9" t="n">
+        <v>45860</v>
+      </c>
       <c r="D5" s="10" t="n">
         <v>492</v>
       </c>
@@ -1571,7 +1617,9 @@
           <t>Curvo Residences</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n"/>
+      <c r="C6" s="9" t="n">
+        <v>46033</v>
+      </c>
       <c r="D6" s="10" t="n">
         <v>830</v>
       </c>
@@ -1600,7 +1648,9 @@
           <t>SkyAman 1 Residences</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
+      <c r="C7" s="9" t="n">
+        <v>45819</v>
+      </c>
       <c r="D7" s="10" t="n">
         <v>510</v>
       </c>
@@ -1629,7 +1679,9 @@
           <t>SkyWorld Pearlmont</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n"/>
+      <c r="C8" s="9" t="n">
+        <v>45855</v>
+      </c>
       <c r="D8" s="10" t="n">
         <v>0</v>
       </c>
@@ -1658,7 +1710,9 @@
           <t>Vesta Residences</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n"/>
+      <c r="C9" s="9" t="n">
+        <v>46220</v>
+      </c>
       <c r="D9" s="10" t="n">
         <v>1001</v>
       </c>
@@ -1795,7 +1849,9 @@
           <t>Trinity Nordic/Zia</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
+      <c r="C5" s="9" t="n">
+        <v>45813</v>
+      </c>
       <c r="D5" s="10" t="n">
         <v>714</v>
       </c>
@@ -1828,7 +1884,9 @@
           <t>Trinity Sensoria</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n"/>
+      <c r="C6" s="9" t="n">
+        <v>45575</v>
+      </c>
       <c r="D6" s="10" t="n">
         <v>737</v>
       </c>
@@ -2009,7 +2067,9 @@
           <t>Trinity Rainfora</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n"/>
+      <c r="C13" s="9" t="n">
+        <v>46165</v>
+      </c>
       <c r="D13" s="10" t="n">
         <v>535</v>
       </c>
@@ -2146,7 +2206,9 @@
           <t>Skyline (Eastside) @ OneSentosa</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
+      <c r="C5" s="9" t="n">
+        <v>45889</v>
+      </c>
       <c r="D5" s="10" t="n">
         <v>1623</v>
       </c>
@@ -2183,7 +2245,9 @@
           <t>Skyline Kuchai</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n"/>
+      <c r="C6" s="9" t="n">
+        <v>46035</v>
+      </c>
       <c r="D6" s="10" t="n">
         <v>1838</v>
       </c>
@@ -2240,7 +2304,9 @@
           <t>Residence Hill</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n"/>
+      <c r="C8" s="9" t="n">
+        <v>44394</v>
+      </c>
       <c r="D8" s="10" t="n">
         <v>42</v>
       </c>
@@ -2269,7 +2335,9 @@
           <t>Skyline Embassy</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n"/>
+      <c r="C9" s="9" t="n">
+        <v>45565</v>
+      </c>
       <c r="D9" s="10" t="n">
         <v>1296</v>
       </c>
@@ -2406,7 +2474,9 @@
           <t>Aetas Seputeh</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
+      <c r="C5" s="9" t="n">
+        <v>45450</v>
+      </c>
       <c r="D5" s="10" t="n">
         <v>126</v>
       </c>
@@ -2439,7 +2509,9 @@
           <t>Alora Residences @ Avenue25</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n"/>
+      <c r="C6" s="9" t="n">
+        <v>45744</v>
+      </c>
       <c r="D6" s="10" t="n">
         <v>770</v>
       </c>
@@ -2468,7 +2540,9 @@
           <t>Amika Residences</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
+      <c r="C7" s="9" t="n">
+        <v>45366</v>
+      </c>
       <c r="D7" s="10" t="n">
         <v>468</v>
       </c>
@@ -2501,7 +2575,9 @@
           <t>Anja Residences &amp; Signature Retail</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n"/>
+      <c r="C8" s="9" t="n">
+        <v>45463</v>
+      </c>
       <c r="D8" s="10" t="n">
         <v>900</v>
       </c>
@@ -2534,7 +2610,9 @@
           <t>Avalon</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n"/>
+      <c r="C9" s="9" t="n">
+        <v>45845</v>
+      </c>
       <c r="D9" s="10" t="n">
         <v>343</v>
       </c>
@@ -2567,7 +2645,9 @@
           <t>Sanderling 2 Lakefront</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n"/>
+      <c r="C10" s="9" t="n">
+        <v>45559</v>
+      </c>
       <c r="D10" s="10" t="n">
         <v>606</v>
       </c>
@@ -2624,7 +2704,9 @@
           <t>Aetas Taman Desa</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n"/>
+      <c r="C12" s="9" t="n">
+        <v>45638</v>
+      </c>
       <c r="D12" s="10" t="n">
         <v>226</v>
       </c>
@@ -2761,7 +2843,9 @@
           <t>Binastra Cochrane</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
+      <c r="C5" s="9" t="n">
+        <v>46205</v>
+      </c>
       <c r="D5" s="10" t="n">
         <v>830</v>
       </c>
@@ -2958,7 +3042,9 @@
           <t>Amberwood Resort Residences</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
+      <c r="C5" s="9" t="n">
+        <v>46028</v>
+      </c>
       <c r="D5" s="10" t="n">
         <v>824</v>
       </c>
@@ -2995,7 +3081,9 @@
           <t>Aricia Residences</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n"/>
+      <c r="C6" s="9" t="n">
+        <v>45682</v>
+      </c>
       <c r="D6" s="10" t="n">
         <v>787</v>
       </c>
@@ -3028,7 +3116,9 @@
           <t>Avantro Residences</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
+      <c r="C7" s="9" t="n">
+        <v>45258</v>
+      </c>
       <c r="D7" s="10" t="n">
         <v>842</v>
       </c>
@@ -3061,7 +3151,9 @@
           <t>Ayanna Resort Residences</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n"/>
+      <c r="C8" s="9" t="n">
+        <v>46194</v>
+      </c>
       <c r="D8" s="10" t="n">
         <v>824</v>
       </c>
@@ -3094,7 +3186,9 @@
           <t>Crown Penang</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n"/>
+      <c r="C9" s="9" t="n">
+        <v>45503</v>
+      </c>
       <c r="D9" s="10" t="n">
         <v>588</v>
       </c>
@@ -3127,7 +3221,9 @@
           <t>DIVINE KLCC</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n"/>
+      <c r="C10" s="9" t="n">
+        <v>46194</v>
+      </c>
       <c r="D10" s="10" t="n">
         <v>1033</v>
       </c>
@@ -3160,7 +3256,9 @@
           <t>Quaver Residence</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n"/>
+      <c r="C11" s="9" t="n">
+        <v>46258</v>
+      </c>
       <c r="D11" s="10" t="n">
         <v>684</v>
       </c>
@@ -3193,7 +3291,9 @@
           <t>Residensi Andalan</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n"/>
+      <c r="C12" s="9" t="n">
+        <v>45488</v>
+      </c>
       <c r="D12" s="10" t="n">
         <v>823</v>
       </c>
@@ -3226,7 +3326,9 @@
           <t>Botanica Hills</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n"/>
+      <c r="C13" s="9" t="n">
+        <v>45896</v>
+      </c>
       <c r="D13" s="10" t="n">
         <v>231</v>
       </c>
@@ -3255,7 +3357,9 @@
           <t>Dawn KLCC</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n"/>
+      <c r="C14" s="9" t="n">
+        <v>45505</v>
+      </c>
       <c r="D14" s="10" t="n">
         <v>492</v>
       </c>
@@ -3392,7 +3496,9 @@
           <t>Branniganz Suites</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
+      <c r="C5" s="9" t="n">
+        <v>45518</v>
+      </c>
       <c r="D5" s="10" t="n">
         <v>269</v>
       </c>
@@ -3425,7 +3531,9 @@
           <t>D'Clover Residences</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n"/>
+      <c r="C6" s="9" t="n">
+        <v>46042</v>
+      </c>
       <c r="D6" s="10" t="n">
         <v>593</v>
       </c>
@@ -3458,7 +3566,9 @@
           <t>D'Terra Residences</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
+      <c r="C7" s="9" t="n">
+        <v>46042</v>
+      </c>
       <c r="D7" s="10" t="n">
         <v>767</v>
       </c>
@@ -3491,7 +3601,9 @@
           <t>D'Tessera Residences</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n"/>
+      <c r="C8" s="9" t="n">
+        <v>46129</v>
+      </c>
       <c r="D8" s="10" t="n">
         <v>671</v>
       </c>
@@ -3524,7 +3636,9 @@
           <t>Hanaz Suites</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n"/>
+      <c r="C9" s="9" t="n">
+        <v>45659</v>
+      </c>
       <c r="D9" s="10" t="n">
         <v>98</v>
       </c>
@@ -3557,7 +3671,9 @@
           <t>Hugoz Suites</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n"/>
+      <c r="C10" s="9" t="n">
+        <v>46280</v>
+      </c>
       <c r="D10" s="10" t="n">
         <v>320</v>
       </c>
@@ -3590,7 +3706,9 @@
           <t>Kyliez Suites</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n"/>
+      <c r="C11" s="9" t="n">
+        <v>45511</v>
+      </c>
       <c r="D11" s="10" t="n">
         <v>126</v>
       </c>
@@ -3623,7 +3741,9 @@
           <t>Noordinz Suites</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n"/>
+      <c r="C12" s="9" t="n">
+        <v>45251</v>
+      </c>
       <c r="D12" s="10" t="n">
         <v>603</v>
       </c>
@@ -3656,7 +3776,9 @@
           <t>Qubaz Suites</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n"/>
+      <c r="C13" s="9" t="n">
+        <v>45716</v>
+      </c>
       <c r="D13" s="10" t="n">
         <v>759</v>
       </c>
@@ -3689,7 +3811,9 @@
           <t>Sea Crestz</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n"/>
+      <c r="C14" s="9" t="n">
+        <v>45736</v>
+      </c>
       <c r="D14" s="10" t="n">
         <v>456</v>
       </c>
@@ -3722,7 +3846,9 @@
           <t>The Aldenz</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n"/>
+      <c r="C15" s="9" t="n">
+        <v>45839</v>
+      </c>
       <c r="D15" s="10" t="n">
         <v>662</v>
       </c>
@@ -3755,7 +3881,9 @@
           <t>The Asteriaz</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n"/>
+      <c r="C16" s="9" t="n">
+        <v>45856</v>
+      </c>
       <c r="D16" s="10" t="n">
         <v>848</v>
       </c>
@@ -3792,7 +3920,9 @@
           <t>The Fiddlewoodz</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n"/>
+      <c r="C17" s="9" t="n">
+        <v>46108</v>
+      </c>
       <c r="D17" s="10" t="n">
         <v>679</v>
       </c>
@@ -3825,7 +3955,9 @@
           <t>The Kingswoodz</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n"/>
+      <c r="C18" s="9" t="n">
+        <v>45516</v>
+      </c>
       <c r="D18" s="10" t="n">
         <v>1558</v>
       </c>
@@ -3858,7 +3990,9 @@
           <t>The Lighthauz</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n"/>
+      <c r="C19" s="9" t="n">
+        <v>45952</v>
+      </c>
       <c r="D19" s="10" t="n">
         <v>671</v>
       </c>
@@ -3891,7 +4025,9 @@
           <t>The Queenswoodz</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n"/>
+      <c r="C20" s="9" t="n">
+        <v>46099</v>
+      </c>
       <c r="D20" s="10" t="n">
         <v>1004</v>
       </c>
@@ -3924,7 +4060,9 @@
           <t>The Vividz</t>
         </is>
       </c>
-      <c r="C21" s="9" t="n"/>
+      <c r="C21" s="9" t="n">
+        <v>45806</v>
+      </c>
       <c r="D21" s="10" t="n">
         <v>1138</v>
       </c>
@@ -3957,7 +4095,9 @@
           <t>Veladaz Residences</t>
         </is>
       </c>
-      <c r="C22" s="9" t="n"/>
+      <c r="C22" s="9" t="n">
+        <v>45218</v>
+      </c>
       <c r="D22" s="10" t="n">
         <v>508</v>
       </c>
@@ -3990,7 +4130,9 @@
           <t>Causewayz Square @ JBCC</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n"/>
+      <c r="C23" s="9" t="n">
+        <v>45966</v>
+      </c>
       <c r="D23" s="10" t="n">
         <v>3692</v>
       </c>
@@ -4023,7 +4165,9 @@
           <t>The Stallionz</t>
         </is>
       </c>
-      <c r="C24" s="9" t="n"/>
+      <c r="C24" s="9" t="n">
+        <v>45936</v>
+      </c>
       <c r="D24" s="10" t="n">
         <v>424</v>
       </c>
@@ -4160,7 +4304,9 @@
           <t>Allamanda 5 &amp; 6 @ Meridin East</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
+      <c r="C5" s="9" t="n">
+        <v>45712</v>
+      </c>
       <c r="D5" s="10" t="n">
         <v>235</v>
       </c>
@@ -4193,7 +4339,9 @@
           <t>Ferringhi Residence 2</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n"/>
+      <c r="C6" s="9" t="n">
+        <v>44060</v>
+      </c>
       <c r="D6" s="10" t="n">
         <v>478</v>
       </c>
@@ -4226,7 +4374,9 @@
           <t>Jasmine 2 @ Meridin East</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
+      <c r="C7" s="9" t="n">
+        <v>45691</v>
+      </c>
       <c r="D7" s="10" t="n">
         <v>168</v>
       </c>
@@ -4259,7 +4409,9 @@
           <t>M Amaya</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n"/>
+      <c r="C8" s="9" t="n">
+        <v>46161</v>
+      </c>
       <c r="D8" s="10" t="n">
         <v>833</v>
       </c>
@@ -4292,7 +4444,9 @@
           <t>M Aria</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n"/>
+      <c r="C9" s="9" t="n">
+        <v>46036</v>
+      </c>
       <c r="D9" s="10" t="n">
         <v>606</v>
       </c>
@@ -4325,7 +4479,9 @@
           <t>M Aspira</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n"/>
+      <c r="C10" s="9" t="n">
+        <v>45531</v>
+      </c>
       <c r="D10" s="10" t="n">
         <v>1618</v>
       </c>
@@ -4362,7 +4518,9 @@
           <t>M Aurora</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n"/>
+      <c r="C11" s="9" t="n">
+        <v>46100</v>
+      </c>
       <c r="D11" s="10" t="n">
         <v>1544</v>
       </c>
@@ -4399,7 +4557,9 @@
           <t>M Azura</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n"/>
+      <c r="C12" s="9" t="n">
+        <v>45531</v>
+      </c>
       <c r="D12" s="10" t="n">
         <v>1140</v>
       </c>
@@ -4432,7 +4592,9 @@
           <t>M Legasi</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n"/>
+      <c r="C13" s="9" t="n">
+        <v>45754</v>
+      </c>
       <c r="D13" s="10" t="n">
         <v>330</v>
       </c>
@@ -4465,7 +4627,9 @@
           <t>M Nova</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n"/>
+      <c r="C14" s="9" t="n">
+        <v>45574</v>
+      </c>
       <c r="D14" s="10" t="n">
         <v>2080</v>
       </c>
@@ -4498,7 +4662,9 @@
           <t>M Panora</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n"/>
+      <c r="C15" s="9" t="n">
+        <v>45906</v>
+      </c>
       <c r="D15" s="10" t="n">
         <v>396</v>
       </c>
@@ -4531,7 +4697,9 @@
           <t>M Sinar @ Southville City</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n"/>
+      <c r="C16" s="9" t="n">
+        <v>45443</v>
+      </c>
       <c r="D16" s="10" t="n">
         <v>999</v>
       </c>
@@ -4564,7 +4732,9 @@
           <t>M Terra</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n"/>
+      <c r="C17" s="9" t="n">
+        <v>45498</v>
+      </c>
       <c r="D17" s="10" t="n">
         <v>999</v>
       </c>
@@ -4597,7 +4767,9 @@
           <t>M Tiara</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n"/>
+      <c r="C18" s="9" t="n">
+        <v>45523</v>
+      </c>
       <c r="D18" s="10" t="n">
         <v>223</v>
       </c>
@@ -4630,7 +4802,9 @@
           <t>M Zenni</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n"/>
+      <c r="C19" s="9" t="n">
+        <v>45923</v>
+      </c>
       <c r="D19" s="10" t="n">
         <v>494</v>
       </c>
@@ -4663,7 +4837,9 @@
           <t>M Zenya</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n"/>
+      <c r="C20" s="9" t="n">
+        <v>45383</v>
+      </c>
       <c r="D20" s="10" t="n">
         <v>619</v>
       </c>
@@ -4696,7 +4872,9 @@
           <t>M Grand Minori</t>
         </is>
       </c>
-      <c r="C21" s="9" t="n"/>
+      <c r="C21" s="9" t="n">
+        <v>45898</v>
+      </c>
       <c r="D21" s="10" t="n">
         <v>1733</v>
       </c>
@@ -4729,7 +4907,9 @@
           <t>M Minori</t>
         </is>
       </c>
-      <c r="C22" s="9" t="n"/>
+      <c r="C22" s="9" t="n">
+        <v>45201</v>
+      </c>
       <c r="D22" s="10" t="n">
         <v>1526</v>
       </c>
@@ -4866,7 +5046,9 @@
           <t>Gen Rise</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
+      <c r="C5" s="9" t="n">
+        <v>45631</v>
+      </c>
       <c r="D5" s="10" t="n">
         <v>732</v>
       </c>
@@ -4899,7 +5081,9 @@
           <t>Gen Sphere</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n"/>
+      <c r="C6" s="9" t="n">
+        <v>45804</v>
+      </c>
       <c r="D6" s="10" t="n">
         <v>996</v>
       </c>
@@ -4936,7 +5120,9 @@
           <t>Gen Starz</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
+      <c r="C7" s="9" t="n">
+        <v>45569</v>
+      </c>
       <c r="D7" s="10" t="n">
         <v>360</v>
       </c>
@@ -4969,7 +5155,9 @@
           <t>Majestic Residence</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n"/>
+      <c r="C8" s="9" t="n">
+        <v>44995</v>
+      </c>
       <c r="D8" s="10" t="n">
         <v>478</v>
       </c>
@@ -5002,7 +5190,9 @@
           <t>Majestic Yu</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n"/>
+      <c r="C9" s="9" t="n">
+        <v>45831</v>
+      </c>
       <c r="D9" s="10" t="n">
         <v>106</v>
       </c>
@@ -5035,7 +5225,9 @@
           <t>Yahya Awal Mixed Development (JV with Sunway Property)</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n"/>
+      <c r="C10" s="9" t="n">
+        <v>45936</v>
+      </c>
       <c r="D10" s="10" t="n">
         <v>1012</v>
       </c>
@@ -5096,7 +5288,9 @@
           <t>Majestic Aman</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n"/>
+      <c r="C12" s="9" t="n">
+        <v>45813</v>
+      </c>
       <c r="D12" s="10" t="n">
         <v>73</v>
       </c>
@@ -5125,7 +5319,9 @@
           <t>Majestic Flora</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n"/>
+      <c r="C13" s="9" t="n">
+        <v>46191</v>
+      </c>
       <c r="D13" s="10" t="n">
         <v>140</v>
       </c>
@@ -5286,7 +5482,9 @@
           <t>Mutiara Kempas</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
+      <c r="C5" s="9" t="n">
+        <v>46121</v>
+      </c>
       <c r="D5" s="10" t="n">
         <v>562</v>
       </c>
@@ -5319,7 +5517,9 @@
           <t>Mutiara Lake Puchong</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n"/>
+      <c r="C6" s="9" t="n">
+        <v>46108</v>
+      </c>
       <c r="D6" s="10" t="n">
         <v>526</v>
       </c>
@@ -5352,7 +5552,9 @@
           <t>Park Green @ Pavilion Bukit Jalil</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
+      <c r="C7" s="9" t="n">
+        <v>45565</v>
+      </c>
       <c r="D7" s="10" t="n">
         <v>453</v>
       </c>
@@ -5385,7 +5587,9 @@
           <t>Ria Bangsar South</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n"/>
+      <c r="C8" s="9" t="n">
+        <v>45768</v>
+      </c>
       <c r="D8" s="10" t="n">
         <v>336</v>
       </c>
@@ -5418,7 +5622,9 @@
           <t>River Park Bangsar South</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n"/>
+      <c r="C9" s="9" t="n">
+        <v>46078</v>
+      </c>
       <c r="D9" s="10" t="n">
         <v>1332</v>
       </c>
@@ -5555,7 +5761,9 @@
           <t>Residensi Max II</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n"/>
+      <c r="C5" s="9" t="n">
+        <v>46199</v>
+      </c>
       <c r="D5" s="10" t="n">
         <v>604</v>
       </c>
@@ -5588,7 +5796,9 @@
           <t>Residensi Maxim D’Parc</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n"/>
+      <c r="C6" s="9" t="n">
+        <v>46057</v>
+      </c>
       <c r="D6" s="10" t="n">
         <v>1116</v>
       </c>
@@ -5621,7 +5831,9 @@
           <t>Residensi Maxim Pelangi</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
+      <c r="C7" s="9" t="n">
+        <v>45884</v>
+      </c>
       <c r="D7" s="10" t="n">
         <v>2743</v>
       </c>
@@ -5658,7 +5870,9 @@
           <t>Residensi Maxim Risen</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n"/>
+      <c r="C8" s="9" t="n">
+        <v>46194</v>
+      </c>
       <c r="D8" s="10" t="n">
         <v>1236</v>
       </c>
@@ -5691,7 +5905,9 @@
           <t>Residensi The Atas</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n"/>
+      <c r="C9" s="9" t="n">
+        <v>45412</v>
+      </c>
       <c r="D9" s="10" t="n">
         <v>624</v>
       </c>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -1149,7 +1149,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Platinum Melati Residences</t>
+          <t>Platinum Melati Residences (Vista Melati)</t>
         </is>
       </c>
       <c r="C7" s="9" t="n">
@@ -1444,30 +1444,6 @@
         <v/>
       </c>
       <c r="J10" s="8" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="n">
-        <v>7</v>
-      </c>
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Vista Melati</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="10" t="n">
-        <v>794</v>
-      </c>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="12" t="n"/>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>Code 31008-1 removed: TEDUH confirms it is Residensi Platinum Melati (794 units), which is the row above. No code matched yet.</t>
-        </is>
-      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -17,9 +17,10 @@
     <sheet name="Malton" sheetId="8" state="visible" r:id="rId8"/>
     <sheet name="Maxim" sheetId="9" state="visible" r:id="rId9"/>
     <sheet name="Platinum Victory" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="Skyworld" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="Trinity Group" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="TS Law" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="Radium" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="Skyworld" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="Trinity Group" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="TS Law" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,7 +1115,7 @@
         </is>
       </c>
       <c r="C20" s="9" t="n">
-        <v>46263</v>
+        <v>45167</v>
       </c>
       <c r="D20" s="10" t="n">
         <v>116</v>
@@ -1358,7 +1359,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>45965</v>
+        <v>44869</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>500</v>
@@ -1491,7 +1492,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>WEEKLY TEDUH SALES REPORT (SKYWORLD)</t>
+          <t>WEEKLY TEDUH SALES REPORT (RADIUM)</t>
         </is>
       </c>
       <c r="G3" s="4" t="n">
@@ -1559,30 +1560,38 @@
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>SkyAwani PRIMA Residences</t>
+          <t>Radium Adesa @ KL (incl. Adesa Luxe Residences)</t>
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>45860</v>
+        <v>45100</v>
       </c>
       <c r="D5" s="10" t="n">
-        <v>492</v>
+        <v>1218</v>
       </c>
       <c r="E5" s="7" t="inlineStr">
         <is>
-          <t>31051-1</t>
-        </is>
-      </c>
-      <c r="F5" s="8" t="inlineStr"/>
+          <t>30363-2</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>FITRAH RESOURCES SDN. BHD.</t>
+        </is>
+      </c>
       <c r="G5" s="11" t="n"/>
       <c r="H5" s="11" t="n">
-        <v>457</v>
+        <v>1127</v>
       </c>
       <c r="I5" s="12">
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr"/>
+      <c r="J5" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 181 units, Block B: 582 units, Block C: 362 units</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="7" t="n">
@@ -1590,24 +1599,28 @@
       </c>
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Curvo Residences</t>
+          <t>Vista Adesa @ KL</t>
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>46033</v>
+        <v>45054</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>830</v>
+        <v>1218</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>30176-1</t>
-        </is>
-      </c>
-      <c r="F6" s="8" t="inlineStr"/>
+          <t>30363-1</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr">
+        <is>
+          <t>FITRAH RESOURCES SDN. BHD.</t>
+        </is>
+      </c>
       <c r="G6" s="11" t="n"/>
       <c r="H6" s="11" t="n">
-        <v>656</v>
+        <v>1123</v>
       </c>
       <c r="I6" s="12">
         <f>H6/$D$6</f>
@@ -1621,30 +1634,38 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>SkyAman 1 Residences</t>
+          <t>Radium Arena @ Old Klang Road</t>
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>45819</v>
+        <v>45590</v>
       </c>
       <c r="D7" s="10" t="n">
-        <v>510</v>
+        <v>988</v>
       </c>
       <c r="E7" s="7" t="inlineStr">
         <is>
-          <t>30976-1</t>
-        </is>
-      </c>
-      <c r="F7" s="8" t="inlineStr"/>
+          <t>30821-1</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr">
+        <is>
+          <t>RADIUM GLOBAL SDN. BHD.</t>
+        </is>
+      </c>
       <c r="G7" s="11" t="n"/>
       <c r="H7" s="11" t="n">
-        <v>240</v>
+        <v>520</v>
       </c>
       <c r="I7" s="12">
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr"/>
+      <c r="J7" s="8" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 259 units, Block B: 260 units</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="7" t="n">
@@ -1652,24 +1673,28 @@
       </c>
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>SkyWorld Pearlmont</t>
+          <t>Chancery Ampang @ KL</t>
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>45855</v>
+        <v>44880</v>
       </c>
       <c r="D8" s="10" t="n">
-        <v>0</v>
+        <v>944</v>
       </c>
       <c r="E8" s="7" t="inlineStr">
         <is>
-          <t>31075-1,31075-2</t>
-        </is>
-      </c>
-      <c r="F8" s="8" t="inlineStr"/>
+          <t>30121-1</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr">
+        <is>
+          <t>IDAMAN SEJIWA (AMPANG) SDN. BHD.</t>
+        </is>
+      </c>
       <c r="G8" s="11" t="n"/>
       <c r="H8" s="11" t="n">
-        <v>1345</v>
+        <v>379</v>
       </c>
       <c r="I8" s="12">
         <f>H8/$D$8</f>
@@ -1683,24 +1708,28 @@
       </c>
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Vesta Residences</t>
+          <t>Radium Evara</t>
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>46220</v>
+        <v>46227</v>
       </c>
       <c r="D9" s="10" t="n">
-        <v>1001</v>
+        <v>797</v>
       </c>
       <c r="E9" s="7" t="inlineStr">
         <is>
-          <t>19840-2</t>
-        </is>
-      </c>
-      <c r="F9" s="8" t="inlineStr"/>
+          <t>31310-1</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr">
+        <is>
+          <t>RASA WANGI DEVELOPMENT SDN. BHD.</t>
+        </is>
+      </c>
       <c r="G9" s="11" t="n"/>
       <c r="H9" s="11" t="n">
-        <v>931</v>
+        <v>0</v>
       </c>
       <c r="I9" s="12">
         <f>H9/$D$9</f>
@@ -1717,6 +1746,269 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="26" customWidth="1" min="6" max="6"/>
+    <col width="9" customWidth="1" min="7" max="7"/>
+    <col width="9" customWidth="1" min="8" max="8"/>
+    <col width="9" customWidth="1" min="9" max="9"/>
+    <col width="46" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>New tracker: the single column below is today's reading standing in for a weekly record, so it has no NEW SALES figure yet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Report as at 01/09/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="3" t="inlineStr">
+        <is>
+          <t>WEEKLY TEDUH SALES REPORT (SKYWORLD)</t>
+        </is>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>46262</v>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>NO</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>PROJECT</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>APDL 
+DATE</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>TOTAL 
+UNIT</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="inlineStr">
+        <is>
+          <t>PROJECT 
+CODE</t>
+        </is>
+      </c>
+      <c r="F4" s="5" t="inlineStr">
+        <is>
+          <t>DEVELOPER</t>
+        </is>
+      </c>
+      <c r="G4" s="6" t="inlineStr">
+        <is>
+          <t>NEW SALES</t>
+        </is>
+      </c>
+      <c r="H4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL SOLD</t>
+        </is>
+      </c>
+      <c r="I4" s="6" t="inlineStr">
+        <is>
+          <t>TOTAL %</t>
+        </is>
+      </c>
+      <c r="J4" s="5" t="inlineStr">
+        <is>
+          <t>NOTES</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>SkyAwani PRIMA Residences</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>45860</v>
+      </c>
+      <c r="D5" s="10" t="n">
+        <v>492</v>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>31051-1</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr"/>
+      <c r="G5" s="11" t="n"/>
+      <c r="H5" s="11" t="n">
+        <v>457</v>
+      </c>
+      <c r="I5" s="12">
+        <f>H5/$D$5</f>
+        <v/>
+      </c>
+      <c r="J5" s="8" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="7" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Curvo Residences</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>44937</v>
+      </c>
+      <c r="D6" s="10" t="n">
+        <v>830</v>
+      </c>
+      <c r="E6" s="7" t="inlineStr">
+        <is>
+          <t>30176-1</t>
+        </is>
+      </c>
+      <c r="F6" s="8" t="inlineStr"/>
+      <c r="G6" s="11" t="n"/>
+      <c r="H6" s="11" t="n">
+        <v>656</v>
+      </c>
+      <c r="I6" s="12">
+        <f>H6/$D$6</f>
+        <v/>
+      </c>
+      <c r="J6" s="8" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="7" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>SkyAman 1 Residences</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>45819</v>
+      </c>
+      <c r="D7" s="10" t="n">
+        <v>510</v>
+      </c>
+      <c r="E7" s="7" t="inlineStr">
+        <is>
+          <t>30976-1</t>
+        </is>
+      </c>
+      <c r="F7" s="8" t="inlineStr"/>
+      <c r="G7" s="11" t="n"/>
+      <c r="H7" s="11" t="n">
+        <v>240</v>
+      </c>
+      <c r="I7" s="12">
+        <f>H7/$D$7</f>
+        <v/>
+      </c>
+      <c r="J7" s="8" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>SkyWorld Pearlmont</t>
+        </is>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>45855</v>
+      </c>
+      <c r="D8" s="10" t="n">
+        <v>3982</v>
+      </c>
+      <c r="E8" s="7" t="inlineStr">
+        <is>
+          <t>31075-1,31075-2</t>
+        </is>
+      </c>
+      <c r="F8" s="8" t="inlineStr"/>
+      <c r="G8" s="11" t="n"/>
+      <c r="H8" s="11" t="n">
+        <v>1345</v>
+      </c>
+      <c r="I8" s="12">
+        <f>H8/$D$8</f>
+        <v/>
+      </c>
+      <c r="J8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="7" t="n">
+        <v>5</v>
+      </c>
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Vesta Residences</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>45124</v>
+      </c>
+      <c r="D9" s="10" t="n">
+        <v>1001</v>
+      </c>
+      <c r="E9" s="7" t="inlineStr">
+        <is>
+          <t>19840-2</t>
+        </is>
+      </c>
+      <c r="F9" s="8" t="inlineStr"/>
+      <c r="G9" s="11" t="n"/>
+      <c r="H9" s="11" t="n">
+        <v>931</v>
+      </c>
+      <c r="I9" s="12">
+        <f>H9/$D$9</f>
+        <v/>
+      </c>
+      <c r="J9" s="8" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G3:I3"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2044,7 +2336,7 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>46165</v>
+        <v>45069</v>
       </c>
       <c r="D13" s="10" t="n">
         <v>535</v>
@@ -2073,7 +2365,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2222,7 +2514,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>46035</v>
+        <v>44939</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>1838</v>
@@ -2312,7 +2604,7 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>45565</v>
+        <v>43722</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>1296</v>
@@ -2486,7 +2778,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>45744</v>
+        <v>45161</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>770</v>
@@ -2681,7 +2973,7 @@
         </is>
       </c>
       <c r="C12" s="9" t="n">
-        <v>45638</v>
+        <v>44177</v>
       </c>
       <c r="D12" s="10" t="n">
         <v>226</v>
@@ -3128,7 +3420,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>46194</v>
+        <v>45098</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>824</v>
@@ -3233,7 +3525,7 @@
         </is>
       </c>
       <c r="C11" s="9" t="n">
-        <v>46258</v>
+        <v>44797</v>
       </c>
       <c r="D11" s="10" t="n">
         <v>684</v>
@@ -3508,7 +3800,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>46042</v>
+        <v>44946</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>593</v>
@@ -3543,7 +3835,7 @@
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>46042</v>
+        <v>44946</v>
       </c>
       <c r="D7" s="10" t="n">
         <v>767</v>
@@ -3578,7 +3870,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>46129</v>
+        <v>45033</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>671</v>
@@ -3648,7 +3940,7 @@
         </is>
       </c>
       <c r="C10" s="9" t="n">
-        <v>46280</v>
+        <v>45184</v>
       </c>
       <c r="D10" s="10" t="n">
         <v>320</v>
@@ -3897,7 +4189,7 @@
         </is>
       </c>
       <c r="C17" s="9" t="n">
-        <v>46108</v>
+        <v>44282</v>
       </c>
       <c r="D17" s="10" t="n">
         <v>679</v>
@@ -4142,7 +4434,7 @@
         </is>
       </c>
       <c r="C24" s="9" t="n">
-        <v>45936</v>
+        <v>44840</v>
       </c>
       <c r="D24" s="10" t="n">
         <v>424</v>
@@ -4316,7 +4608,7 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>44060</v>
+        <v>42552</v>
       </c>
       <c r="D6" s="10" t="n">
         <v>478</v>
@@ -4604,7 +4896,7 @@
         </is>
       </c>
       <c r="C14" s="9" t="n">
-        <v>45574</v>
+        <v>45146</v>
       </c>
       <c r="D14" s="10" t="n">
         <v>2080</v>
@@ -4639,7 +4931,7 @@
         </is>
       </c>
       <c r="C15" s="9" t="n">
-        <v>45906</v>
+        <v>44810</v>
       </c>
       <c r="D15" s="10" t="n">
         <v>396</v>
@@ -4747,7 +5039,7 @@
         <v>45523</v>
       </c>
       <c r="D18" s="10" t="n">
-        <v>223</v>
+        <v>754</v>
       </c>
       <c r="E18" s="7" t="inlineStr">
         <is>
@@ -5599,7 +5891,7 @@
         </is>
       </c>
       <c r="C9" s="9" t="n">
-        <v>46078</v>
+        <v>44617</v>
       </c>
       <c r="D9" s="10" t="n">
         <v>1332</v>
@@ -5738,7 +6030,7 @@
         </is>
       </c>
       <c r="C5" s="9" t="n">
-        <v>46199</v>
+        <v>45103</v>
       </c>
       <c r="D5" s="10" t="n">
         <v>604</v>
@@ -5847,7 +6139,7 @@
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>46194</v>
+        <v>44733</v>
       </c>
       <c r="D8" s="10" t="n">
         <v>1236</v>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -527,7 +527,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 01/09/2026</t>
+          <t>Report as at 02/09/2026</t>
         </is>
       </c>
     </row>
@@ -759,7 +759,7 @@
       </c>
       <c r="G9" s="11" t="n"/>
       <c r="H9" s="11" t="n">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="I9" s="12">
         <f>H9/$D$9</f>
@@ -1097,7 +1097,7 @@
       <c r="F19" s="8" t="inlineStr"/>
       <c r="G19" s="11" t="n"/>
       <c r="H19" s="11" t="n">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="I19" s="12">
         <f>H19/$D$19</f>
@@ -1175,7 +1175,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 01/09/2026</t>
+          <t>Report as at 02/09/2026</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="G5" s="11" t="n"/>
       <c r="H5" s="11" t="n">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="I5" s="12">
         <f>H5/$D$5</f>
@@ -1403,7 +1403,7 @@
       <c r="F9" s="8" t="inlineStr"/>
       <c r="G9" s="11" t="n"/>
       <c r="H9" s="11" t="n">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="I9" s="12">
         <f>H9/$D$9</f>
@@ -1485,7 +1485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 01/09/2026</t>
+          <t>Report as at 02/09/2026</t>
         </is>
       </c>
     </row>
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G5" s="11" t="n"/>
       <c r="H5" s="11" t="n">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="I5" s="12">
         <f>H5/$D$5</f>
@@ -1620,7 +1620,7 @@
       </c>
       <c r="G6" s="11" t="n"/>
       <c r="H6" s="11" t="n">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="I6" s="12">
         <f>H6/$D$6</f>
@@ -1655,7 +1655,7 @@
       </c>
       <c r="G7" s="11" t="n"/>
       <c r="H7" s="11" t="n">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="I7" s="12">
         <f>H7/$D$7</f>
@@ -1776,7 +1776,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 01/09/2026</t>
+          <t>Report as at 02/09/2026</t>
         </is>
       </c>
     </row>
@@ -1961,7 +1961,7 @@
       <c r="F8" s="8" t="inlineStr"/>
       <c r="G8" s="11" t="n"/>
       <c r="H8" s="11" t="n">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="I8" s="12">
         <f>H8/$D$8</f>
@@ -2039,7 +2039,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 01/09/2026</t>
+          <t>Report as at 02/09/2026</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2349,7 @@
       <c r="F13" s="8" t="inlineStr"/>
       <c r="G13" s="11" t="n"/>
       <c r="H13" s="11" t="n">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="I13" s="12">
         <f>H13/$D$13</f>
@@ -2396,7 +2396,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 01/09/2026</t>
+          <t>Report as at 02/09/2026</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 01/09/2026</t>
+          <t>Report as at 02/09/2026</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 01/09/2026</t>
+          <t>Report as at 02/09/2026</t>
         </is>
       </c>
     </row>
@@ -3129,7 +3129,7 @@
       </c>
       <c r="G5" s="11" t="n"/>
       <c r="H5" s="11" t="n">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="I5" s="12">
         <f>H5/$D$5</f>
@@ -3232,7 +3232,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 01/09/2026</t>
+          <t>Report as at 02/09/2026</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="G10" s="11" t="n"/>
       <c r="H10" s="11" t="n">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="I10" s="12">
         <f>H10/$D$10</f>
@@ -3686,7 +3686,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 01/09/2026</t>
+          <t>Report as at 02/09/2026</t>
         </is>
       </c>
     </row>
@@ -4062,7 +4062,7 @@
       </c>
       <c r="G13" s="11" t="n"/>
       <c r="H13" s="11" t="n">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="I13" s="12">
         <f>H13/$D$13</f>
@@ -4132,7 +4132,7 @@
       </c>
       <c r="G15" s="11" t="n"/>
       <c r="H15" s="11" t="n">
-        <v>167</v>
+        <v>174</v>
       </c>
       <c r="I15" s="12">
         <f>H15/$D$15</f>
@@ -4346,7 +4346,7 @@
       </c>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="I21" s="12">
         <f>H21/$D$21</f>
@@ -4412,7 +4412,7 @@
       <c r="F23" s="8" t="inlineStr"/>
       <c r="G23" s="11" t="n"/>
       <c r="H23" s="11" t="n">
-        <v>1498</v>
+        <v>1500</v>
       </c>
       <c r="I23" s="12">
         <f>H23/$D$23</f>
@@ -4494,7 +4494,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 01/09/2026</t>
+          <t>Report as at 02/09/2026</t>
         </is>
       </c>
     </row>
@@ -4695,7 +4695,7 @@
       </c>
       <c r="G8" s="11" t="n"/>
       <c r="H8" s="11" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I8" s="12">
         <f>H8/$D$8</f>
@@ -4765,7 +4765,7 @@
       </c>
       <c r="G10" s="11" t="n"/>
       <c r="H10" s="11" t="n">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="I10" s="12">
         <f>H10/$D$10</f>
@@ -4804,7 +4804,7 @@
       </c>
       <c r="G11" s="11" t="n"/>
       <c r="H11" s="11" t="n">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="I11" s="12">
         <f>H11/$D$11</f>
@@ -4878,7 +4878,7 @@
       </c>
       <c r="G13" s="11" t="n"/>
       <c r="H13" s="11" t="n">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="I13" s="12">
         <f>H13/$D$13</f>
@@ -5154,7 +5154,7 @@
       <c r="F21" s="8" t="inlineStr"/>
       <c r="G21" s="11" t="n"/>
       <c r="H21" s="11" t="n">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="I21" s="12">
         <f>H21/$D$21</f>
@@ -5189,7 +5189,7 @@
       <c r="F22" s="8" t="inlineStr"/>
       <c r="G22" s="11" t="n"/>
       <c r="H22" s="11" t="n">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="I22" s="12">
         <f>H22/$D$22</f>
@@ -5236,7 +5236,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 01/09/2026</t>
+          <t>Report as at 02/09/2026</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="G10" s="11" t="n"/>
       <c r="H10" s="11" t="n">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="I10" s="12">
         <f>H10/$D$10</f>
@@ -5672,7 +5672,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 01/09/2026</t>
+          <t>Report as at 02/09/2026</t>
         </is>
       </c>
     </row>
@@ -5904,7 +5904,7 @@
       <c r="F9" s="8" t="inlineStr"/>
       <c r="G9" s="11" t="n"/>
       <c r="H9" s="11" t="n">
-        <v>978</v>
+        <v>980</v>
       </c>
       <c r="I9" s="12">
         <f>H9/$D$9</f>
@@ -5951,7 +5951,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 01/09/2026</t>
+          <t>Report as at 02/09/2026</t>
         </is>
       </c>
     </row>
@@ -6082,7 +6082,7 @@
       </c>
       <c r="G6" s="11" t="n"/>
       <c r="H6" s="11" t="n">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="I6" s="12">
         <f>H6/$D$6</f>
@@ -6117,7 +6117,7 @@
       </c>
       <c r="G7" s="11" t="n"/>
       <c r="H7" s="11" t="n">
-        <v>1008</v>
+        <v>1010</v>
       </c>
       <c r="I7" s="12">
         <f>H7/$D$7</f>
@@ -6191,7 +6191,7 @@
       </c>
       <c r="G9" s="11" t="n"/>
       <c r="H9" s="11" t="n">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="I9" s="12">
         <f>H9/$D$9</f>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -4402,7 +4402,7 @@
         <v>45966</v>
       </c>
       <c r="D23" s="10" t="n">
-        <v>3692</v>
+        <v>4525</v>
       </c>
       <c r="E23" s="7" t="inlineStr">
         <is>
@@ -4608,14 +4608,14 @@
         </is>
       </c>
       <c r="C6" s="9" t="n">
-        <v>42552</v>
+        <v>41622</v>
       </c>
       <c r="D6" s="10" t="n">
-        <v>478</v>
+        <v>678</v>
       </c>
       <c r="E6" s="7" t="inlineStr">
         <is>
-          <t>12324-2</t>
+          <t>12324-1,12324-2</t>
         </is>
       </c>
       <c r="F6" s="8" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="G6" s="11" t="n"/>
       <c r="H6" s="11" t="n">
-        <v>205</v>
+        <v>377</v>
       </c>
       <c r="I6" s="12">
         <f>H6/$D$6</f>
@@ -4864,11 +4864,11 @@
         <v>45754</v>
       </c>
       <c r="D13" s="10" t="n">
-        <v>330</v>
+        <v>817</v>
       </c>
       <c r="E13" s="7" t="inlineStr">
         <is>
-          <t>30897-1</t>
+          <t>30897-1,30897-2,30897-3</t>
         </is>
       </c>
       <c r="F13" s="8" t="inlineStr">
@@ -4878,7 +4878,7 @@
       </c>
       <c r="G13" s="11" t="n"/>
       <c r="H13" s="11" t="n">
-        <v>316</v>
+        <v>644</v>
       </c>
       <c r="I13" s="12">
         <f>H13/$D$13</f>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -527,7 +527,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 02/09/2026</t>
+          <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
@@ -1175,7 +1175,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 02/09/2026</t>
+          <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 02/09/2026</t>
+          <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 02/09/2026</t>
+          <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
@@ -2039,7 +2039,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 02/09/2026</t>
+          <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 02/09/2026</t>
+          <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
@@ -2664,7 +2664,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 02/09/2026</t>
+          <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
@@ -3033,7 +3033,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 02/09/2026</t>
+          <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
@@ -3232,7 +3232,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 02/09/2026</t>
+          <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
@@ -3686,7 +3686,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 02/09/2026</t>
+          <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
@@ -4494,7 +4494,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 02/09/2026</t>
+          <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
@@ -5236,7 +5236,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 02/09/2026</t>
+          <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 02/09/2026</t>
+          <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
@@ -5951,7 +5951,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Report as at 02/09/2026</t>
+          <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -34,7 +34,7 @@
     <numFmt numFmtId="165" formatCode="DD/MM/YYYY"/>
     <numFmt numFmtId="166" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -52,12 +52,6 @@
       <name val="Arial"/>
       <b val="1"/>
       <sz val="12"/>
-    </font>
-    <font>
-      <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="9"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -105,36 +99,35 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="3" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="166" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -502,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J20"/>
+  <dimension ref="A2:J20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -517,624 +510,637 @@
     <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>New tracker: the single column below is today's reading standing in for a weekly record, so it has no NEW SALES figure yet.</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>WEEKLY TEDUH SALES REPORT (ARMANI)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>46262</v>
+      <c r="G3" s="3" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>PROJECT</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>APDL 
 DATE</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>TOTAL 
 UNIT</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>PROJECT 
 CODE</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>DEVELOPER</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Alderwood Residence</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>46028</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>186</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>31112-1</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>GOLDEN ALDERWOOD PROPERTIES SDN. BHD.</t>
         </is>
       </c>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n">
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n">
         <v>58</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Armani Avani</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="8" t="n">
         <v>46086</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>328</v>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>30135-3</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>ARMANI DEVELOPMENT SDN. BHD.</t>
         </is>
       </c>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n">
-        <v>69</v>
-      </c>
-      <c r="I6" s="12">
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n">
+        <v>72</v>
+      </c>
+      <c r="I6" s="11">
         <f>H6/$D$6</f>
         <v/>
       </c>
-      <c r="J6" s="8" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Armani Business Park</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8" t="n">
         <v>45632</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="9" t="n">
         <v>44</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>30705-2</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>USAHA MULIA SDN. BHD.</t>
         </is>
       </c>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n">
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n">
         <v>2</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="11">
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Armani Cameron Residence</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="8" t="n">
         <v>45790</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>232</v>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>30273-1,30273-2</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n">
-        <v>111</v>
-      </c>
-      <c r="I8" s="12">
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n">
+        <v>112</v>
+      </c>
+      <c r="I8" s="11">
         <f>H8/$D$8</f>
         <v/>
       </c>
-      <c r="J8" s="8" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Armani Hallson KLCC</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>45820</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="9" t="n">
         <v>2215</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>30256-2</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>ARMANI HALLSON KLCC SDN. BHD.</t>
         </is>
       </c>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n">
-        <v>999</v>
-      </c>
-      <c r="I9" s="12">
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n">
+        <v>1006</v>
+      </c>
+      <c r="I9" s="11">
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 400 units, Block B: 361 units, Block C: 245 units</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Armani Residence Kepong</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="8" t="n">
         <v>45436</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="9" t="n">
         <v>306</v>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>6820-8</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>MAGNA PARK SDN. BHD.</t>
         </is>
       </c>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n">
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n">
         <v>277</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="11">
         <f>H10/$D$10</f>
         <v/>
       </c>
-      <c r="J10" s="8" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Armani Residence Setia Alam</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="8" t="n">
         <v>45561</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="9" t="n">
         <v>648</v>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>30727-1</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n">
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n">
         <v>573</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="11">
         <f>H11/$D$11</f>
         <v/>
       </c>
-      <c r="J11" s="8" t="inlineStr"/>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 92 units, Block B: 481 units</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Armani Residence Setia Alam 2</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="8" t="n">
         <v>46162</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="9" t="n">
         <v>998</v>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>30727-2</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n">
-        <v>281</v>
-      </c>
-      <c r="I12" s="12">
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n">
+        <v>284</v>
+      </c>
+      <c r="I12" s="11">
         <f>H12/$D$12</f>
         <v/>
       </c>
-      <c r="J12" s="8" t="inlineStr"/>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 62 units, Block B: 222 units</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Armani Residence Shah Alam</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="8" t="n">
         <v>45303</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="9" t="n">
         <v>338</v>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>30339-1</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>ARMANI ALLIANCE SDN. BHD.</t>
         </is>
       </c>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n">
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n">
         <v>331</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="11">
         <f>H13/$D$13</f>
         <v/>
       </c>
-      <c r="J13" s="8" t="inlineStr"/>
+      <c r="J13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Armani Signature Residence</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="8" t="n">
         <v>45252</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="9" t="n">
         <v>315</v>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>13975-5</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>GOLDEN ARMANI SDN. BHD.</t>
         </is>
       </c>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="n">
-        <v>263</v>
-      </c>
-      <c r="I14" s="12">
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n">
+        <v>266</v>
+      </c>
+      <c r="I14" s="11">
         <f>H14/$D$14</f>
         <v/>
       </c>
-      <c r="J14" s="8" t="inlineStr"/>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block 1: 85 units, Block 2: 82 units, Block 3: 99 units</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>Lofthill Residence</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="8" t="n">
         <v>45506</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="9" t="n">
         <v>653</v>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>30641-1</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>LOFTHILL DEVELOPMENT SDN. BHD.</t>
         </is>
       </c>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n">
+      <c r="G15" s="10" t="n"/>
+      <c r="H15" s="10" t="n">
         <v>647</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="11">
         <f>H15/$D$15</f>
         <v/>
       </c>
-      <c r="J15" s="8" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>Residensi Armani Kg Baru 1</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="8" t="n">
         <v>45632</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="9" t="n">
         <v>387</v>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>13975-6</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>GOLDEN ARMANI SDN. BHD.</t>
         </is>
       </c>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="11" t="n">
+      <c r="G16" s="10" t="n"/>
+      <c r="H16" s="10" t="n">
         <v>384</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="11">
         <f>H16/$D$16</f>
         <v/>
       </c>
-      <c r="J16" s="8" t="inlineStr"/>
+      <c r="J16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>Residensi Armani Putra</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="8" t="n">
         <v>46183</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="9" t="n">
         <v>984</v>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>30799-1</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>GOLDEN CHAIN DEVELOPMENT SDN. BHD.</t>
         </is>
       </c>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n">
-        <v>28</v>
-      </c>
-      <c r="I17" s="12">
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="10" t="n">
+        <v>29</v>
+      </c>
+      <c r="I17" s="11">
         <f>H17/$D$17</f>
         <v/>
       </c>
-      <c r="J17" s="8" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 13 units, Block B: 16 units</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>Taman Bukit Tualang 2</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="8" t="n">
         <v>46238</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="9" t="n">
         <v>30</v>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>30393-1</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>GOLDEN ARMANI DEVELOPMENT SDN. BHD.</t>
         </is>
       </c>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="n">
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="11">
         <f>H18/$D$18</f>
         <v/>
       </c>
-      <c r="J18" s="8" t="inlineStr"/>
+      <c r="J18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>Armani Prestige</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="8" t="n">
         <v>45862</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="9" t="n">
         <v>280</v>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>30135-2</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr"/>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="n">
-        <v>95</v>
-      </c>
-      <c r="I19" s="12">
+      <c r="F19" s="7" t="inlineStr"/>
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n">
+        <v>96</v>
+      </c>
+      <c r="I19" s="11">
         <f>H19/$D$19</f>
         <v/>
       </c>
-      <c r="J19" s="8" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>Taman PMINT Tebing Tembah 2</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="8" t="n">
         <v>45167</v>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="9" t="n">
         <v>116</v>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>13970-3</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr"/>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="11" t="n">
+      <c r="F20" s="7" t="inlineStr"/>
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="10" t="n">
         <v>81</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="11">
         <f>H20/$D$20</f>
         <v/>
       </c>
-      <c r="J20" s="8" t="inlineStr"/>
+      <c r="J20" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1150,7 +1156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A2:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1165,286 +1171,291 @@
     <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>New tracker: the single column below is today's reading standing in for a weekly record, so it has no NEW SALES figure yet.</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>WEEKLY TEDUH SALES REPORT (PLATINUM VICTORY)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>46262</v>
+      <c r="G3" s="3" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>PROJECT</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>APDL 
 DATE</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>TOTAL 
 UNIT</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>PROJECT 
 CODE</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>DEVELOPER</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>MHP3 Residences</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>45270</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>1688</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>30581-1</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>MHP3 SDN. BHD.</t>
         </is>
       </c>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n">
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n">
         <v>1672</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 862 units, Block B: 810 units</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>PV22 Residences</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="8" t="n">
         <v>45334</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>2082</v>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>9832-11</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>PLATINUM VICTORY DEVELOPMENT SDN. BHD.</t>
         </is>
       </c>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n">
-        <v>1202</v>
-      </c>
-      <c r="I6" s="12">
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n">
+        <v>1206</v>
+      </c>
+      <c r="I6" s="11">
         <f>H6/$D$6</f>
         <v/>
       </c>
-      <c r="J6" s="8" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 469 units, Block B: 737 units</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Platinum Melati Residences (Vista Melati)</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8" t="n">
         <v>45827</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="9" t="n">
         <v>794</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>31008-1</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>SMART ADVANCE RESOURCES SDN. BHD.</t>
         </is>
       </c>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n">
-        <v>522</v>
-      </c>
-      <c r="I7" s="12">
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n">
+        <v>524</v>
+      </c>
+      <c r="I7" s="11">
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 129 units, Block B: 163 units, Block C: 232 units</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>PSV1 Residences</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="8" t="n">
         <v>44869</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>500</v>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>20253-2</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n">
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n">
         <v>467</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="11">
         <f>H8/$D$8</f>
         <v/>
       </c>
-      <c r="J8" s="8" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>PSV2 Residences</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>45610</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="9" t="n">
         <v>1500</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>20253-3</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n">
-        <v>1162</v>
-      </c>
-      <c r="I9" s="12">
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n">
+        <v>1163</v>
+      </c>
+      <c r="I9" s="11">
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block W: 598 units, Block X: 559 units</t>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block W: 600 units, Block X: 563 units</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>The Maison 23</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="8" t="n">
         <v>45714</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="9" t="n">
         <v>23</v>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>30937-1</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n">
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n">
         <v>18</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="11">
         <f>H10/$D$10</f>
         <v/>
       </c>
-      <c r="J10" s="8" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1460,7 +1471,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A2:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1475,267 +1486,264 @@
     <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>New tracker: the single column below is today's reading standing in for a weekly record, so it has no NEW SALES figure yet.</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>WEEKLY TEDUH SALES REPORT (RADIUM)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>46262</v>
+      <c r="G3" s="3" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>PROJECT</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>APDL 
 DATE</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>TOTAL 
 UNIT</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>PROJECT 
 CODE</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>DEVELOPER</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Radium Adesa @ KL (incl. Adesa Luxe Residences)</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>45100</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>1218</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>30363-2</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>FITRAH RESOURCES SDN. BHD.</t>
         </is>
       </c>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n">
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n">
         <v>1128</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 181 units, Block B: 582 units, Block C: 362 units</t>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 182 units, Block B: 583 units, Block C: 362 units</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Vista Adesa @ KL</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="8" t="n">
         <v>45054</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>1218</v>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>30363-1</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>FITRAH RESOURCES SDN. BHD.</t>
         </is>
       </c>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n">
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n">
         <v>1124</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="11">
         <f>H6/$D$6</f>
         <v/>
       </c>
-      <c r="J6" s="8" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block D: 602 units, Block E: 522 units</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Radium Arena @ Old Klang Road</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8" t="n">
         <v>45590</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="9" t="n">
         <v>988</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>30821-1</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>RADIUM GLOBAL SDN. BHD.</t>
         </is>
       </c>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n">
-        <v>519</v>
-      </c>
-      <c r="I7" s="12">
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n">
+        <v>521</v>
+      </c>
+      <c r="I7" s="11">
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 259 units, Block B: 260 units</t>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 261 units, Block B: 260 units</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Chancery Ampang @ KL</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="8" t="n">
         <v>44880</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>944</v>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>30121-1</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>IDAMAN SEJIWA (AMPANG) SDN. BHD.</t>
         </is>
       </c>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n">
-        <v>379</v>
-      </c>
-      <c r="I8" s="12">
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n">
+        <v>380</v>
+      </c>
+      <c r="I8" s="11">
         <f>H8/$D$8</f>
         <v/>
       </c>
-      <c r="J8" s="8" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Radium Evara</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>46227</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="9" t="n">
         <v>797</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>31310-1</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>RASA WANGI DEVELOPMENT SDN. BHD.</t>
         </is>
       </c>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n">
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="11">
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -1751,7 +1759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A2:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -1766,239 +1774,248 @@
     <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>New tracker: the single column below is today's reading standing in for a weekly record, so it has no NEW SALES figure yet.</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>WEEKLY TEDUH SALES REPORT (SKYWORLD)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>46262</v>
+      <c r="G3" s="3" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>PROJECT</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>APDL 
 DATE</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>TOTAL 
 UNIT</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>PROJECT 
 CODE</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>DEVELOPER</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>SkyAwani PRIMA Residences</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>45860</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>492</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>31051-1</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr"/>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n">
+      <c r="F5" s="7" t="inlineStr"/>
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n">
         <v>457</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Curvo Residences</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="8" t="n">
         <v>44937</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>830</v>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>30176-1</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n">
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n">
         <v>656</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="11">
         <f>H6/$D$6</f>
         <v/>
       </c>
-      <c r="J6" s="8" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 429 units, Block B: 227 units</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>SkyAman 1 Residences</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8" t="n">
         <v>45819</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="9" t="n">
         <v>510</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>30976-1</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n">
-        <v>240</v>
-      </c>
-      <c r="I7" s="12">
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n">
+        <v>241</v>
+      </c>
+      <c r="I7" s="11">
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 241 units</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>SkyWorld Pearlmont</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="8" t="n">
         <v>45855</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>3982</v>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>31075-1,31075-2</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n">
-        <v>1347</v>
-      </c>
-      <c r="I8" s="12">
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n">
+        <v>1351</v>
+      </c>
+      <c r="I8" s="11">
         <f>H8/$D$8</f>
         <v/>
       </c>
-      <c r="J8" s="8" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block 1B: 567 units, Block 1C: 530 units, Block 1D: 254 units</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Vesta Residences</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>45124</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="9" t="n">
         <v>1001</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>19840-2</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n">
-        <v>931</v>
-      </c>
-      <c r="I9" s="12">
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n">
+        <v>932</v>
+      </c>
+      <c r="I9" s="11">
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 467 units, Block B: 465 units</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2014,7 +2031,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A2:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2029,333 +2046,334 @@
     <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>New tracker: the single column below is today's reading standing in for a weekly record, so it has no NEW SALES figure yet.</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>WEEKLY TEDUH SALES REPORT (TRINITY GROUP)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>46262</v>
+      <c r="G3" s="3" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>PROJECT</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>APDL 
 DATE</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>TOTAL 
 UNIT</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>PROJECT 
 CODE</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>DEVELOPER</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Trinity Nordic/Zia</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>45813</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>714</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>30857-1</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>OLYMPIC BUILDERS SDN. BHD.</t>
         </is>
       </c>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n">
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n">
         <v>36</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 1 units, Block B: 35 units</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Trinity Sensoria</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="8" t="n">
         <v>45575</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>737</v>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>20140-2</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>TRINITY WELLNESSA &amp; ENLIVEA DEVELOPMENT SDN. BHD.</t>
         </is>
       </c>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n">
-        <v>347</v>
-      </c>
-      <c r="I6" s="12">
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n">
+        <v>348</v>
+      </c>
+      <c r="I6" s="11">
         <f>H6/$D$6</f>
         <v/>
       </c>
-      <c r="J6" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A1: 45 units, Block A2: 202 units, Block B: 100 units</t>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A1: 45 units, Block A2: 203 units, Block B: 100 units</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Lot 850 @ Ampang</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="10" t="n">
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="12" t="n"/>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Not launched yet.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>MA Land</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="10" t="n">
+      <c r="C8" s="8" t="n"/>
+      <c r="D8" s="9" t="n">
         <v>2964</v>
       </c>
-      <c r="E8" s="7" t="inlineStr"/>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n"/>
-      <c r="I8" s="12" t="n"/>
-      <c r="J8" s="8" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr"/>
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n"/>
+      <c r="I8" s="11" t="n"/>
+      <c r="J8" s="7" t="inlineStr">
         <is>
           <t>Not launched yet.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Permas Jaya – Phase 1</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n"/>
-      <c r="D9" s="10" t="n">
+      <c r="C9" s="8" t="n"/>
+      <c r="D9" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" s="7" t="inlineStr"/>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n"/>
-      <c r="I9" s="12" t="n"/>
-      <c r="J9" s="8" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr"/>
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n"/>
+      <c r="I9" s="11" t="n"/>
+      <c r="J9" s="7" t="inlineStr">
         <is>
           <t>Not launched yet.</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Permas Jaya – Phase 2</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="10" t="n">
+      <c r="C10" s="8" t="n"/>
+      <c r="D10" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E10" s="7" t="inlineStr"/>
-      <c r="F10" s="8" t="inlineStr"/>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n"/>
-      <c r="I10" s="12" t="n"/>
-      <c r="J10" s="8" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr"/>
+      <c r="F10" s="7" t="inlineStr"/>
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n"/>
+      <c r="I10" s="11" t="n"/>
+      <c r="J10" s="7" t="inlineStr">
         <is>
           <t>Not launched yet.</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Permas Jaya – Phase 3</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="10" t="n">
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="12" t="n"/>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Not launched yet.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Trinity Activerse</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="10" t="n">
+      <c r="C12" s="8" t="n"/>
+      <c r="D12" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="7" t="inlineStr"/>
-      <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n"/>
-      <c r="I12" s="12" t="n"/>
-      <c r="J12" s="8" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr"/>
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n"/>
+      <c r="I12" s="11" t="n"/>
+      <c r="J12" s="7" t="inlineStr">
         <is>
           <t>Not launched yet.</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Trinity Rainfora</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="8" t="n">
         <v>45069</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="9" t="n">
         <v>535</v>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>10826-4</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n">
-        <v>332</v>
-      </c>
-      <c r="I13" s="12">
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n">
+        <v>333</v>
+      </c>
+      <c r="I13" s="11">
         <f>H13/$D$13</f>
         <v/>
       </c>
-      <c r="J13" s="8" t="inlineStr"/>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 196 units, Block B: 137 units</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2371,7 +2389,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A2:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2386,244 +2404,245 @@
     <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>New tracker: the single column below is today's reading standing in for a weekly record, so it has no NEW SALES figure yet.</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>WEEKLY TEDUH SALES REPORT (TS LAW)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>46262</v>
+      <c r="G3" s="3" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>PROJECT</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>APDL 
 DATE</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>TOTAL 
 UNIT</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>PROJECT 
 CODE</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>DEVELOPER</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Skyline (Eastside) @ OneSentosa</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>45889</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>1623</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>31031-1</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>PLAZA SENTOSA PROPERTIES SDN. BHD.</t>
         </is>
       </c>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n">
-        <v>1397</v>
-      </c>
-      <c r="I5" s="12">
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n">
+        <v>1400</v>
+      </c>
+      <c r="I5" s="11">
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 728 units, Block B: 668 units</t>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 728 units, Block B: 672 units</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Skyline Kuchai</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="8" t="n">
         <v>44939</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>1838</v>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>30331-1,30331-2</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>L &amp; T REALTY SDN. BHD.</t>
         </is>
       </c>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n">
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n">
         <v>1825</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="11">
         <f>H6/$D$6</f>
         <v/>
       </c>
-      <c r="J6" s="8" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 937 units, Block B: 888 units</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>KL Exchange (KLX)</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="10" t="n">
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="12" t="n"/>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Not launched yet.</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Residence Hill</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="8" t="n">
         <v>44394</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>42</v>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>9158-9</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr"/>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n">
+      <c r="F8" s="7" t="inlineStr"/>
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n">
         <v>42</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="11">
         <f>H8/$D$8</f>
         <v/>
       </c>
-      <c r="J8" s="8" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Skyline Embassy</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>43722</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="9" t="n">
         <v>1296</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>19760-1,19760-2</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n">
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n">
         <v>1286</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="11">
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 431 units, Block B: 424 units, Block C: 431 units</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -2639,7 +2658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A2:J12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2654,345 +2673,362 @@
     <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>New tracker: the single column below is today's reading standing in for a weekly record, so it has no NEW SALES figure yet.</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>WEEKLY TEDUH SALES REPORT (AVALAND)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>46262</v>
+      <c r="G3" s="3" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>PROJECT</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>APDL 
 DATE</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>TOTAL 
 UNIT</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>PROJECT 
 CODE</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>DEVELOPER</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Aetas Seputeh</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>45450</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>126</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>30624-1</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>ARDENT RESIDENCE SDN. BHD.</t>
         </is>
       </c>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n">
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n">
         <v>125</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 70 units, Block B: 55 units</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Alora Residences @ Avenue25</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="8" t="n">
         <v>45161</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>770</v>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>30162-1,30162-2</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr"/>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n">
-        <v>424</v>
-      </c>
-      <c r="I6" s="12">
+      <c r="F6" s="7" t="inlineStr"/>
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n">
+        <v>425</v>
+      </c>
+      <c r="I6" s="11">
         <f>H6/$D$6</f>
         <v/>
       </c>
-      <c r="J6" s="8" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 317 units, Block B: 108 units</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Amika Residences</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8" t="n">
         <v>45366</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="9" t="n">
         <v>468</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>20185-3</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>NEXT DELTA SDN. BHD.</t>
         </is>
       </c>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n">
-        <v>456</v>
-      </c>
-      <c r="I7" s="12">
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n">
+        <v>457</v>
+      </c>
+      <c r="I7" s="11">
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 216 units, Block B: 241 units</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Anja Residences &amp; Signature Retail</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="8" t="n">
         <v>45463</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>900</v>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>9490-3,9490-4</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>USJ ONE AVENUE SDN. BHD.</t>
         </is>
       </c>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n">
-        <v>274</v>
-      </c>
-      <c r="I8" s="12">
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n">
+        <v>275</v>
+      </c>
+      <c r="I8" s="11">
         <f>H8/$D$8</f>
         <v/>
       </c>
-      <c r="J8" s="8" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 275 units</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Avalon</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>45845</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="9" t="n">
         <v>343</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>30240-3,30240-4</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>ECOLAKE RESIDENCE SDN. BHD.</t>
         </is>
       </c>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n">
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n">
         <v>180</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="11">
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Sanderling 2 Lakefront</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="8" t="n">
         <v>45559</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="9" t="n">
         <v>606</v>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>12047-4</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>LAKEFRONT RESIDENCE SDN. BHD.</t>
         </is>
       </c>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n">
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n">
         <v>232</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="11">
         <f>H10/$D$10</f>
         <v/>
       </c>
-      <c r="J10" s="8" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block T7: 97 units, Block T8: 135 units</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Accent Petaling Jaya</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="10" t="n">
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="9" t="n">
         <v>231</v>
       </c>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="12" t="n"/>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Not launched yet.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Aetas Taman Desa</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="8" t="n">
         <v>44177</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="9" t="n">
         <v>226</v>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>20017-1</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n">
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n">
         <v>221</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="11">
         <f>H12/$D$12</f>
         <v/>
       </c>
-      <c r="J12" s="8" t="inlineStr"/>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 144 units, Block B: 77 units</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3008,7 +3044,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A2:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3023,171 +3059,164 @@
     <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>New tracker: the single column below is today's reading standing in for a weekly record, so it has no NEW SALES figure yet.</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>WEEKLY TEDUH SALES REPORT (BINASTRA)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>46262</v>
+      <c r="G3" s="3" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>PROJECT</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>APDL 
 DATE</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>TOTAL 
 UNIT</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>PROJECT 
 CODE</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>DEVELOPER</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Binastra Cochrane</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>46205</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>830</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>31332-1</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>BINASTRA SYNERGY SDN. BHD.</t>
         </is>
       </c>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n">
-        <v>280</v>
-      </c>
-      <c r="I5" s="12">
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n">
+        <v>303</v>
+      </c>
+      <c r="I5" s="11">
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 169 units, Block B: 91 units</t>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 189 units, Block B: 114 units</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Binastra Cochrane 2</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n"/>
-      <c r="D6" s="10" t="n">
+      <c r="C6" s="8" t="n"/>
+      <c r="D6" s="9" t="n">
         <v>830</v>
       </c>
-      <c r="E6" s="7" t="inlineStr"/>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr"/>
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>BINASTRA SYNERGY SDN. BHD.</t>
         </is>
       </c>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n"/>
-      <c r="I6" s="12" t="n"/>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n"/>
+      <c r="I6" s="11" t="n"/>
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>Not launched yet.</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Binastra The Hill @ Kemensah</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n"/>
-      <c r="D7" s="10" t="n">
+      <c r="C7" s="8" t="n"/>
+      <c r="D7" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E7" s="7" t="inlineStr"/>
-      <c r="F7" s="8" t="inlineStr"/>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n"/>
-      <c r="I7" s="12" t="n"/>
-      <c r="J7" s="8" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr"/>
+      <c r="F7" s="7" t="inlineStr"/>
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="7" t="inlineStr">
         <is>
           <t>Not on TEDUH.</t>
         </is>
@@ -3207,7 +3236,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A2:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3222,430 +3251,443 @@
     <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>New tracker: the single column below is today's reading standing in for a weekly record, so it has no NEW SALES figure yet.</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>WEEKLY TEDUH SALES REPORT (CHIN HIN)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>46262</v>
+      <c r="G3" s="3" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>PROJECT</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>APDL 
 DATE</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>TOTAL 
 UNIT</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>PROJECT 
 CODE</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>DEVELOPER</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Amberwood Resort Residences</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>46028</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>824</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>13531-2</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>AFFLUENT CRAFTS SDN. BHD.</t>
         </is>
       </c>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n">
-        <v>726</v>
-      </c>
-      <c r="I5" s="12">
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n">
+        <v>727</v>
+      </c>
+      <c r="I5" s="11">
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 439 units, Block B: 286 units</t>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 440 units, Block B: 287 units</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Aricia Residences</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="8" t="n">
         <v>45682</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>787</v>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>30632-1</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>ARICIA SDN. BHD.</t>
         </is>
       </c>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n">
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n">
         <v>603</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="11">
         <f>H6/$D$6</f>
         <v/>
       </c>
-      <c r="J6" s="8" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 299 units, Block B: 304 units</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Avantro Residences</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8" t="n">
         <v>45258</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="9" t="n">
         <v>842</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>30190-1</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>BOON KOON COMMERCIAL SDN. BHD.</t>
         </is>
       </c>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n">
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n">
         <v>809</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="11">
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 335 units, Block B: 474 units</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Ayanna Resort Residences</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="8" t="n">
         <v>45098</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>824</v>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>30382-1,30382-2</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>BKSP AUTOWORLD SDN. BHD.</t>
         </is>
       </c>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n">
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n">
         <v>761</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="11">
         <f>H8/$D$8</f>
         <v/>
       </c>
-      <c r="J8" s="8" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 322 units, Block B: 439 units</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Crown Penang</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>45503</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="9" t="n">
         <v>588</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>30744-1</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>STELLAR PLATINUM SDN. BHD.</t>
         </is>
       </c>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n">
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n">
         <v>482</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="11">
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>DIVINE KLCC</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="8" t="n">
         <v>46194</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="9" t="n">
         <v>1033</v>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>31096-1</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>SINARAN URUSJUTA SDN. BHD.</t>
         </is>
       </c>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n">
-        <v>270</v>
-      </c>
-      <c r="I10" s="12">
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n">
+        <v>275</v>
+      </c>
+      <c r="I10" s="11">
         <f>H10/$D$10</f>
         <v/>
       </c>
-      <c r="J10" s="8" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Quaver Residence</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="8" t="n">
         <v>44797</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="9" t="n">
         <v>684</v>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>30064-1</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>QUAVER SDN. BHD.</t>
         </is>
       </c>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n">
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n">
         <v>678</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="11">
         <f>H11/$D$11</f>
         <v/>
       </c>
-      <c r="J11" s="8" t="inlineStr"/>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 313 units, Block B: 365 units</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Residensi Andalan</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="8" t="n">
         <v>45488</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="9" t="n">
         <v>823</v>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>30382-3</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>BKSP AUTOWORLD SDN. BHD.</t>
         </is>
       </c>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n">
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n">
         <v>822</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="11">
         <f>H12/$D$12</f>
         <v/>
       </c>
-      <c r="J12" s="8" t="inlineStr"/>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 822 units</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Botanica Hills</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="8" t="n">
         <v>45896</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="9" t="n">
         <v>231</v>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>30907-1,30907-2</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n">
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n">
         <v>221</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="11">
         <f>H13/$D$13</f>
         <v/>
       </c>
-      <c r="J13" s="8" t="inlineStr"/>
+      <c r="J13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Dawn KLCC</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="8" t="n">
         <v>45505</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="9" t="n">
         <v>492</v>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>30629-2</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr"/>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="n">
+      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n">
         <v>477</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="11">
         <f>H14/$D$14</f>
         <v/>
       </c>
-      <c r="J14" s="8" t="inlineStr"/>
+      <c r="J14" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -3661,7 +3703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J24"/>
+  <dimension ref="A2:J24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3676,784 +3718,809 @@
     <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>New tracker: the single column below is today's reading standing in for a weekly record, so it has no NEW SALES figure yet.</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>WEEKLY TEDUH SALES REPORT (EXSIM)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>46262</v>
+      <c r="G3" s="3" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>PROJECT</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>APDL 
 DATE</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>TOTAL 
 UNIT</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>PROJECT 
 CODE</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>DEVELOPER</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Branniganz Suites</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>45518</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>269</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>30784-1</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>LEMBARAN BERUNTUNG SDN. BHD.</t>
         </is>
       </c>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n">
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n">
         <v>268</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block B: 268 units</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>D'Clover Residences</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="8" t="n">
         <v>44946</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>593</v>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>20011-3</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>MIGHTYPROP  SDN. BHD.</t>
         </is>
       </c>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n">
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n">
         <v>593</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="11">
         <f>H6/$D$6</f>
         <v/>
       </c>
-      <c r="J6" s="8" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 593 units</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>D'Terra Residences</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8" t="n">
         <v>44946</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="9" t="n">
         <v>767</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>20011-2</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>MIGHTYPROP  SDN. BHD.</t>
         </is>
       </c>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n">
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n">
         <v>767</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="11">
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block B: 767 units</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>D'Tessera Residences</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="8" t="n">
         <v>45033</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>671</v>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>20011-4</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>MIGHTYPROP  SDN. BHD.</t>
         </is>
       </c>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n">
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n">
         <v>664</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="11">
         <f>H8/$D$8</f>
         <v/>
       </c>
-      <c r="J8" s="8" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block C: 664 units</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Hanaz Suites</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>45659</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="9" t="n">
         <v>98</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>13666-2</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>SUNRISE CHARM SDN. BHD.</t>
         </is>
       </c>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n">
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n">
         <v>98</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="11">
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Hugoz Suites</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="8" t="n">
         <v>45184</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="9" t="n">
         <v>320</v>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>30370-1</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>ARMADA ISTIMEWA SDN. BHD.</t>
         </is>
       </c>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n">
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n">
         <v>319</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="11">
         <f>H10/$D$10</f>
         <v/>
       </c>
-      <c r="J10" s="8" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>Kyliez Suites</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="8" t="n">
         <v>45511</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="9" t="n">
         <v>126</v>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>30789-1</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>EXSIM AVENUE SDN. BHD.</t>
         </is>
       </c>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n">
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n">
         <v>126</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="11">
         <f>H11/$D$11</f>
         <v/>
       </c>
-      <c r="J11" s="8" t="inlineStr"/>
+      <c r="J11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Noordinz Suites</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="8" t="n">
         <v>45251</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="9" t="n">
         <v>603</v>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>30571-1</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>EXSIM NOORDIN SDN. BHD.</t>
         </is>
       </c>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n">
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n">
         <v>602</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="11">
         <f>H12/$D$12</f>
         <v/>
       </c>
-      <c r="J12" s="8" t="inlineStr"/>
+      <c r="J12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Qubaz Suites</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="8" t="n">
         <v>45716</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="9" t="n">
         <v>759</v>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>30914-1</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>EXSIM KG TIONG (KT)  SDN. BHD.</t>
         </is>
       </c>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n">
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n">
         <v>625</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="11">
         <f>H13/$D$13</f>
         <v/>
       </c>
-      <c r="J13" s="8" t="inlineStr"/>
+      <c r="J13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Sea Crestz</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="8" t="n">
         <v>45736</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="9" t="n">
         <v>456</v>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>30830-1</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>KUANTAN WATERFRONT RESORT CITY SDN. BHD.</t>
         </is>
       </c>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="n">
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n">
         <v>317</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="11">
         <f>H14/$D$14</f>
         <v/>
       </c>
-      <c r="J14" s="8" t="inlineStr"/>
+      <c r="J14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>The Aldenz</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="8" t="n">
         <v>45839</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="9" t="n">
         <v>662</v>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>20011-5</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>MIGHTYPROP  SDN. BHD.</t>
         </is>
       </c>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n">
-        <v>174</v>
-      </c>
-      <c r="I15" s="12">
+      <c r="G15" s="10" t="n"/>
+      <c r="H15" s="10" t="n">
+        <v>181</v>
+      </c>
+      <c r="I15" s="11">
         <f>H15/$D$15</f>
         <v/>
       </c>
-      <c r="J15" s="8" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>The Asteriaz</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="8" t="n">
         <v>45856</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="9" t="n">
         <v>848</v>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>31007-1</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>EXSIM KEBUN TEH SDN. BHD.</t>
         </is>
       </c>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="11" t="n">
+      <c r="G16" s="10" t="n"/>
+      <c r="H16" s="10" t="n">
         <v>845</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="11">
         <f>H16/$D$16</f>
         <v/>
       </c>
-      <c r="J16" s="8" t="inlineStr">
+      <c r="J16" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>The Fiddlewoodz</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="8" t="n">
         <v>44282</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="9" t="n">
         <v>679</v>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>20084-1</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>IVORY INTERPOINT SDN. BHD.</t>
         </is>
       </c>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n">
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="10" t="n">
         <v>339</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="11">
         <f>H17/$D$17</f>
         <v/>
       </c>
-      <c r="J17" s="8" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 312 units, Block B: 27 units</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>The Kingswoodz</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="8" t="n">
         <v>45516</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="9" t="n">
         <v>1558</v>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>30741-1</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>EXSIM JALIL LINK   SDN. BHD.</t>
         </is>
       </c>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="n">
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="10" t="n">
         <v>1552</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="11">
         <f>H18/$D$18</f>
         <v/>
       </c>
-      <c r="J18" s="8" t="inlineStr"/>
+      <c r="J18" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 457 units, Block B: 505 units, Block C: 590 units</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>The Lighthauz</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="8" t="n">
         <v>45952</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="9" t="n">
         <v>671</v>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>31088-1</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>EXSIM WATERFRONT SDN. BHD.</t>
         </is>
       </c>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="n">
-        <v>550</v>
-      </c>
-      <c r="I19" s="12">
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n">
+        <v>553</v>
+      </c>
+      <c r="I19" s="11">
         <f>H19/$D$19</f>
         <v/>
       </c>
-      <c r="J19" s="8" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>The Queenswoodz</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="8" t="n">
         <v>46099</v>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="9" t="n">
         <v>1004</v>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>30741-2</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>EXSIM JALIL LINK   SDN. BHD.</t>
         </is>
       </c>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="11" t="n">
-        <v>435</v>
-      </c>
-      <c r="I20" s="12">
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="10" t="n">
+        <v>438</v>
+      </c>
+      <c r="I20" s="11">
         <f>H20/$D$20</f>
         <v/>
       </c>
-      <c r="J20" s="8" t="inlineStr"/>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 193 units, Block B: 245 units</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>The Vividz</t>
         </is>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C21" s="8" t="n">
         <v>45806</v>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="9" t="n">
         <v>1138</v>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>30357-2</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr">
+      <c r="F21" s="7" t="inlineStr">
         <is>
           <t>EXSIM BUKIT JALIL CITY SDN. BHD.</t>
         </is>
       </c>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n">
-        <v>657</v>
-      </c>
-      <c r="I21" s="12">
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n">
+        <v>658</v>
+      </c>
+      <c r="I21" s="11">
         <f>H21/$D$21</f>
         <v/>
       </c>
-      <c r="J21" s="8" t="inlineStr"/>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 358 units, Block B: 300 units</t>
+        </is>
+      </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>Veladaz Residences</t>
         </is>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="8" t="n">
         <v>45218</v>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D22" s="9" t="n">
         <v>508</v>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>30357-1</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr">
+      <c r="F22" s="7" t="inlineStr">
         <is>
           <t>EXSIM BUKIT JALIL CITY SDN. BHD.</t>
         </is>
       </c>
-      <c r="G22" s="11" t="n"/>
-      <c r="H22" s="11" t="n">
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="10" t="n">
         <v>507</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="11">
         <f>H22/$D$22</f>
         <v/>
       </c>
-      <c r="J22" s="8" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="7" t="n">
+      <c r="A23" s="6" t="n">
         <v>19</v>
       </c>
-      <c r="B23" s="8" t="inlineStr">
+      <c r="B23" s="7" t="inlineStr">
         <is>
           <t>Causewayz Square @ JBCC</t>
         </is>
       </c>
-      <c r="C23" s="9" t="n">
+      <c r="C23" s="8" t="n">
         <v>45966</v>
       </c>
-      <c r="D23" s="10" t="n">
+      <c r="D23" s="9" t="n">
         <v>4525</v>
       </c>
-      <c r="E23" s="7" t="inlineStr">
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>31100-1,31100-2,31100-3,31100-4</t>
         </is>
       </c>
-      <c r="F23" s="8" t="inlineStr"/>
-      <c r="G23" s="11" t="n"/>
-      <c r="H23" s="11" t="n">
-        <v>1500</v>
-      </c>
-      <c r="I23" s="12">
+      <c r="F23" s="7" t="inlineStr"/>
+      <c r="G23" s="10" t="n"/>
+      <c r="H23" s="10" t="n">
+        <v>1503</v>
+      </c>
+      <c r="I23" s="11">
         <f>H23/$D$23</f>
         <v/>
       </c>
-      <c r="J23" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 493 units, Block B: 531 units, Block D: 473 units</t>
+      <c r="J23" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 497 units, Block B: 531 units, Block D: 475 units</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="n">
+      <c r="A24" s="6" t="n">
         <v>20</v>
       </c>
-      <c r="B24" s="8" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>The Stallionz</t>
         </is>
       </c>
-      <c r="C24" s="9" t="n">
+      <c r="C24" s="8" t="n">
         <v>44840</v>
       </c>
-      <c r="D24" s="10" t="n">
+      <c r="D24" s="9" t="n">
         <v>424</v>
       </c>
-      <c r="E24" s="7" t="inlineStr">
+      <c r="E24" s="6" t="inlineStr">
         <is>
           <t>30131-1</t>
         </is>
       </c>
-      <c r="F24" s="8" t="inlineStr"/>
-      <c r="G24" s="11" t="n"/>
-      <c r="H24" s="11" t="n">
+      <c r="F24" s="7" t="inlineStr"/>
+      <c r="G24" s="10" t="n"/>
+      <c r="H24" s="10" t="n">
         <v>424</v>
       </c>
-      <c r="I24" s="12">
+      <c r="I24" s="11">
         <f>H24/$D$24</f>
         <v/>
       </c>
-      <c r="J24" s="8" t="inlineStr"/>
+      <c r="J24" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -4469,7 +4536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A2:J22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -4484,718 +4551,735 @@
     <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>New tracker: the single column below is today's reading standing in for a weekly record, so it has no NEW SALES figure yet.</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>WEEKLY TEDUH SALES REPORT (MAH SING)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>46262</v>
+      <c r="G3" s="3" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>PROJECT</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>APDL 
 DATE</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>TOTAL 
 UNIT</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>PROJECT 
 CODE</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>DEVELOPER</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Allamanda 5 &amp; 6 @ Meridin East</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>45712</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>235</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>14297-25,14297-28</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>MERIDIN EAST SDN. BHD.</t>
         </is>
       </c>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n">
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n">
         <v>158</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Ferringhi Residence 2</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="8" t="n">
         <v>41622</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>678</v>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>12324-1,12324-2</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>UPTREND HOUSING DEVELOPMENT SDN. BHD.</t>
         </is>
       </c>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n">
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n">
         <v>377</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="11">
         <f>H6/$D$6</f>
         <v/>
       </c>
-      <c r="J6" s="8" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Ferringhi Residence 1: 172 units, Ferringhi Residence 2: 205 units</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Jasmine 2 @ Meridin East</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8" t="n">
         <v>45691</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="9" t="n">
         <v>168</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>14297-24</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>MERIDIN EAST SDN. BHD.</t>
         </is>
       </c>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n">
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n">
         <v>144</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="11">
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>M Amaya</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="8" t="n">
         <v>46161</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>833</v>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>12029-4</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>VIENNA VIEW DEVELOPMENT SDN. BHD.</t>
         </is>
       </c>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n">
-        <v>70</v>
-      </c>
-      <c r="I8" s="12">
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n">
+        <v>73</v>
+      </c>
+      <c r="I8" s="11">
         <f>H8/$D$8</f>
         <v/>
       </c>
-      <c r="J8" s="8" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>M Aria</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>46036</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="9" t="n">
         <v>606</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>31251-1</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>M ARIA SDN. BHD.</t>
         </is>
       </c>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n">
-        <v>48</v>
-      </c>
-      <c r="I9" s="12">
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n">
+        <v>50</v>
+      </c>
+      <c r="I9" s="11">
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>M Aspira</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="8" t="n">
         <v>45531</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="9" t="n">
         <v>1618</v>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>5911-33</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>MAH SING PROPERTIES SDN. BHD.</t>
         </is>
       </c>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n">
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n">
         <v>1013</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="11">
         <f>H10/$D$10</f>
         <v/>
       </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 460 units, Block B: 549 units</t>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 462 units, Block B: 551 units</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>M Aurora</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n">
+      <c r="C11" s="8" t="n">
         <v>46100</v>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="9" t="n">
         <v>1544</v>
       </c>
-      <c r="E11" s="7" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>13262-2</t>
         </is>
       </c>
-      <c r="F11" s="8" t="inlineStr">
+      <c r="F11" s="7" t="inlineStr">
         <is>
           <t>MAJOR LAND DEVELOPMENT SDN. BHD.</t>
         </is>
       </c>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n">
-        <v>359</v>
-      </c>
-      <c r="I11" s="12">
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n">
+        <v>365</v>
+      </c>
+      <c r="I11" s="11">
         <f>H11/$D$11</f>
         <v/>
       </c>
-      <c r="J11" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 51 units, Block B: 304 units</t>
+      <c r="J11" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 57 units, Block B: 308 units</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>M Azura</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="8" t="n">
         <v>45531</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="9" t="n">
         <v>1140</v>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>30834-1</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr">
+      <c r="F12" s="7" t="inlineStr">
         <is>
           <t>M AZURA  SDN. BHD.</t>
         </is>
       </c>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n">
-        <v>795</v>
-      </c>
-      <c r="I12" s="12">
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n">
+        <v>796</v>
+      </c>
+      <c r="I12" s="11">
         <f>H12/$D$12</f>
         <v/>
       </c>
-      <c r="J12" s="8" t="inlineStr"/>
+      <c r="J12" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 424 units, Block B: 372 units</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>M Legasi</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="8" t="n">
         <v>45754</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="9" t="n">
         <v>817</v>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>30897-1,30897-2,30897-3</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr">
+      <c r="F13" s="7" t="inlineStr">
         <is>
           <t>MESTIKA BISTARI SDN. BHD.</t>
         </is>
       </c>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n">
-        <v>644</v>
-      </c>
-      <c r="I13" s="12">
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n">
+        <v>652</v>
+      </c>
+      <c r="I13" s="11">
         <f>H13/$D$13</f>
         <v/>
       </c>
-      <c r="J13" s="8" t="inlineStr"/>
+      <c r="J13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>M Nova</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n">
+      <c r="C14" s="8" t="n">
         <v>45146</v>
       </c>
-      <c r="D14" s="10" t="n">
+      <c r="D14" s="9" t="n">
         <v>2080</v>
       </c>
-      <c r="E14" s="7" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr">
         <is>
           <t>11202-4,11202-5</t>
         </is>
       </c>
-      <c r="F14" s="8" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>MYVILLA DEVELOPMENT SDN. BHD.</t>
         </is>
       </c>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="n">
-        <v>1871</v>
-      </c>
-      <c r="I14" s="12">
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n">
+        <v>1873</v>
+      </c>
+      <c r="I14" s="11">
         <f>H14/$D$14</f>
         <v/>
       </c>
-      <c r="J14" s="8" t="inlineStr"/>
+      <c r="J14" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 614 units, Block B: 611 units, Block C: 648 units</t>
+        </is>
+      </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="n">
+      <c r="A15" s="6" t="n">
         <v>11</v>
       </c>
-      <c r="B15" s="8" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
         <is>
           <t>M Panora</t>
         </is>
       </c>
-      <c r="C15" s="9" t="n">
+      <c r="C15" s="8" t="n">
         <v>44810</v>
       </c>
-      <c r="D15" s="10" t="n">
+      <c r="D15" s="9" t="n">
         <v>396</v>
       </c>
-      <c r="E15" s="7" t="inlineStr">
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>11998-4,11998-5</t>
         </is>
       </c>
-      <c r="F15" s="8" t="inlineStr">
+      <c r="F15" s="7" t="inlineStr">
         <is>
           <t>SEMAI MERANTI SDN. BHD.</t>
         </is>
       </c>
-      <c r="G15" s="11" t="n"/>
-      <c r="H15" s="11" t="n">
+      <c r="G15" s="10" t="n"/>
+      <c r="H15" s="10" t="n">
         <v>396</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="11">
         <f>H15/$D$15</f>
         <v/>
       </c>
-      <c r="J15" s="8" t="inlineStr"/>
+      <c r="J15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="7" t="n">
+      <c r="A16" s="6" t="n">
         <v>12</v>
       </c>
-      <c r="B16" s="8" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>M Sinar @ Southville City</t>
         </is>
       </c>
-      <c r="C16" s="9" t="n">
+      <c r="C16" s="8" t="n">
         <v>45443</v>
       </c>
-      <c r="D16" s="10" t="n">
+      <c r="D16" s="9" t="n">
         <v>999</v>
       </c>
-      <c r="E16" s="7" t="inlineStr">
+      <c r="E16" s="6" t="inlineStr">
         <is>
           <t>13425-8,13425-9</t>
         </is>
       </c>
-      <c r="F16" s="8" t="inlineStr">
+      <c r="F16" s="7" t="inlineStr">
         <is>
           <t>SOUTHVILLE CITY SDN. BHD.</t>
         </is>
       </c>
-      <c r="G16" s="11" t="n"/>
-      <c r="H16" s="11" t="n">
-        <v>393</v>
-      </c>
-      <c r="I16" s="12">
+      <c r="G16" s="10" t="n"/>
+      <c r="H16" s="10" t="n">
+        <v>394</v>
+      </c>
+      <c r="I16" s="11">
         <f>H16/$D$16</f>
         <v/>
       </c>
-      <c r="J16" s="8" t="inlineStr"/>
+      <c r="J16" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 394 units</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="7" t="n">
+      <c r="A17" s="6" t="n">
         <v>13</v>
       </c>
-      <c r="B17" s="8" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>M Terra</t>
         </is>
       </c>
-      <c r="C17" s="9" t="n">
+      <c r="C17" s="8" t="n">
         <v>45498</v>
       </c>
-      <c r="D17" s="10" t="n">
+      <c r="D17" s="9" t="n">
         <v>999</v>
       </c>
-      <c r="E17" s="7" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>30805-1</t>
         </is>
       </c>
-      <c r="F17" s="8" t="inlineStr">
+      <c r="F17" s="7" t="inlineStr">
         <is>
           <t>SUPREME SPRINGS SDN. BHD.</t>
         </is>
       </c>
-      <c r="G17" s="11" t="n"/>
-      <c r="H17" s="11" t="n">
-        <v>578</v>
-      </c>
-      <c r="I17" s="12">
+      <c r="G17" s="10" t="n"/>
+      <c r="H17" s="10" t="n">
+        <v>581</v>
+      </c>
+      <c r="I17" s="11">
         <f>H17/$D$17</f>
         <v/>
       </c>
-      <c r="J17" s="8" t="inlineStr"/>
+      <c r="J17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="7" t="n">
+      <c r="A18" s="6" t="n">
         <v>14</v>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>M Tiara</t>
         </is>
       </c>
-      <c r="C18" s="9" t="n">
+      <c r="C18" s="8" t="n">
         <v>45523</v>
       </c>
-      <c r="D18" s="10" t="n">
+      <c r="D18" s="9" t="n">
         <v>754</v>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E18" s="6" t="inlineStr">
         <is>
           <t>10279-5,10279-6,10279-7,10279-8</t>
         </is>
       </c>
-      <c r="F18" s="8" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>VENICE VIEW DEVELOPMENT SDN. BHD.</t>
         </is>
       </c>
-      <c r="G18" s="11" t="n"/>
-      <c r="H18" s="11" t="n">
-        <v>651</v>
-      </c>
-      <c r="I18" s="12">
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="10" t="n">
+        <v>652</v>
+      </c>
+      <c r="I18" s="11">
         <f>H18/$D$18</f>
         <v/>
       </c>
-      <c r="J18" s="8" t="inlineStr"/>
+      <c r="J18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="n">
+      <c r="A19" s="6" t="n">
         <v>15</v>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>M Zenni</t>
         </is>
       </c>
-      <c r="C19" s="9" t="n">
+      <c r="C19" s="8" t="n">
         <v>45923</v>
       </c>
-      <c r="D19" s="10" t="n">
+      <c r="D19" s="9" t="n">
         <v>494</v>
       </c>
-      <c r="E19" s="7" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>12029-3</t>
         </is>
       </c>
-      <c r="F19" s="8" t="inlineStr">
+      <c r="F19" s="7" t="inlineStr">
         <is>
           <t>VIENNA VIEW DEVELOPMENT SDN. BHD.</t>
         </is>
       </c>
-      <c r="G19" s="11" t="n"/>
-      <c r="H19" s="11" t="n">
-        <v>228</v>
-      </c>
-      <c r="I19" s="12">
+      <c r="G19" s="10" t="n"/>
+      <c r="H19" s="10" t="n">
+        <v>232</v>
+      </c>
+      <c r="I19" s="11">
         <f>H19/$D$19</f>
         <v/>
       </c>
-      <c r="J19" s="8" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="7" t="n">
+      <c r="A20" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>M Zenya</t>
         </is>
       </c>
-      <c r="C20" s="9" t="n">
+      <c r="C20" s="8" t="n">
         <v>45383</v>
       </c>
-      <c r="D20" s="10" t="n">
+      <c r="D20" s="9" t="n">
         <v>619</v>
       </c>
-      <c r="E20" s="7" t="inlineStr">
+      <c r="E20" s="6" t="inlineStr">
         <is>
           <t>11430-2</t>
         </is>
       </c>
-      <c r="F20" s="8" t="inlineStr">
+      <c r="F20" s="7" t="inlineStr">
         <is>
           <t>M ZENYA  SDN. BHD.</t>
         </is>
       </c>
-      <c r="G20" s="11" t="n"/>
-      <c r="H20" s="11" t="n">
+      <c r="G20" s="10" t="n"/>
+      <c r="H20" s="10" t="n">
         <v>618</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="11">
         <f>H20/$D$20</f>
         <v/>
       </c>
-      <c r="J20" s="8" t="inlineStr"/>
+      <c r="J20" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 618 units</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="n">
+      <c r="A21" s="6" t="n">
         <v>17</v>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B21" s="7" t="inlineStr">
         <is>
           <t>M Grand Minori</t>
         </is>
       </c>
-      <c r="C21" s="9" t="n">
+      <c r="C21" s="8" t="n">
         <v>45898</v>
       </c>
-      <c r="D21" s="10" t="n">
+      <c r="D21" s="9" t="n">
         <v>1733</v>
       </c>
-      <c r="E21" s="7" t="inlineStr">
+      <c r="E21" s="6" t="inlineStr">
         <is>
           <t>9600-6,9600-7</t>
         </is>
       </c>
-      <c r="F21" s="8" t="inlineStr"/>
-      <c r="G21" s="11" t="n"/>
-      <c r="H21" s="11" t="n">
+      <c r="F21" s="7" t="inlineStr"/>
+      <c r="G21" s="10" t="n"/>
+      <c r="H21" s="10" t="n">
         <v>762</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="11">
         <f>H21/$D$21</f>
         <v/>
       </c>
-      <c r="J21" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 499 units, Block B: 257 units</t>
+      <c r="J21" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 501 units, Block B: 261 units</t>
         </is>
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="n">
+      <c r="A22" s="6" t="n">
         <v>18</v>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B22" s="7" t="inlineStr">
         <is>
           <t>M Minori</t>
         </is>
       </c>
-      <c r="C22" s="9" t="n">
+      <c r="C22" s="8" t="n">
         <v>45201</v>
       </c>
-      <c r="D22" s="10" t="n">
+      <c r="D22" s="9" t="n">
         <v>1526</v>
       </c>
-      <c r="E22" s="7" t="inlineStr">
+      <c r="E22" s="6" t="inlineStr">
         <is>
           <t>30440-1,30440-2,30440-3</t>
         </is>
       </c>
-      <c r="F22" s="8" t="inlineStr"/>
-      <c r="G22" s="11" t="n"/>
-      <c r="H22" s="11" t="n">
-        <v>1471</v>
-      </c>
-      <c r="I22" s="12">
+      <c r="F22" s="7" t="inlineStr"/>
+      <c r="G22" s="10" t="n"/>
+      <c r="H22" s="10" t="n">
+        <v>1474</v>
+      </c>
+      <c r="I22" s="11">
         <f>H22/$D$22</f>
         <v/>
       </c>
-      <c r="J22" s="8" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 416 units, Block B: 578 units, Block C: 480 units</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5211,7 +5295,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A2:J14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5226,408 +5310,401 @@
     <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>New tracker: the single column below is today's reading standing in for a weekly record, so it has no NEW SALES figure yet.</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>WEEKLY TEDUH SALES REPORT (MAJESTIC GEN)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>46262</v>
+      <c r="G3" s="3" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>PROJECT</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>APDL 
 DATE</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>TOTAL 
 UNIT</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>PROJECT 
 CODE</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>DEVELOPER</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Gen Rise</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>45631</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>732</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>30828-2</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>MAJESTIC GEN  SDN. BHD.</t>
         </is>
       </c>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n">
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n">
         <v>731</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Gen Sphere</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="8" t="n">
         <v>45804</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>996</v>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>30828-3</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>MAJESTIC GEN  SDN. BHD.</t>
         </is>
       </c>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n">
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n">
         <v>908</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="11">
         <f>H6/$D$6</f>
         <v/>
       </c>
-      <c r="J6" s="8" t="inlineStr">
+      <c r="J6" s="7" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Gen Starz</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8" t="n">
         <v>45569</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="9" t="n">
         <v>360</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>30828-1</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>MAJESTIC GEN  SDN. BHD.</t>
         </is>
       </c>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n">
-        <v>354</v>
-      </c>
-      <c r="I7" s="12">
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n">
+        <v>355</v>
+      </c>
+      <c r="I7" s="11">
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Majestic Residence</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="8" t="n">
         <v>44995</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>478</v>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>30244-1</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>MAJESTIC LUXE SDN. BHD.</t>
         </is>
       </c>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n">
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n">
         <v>478</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="11">
         <f>H8/$D$8</f>
         <v/>
       </c>
-      <c r="J8" s="8" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Majestic Yu</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>45831</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="9" t="n">
         <v>106</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>30990-1</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>MAJESTIC GEN (SOUTHERN) SDN. BHD.</t>
         </is>
       </c>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n">
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n">
         <v>98</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="11">
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="7" t="n">
+      <c r="A10" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B10" s="8" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>Yahya Awal Mixed Development (JV with Sunway Property)</t>
         </is>
       </c>
-      <c r="C10" s="9" t="n">
+      <c r="C10" s="8" t="n">
         <v>45936</v>
       </c>
-      <c r="D10" s="10" t="n">
+      <c r="D10" s="9" t="n">
         <v>1012</v>
       </c>
-      <c r="E10" s="7" t="inlineStr">
+      <c r="E10" s="6" t="inlineStr">
         <is>
           <t>31034-1</t>
         </is>
       </c>
-      <c r="F10" s="8" t="inlineStr">
+      <c r="F10" s="7" t="inlineStr">
         <is>
           <t>SUNWAY MAJESTIC  SDN. BHD.</t>
         </is>
       </c>
-      <c r="G10" s="11" t="n"/>
-      <c r="H10" s="11" t="n">
-        <v>392</v>
-      </c>
-      <c r="I10" s="12">
+      <c r="G10" s="10" t="n"/>
+      <c r="H10" s="10" t="n">
+        <v>393</v>
+      </c>
+      <c r="I10" s="11">
         <f>H10/$D$10</f>
         <v/>
       </c>
-      <c r="J10" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 297 units, Block B: 93 units</t>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 297 units, Block B: 96 units</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n">
+      <c r="A11" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B11" s="8" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>George Town High-Rise Development</t>
         </is>
       </c>
-      <c r="C11" s="9" t="n"/>
-      <c r="D11" s="10" t="n">
+      <c r="C11" s="8" t="n"/>
+      <c r="D11" s="9" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="7" t="inlineStr"/>
-      <c r="F11" s="8" t="inlineStr"/>
-      <c r="G11" s="11" t="n"/>
-      <c r="H11" s="11" t="n"/>
-      <c r="I11" s="12" t="n"/>
-      <c r="J11" s="8" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr"/>
+      <c r="F11" s="7" t="inlineStr"/>
+      <c r="G11" s="10" t="n"/>
+      <c r="H11" s="10" t="n"/>
+      <c r="I11" s="11" t="n"/>
+      <c r="J11" s="7" t="inlineStr">
         <is>
           <t>Not launched yet.</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="n">
+      <c r="A12" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B12" s="8" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>Majestic Aman</t>
         </is>
       </c>
-      <c r="C12" s="9" t="n">
+      <c r="C12" s="8" t="n">
         <v>45813</v>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="9" t="n">
         <v>73</v>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E12" s="6" t="inlineStr">
         <is>
           <t>30989-1</t>
         </is>
       </c>
-      <c r="F12" s="8" t="inlineStr"/>
-      <c r="G12" s="11" t="n"/>
-      <c r="H12" s="11" t="n">
+      <c r="F12" s="7" t="inlineStr"/>
+      <c r="G12" s="10" t="n"/>
+      <c r="H12" s="10" t="n">
         <v>73</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="11">
         <f>H12/$D$12</f>
         <v/>
       </c>
-      <c r="J12" s="8" t="inlineStr"/>
+      <c r="J12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="n">
+      <c r="A13" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B13" s="8" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>Majestic Flora</t>
         </is>
       </c>
-      <c r="C13" s="9" t="n">
+      <c r="C13" s="8" t="n">
         <v>46191</v>
       </c>
-      <c r="D13" s="10" t="n">
+      <c r="D13" s="9" t="n">
         <v>140</v>
       </c>
-      <c r="E13" s="7" t="inlineStr">
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>12069-7</t>
         </is>
       </c>
-      <c r="F13" s="8" t="inlineStr"/>
-      <c r="G13" s="11" t="n"/>
-      <c r="H13" s="11" t="n">
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n">
         <v>0</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="11">
         <f>H13/$D$13</f>
         <v/>
       </c>
-      <c r="J13" s="8" t="inlineStr"/>
+      <c r="J13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="n">
+      <c r="A14" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="B14" s="8" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>Majestic PD Township*</t>
         </is>
       </c>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="10" t="n">
+      <c r="C14" s="8" t="n"/>
+      <c r="D14" s="9" t="n">
         <v>97</v>
       </c>
-      <c r="E14" s="7" t="inlineStr"/>
-      <c r="F14" s="8" t="inlineStr"/>
-      <c r="G14" s="11" t="n"/>
-      <c r="H14" s="11" t="n"/>
-      <c r="I14" s="12" t="n"/>
-      <c r="J14" s="8" t="inlineStr">
+      <c r="E14" s="6" t="inlineStr"/>
+      <c r="F14" s="7" t="inlineStr"/>
+      <c r="G14" s="10" t="n"/>
+      <c r="H14" s="10" t="n"/>
+      <c r="I14" s="11" t="n"/>
+      <c r="J14" s="7" t="inlineStr">
         <is>
           <t>Not launched yet.</t>
         </is>
@@ -5647,7 +5724,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A2:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5662,255 +5739,260 @@
     <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>New tracker: the single column below is today's reading standing in for a weekly record, so it has no NEW SALES figure yet.</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>WEEKLY TEDUH SALES REPORT (MALTON)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>46262</v>
+      <c r="G3" s="3" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>PROJECT</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>APDL 
 DATE</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>TOTAL 
 UNIT</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>PROJECT 
 CODE</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>DEVELOPER</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Mutiara Kempas</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>46121</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>562</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>31139-1</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>KHUAN CHOO SDN. BHD.</t>
         </is>
       </c>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n">
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n">
         <v>349</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Mutiara Lake Puchong</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="8" t="n">
         <v>46108</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>526</v>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>8950-4</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>INTERPILE (M) SDN BHD</t>
         </is>
       </c>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n">
-        <v>12</v>
-      </c>
-      <c r="I6" s="12">
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n">
+        <v>13</v>
+      </c>
+      <c r="I6" s="11">
         <f>H6/$D$6</f>
         <v/>
       </c>
-      <c r="J6" s="8" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block N: 7 units, Block S: 6 units</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Park Green @ Pavilion Bukit Jalil</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8" t="n">
         <v>45565</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="9" t="n">
         <v>453</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>30667-1</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>REGAL PATH SDN. BHD.</t>
         </is>
       </c>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n">
-        <v>392</v>
-      </c>
-      <c r="I7" s="12">
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n">
+        <v>393</v>
+      </c>
+      <c r="I7" s="11">
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr"/>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 170 units, Block B: 223 units</t>
+        </is>
+      </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Ria Bangsar South</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="8" t="n">
         <v>45768</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>336</v>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>14035-6</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>KUMPULAN GAPADU SDN. BHD.</t>
         </is>
       </c>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n">
-        <v>328</v>
-      </c>
-      <c r="I8" s="12">
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n">
+        <v>329</v>
+      </c>
+      <c r="I8" s="11">
         <f>H8/$D$8</f>
         <v/>
       </c>
-      <c r="J8" s="8" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>River Park Bangsar South</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>44617</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="9" t="n">
         <v>1332</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>14035-4,14035-5</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr"/>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n">
-        <v>980</v>
-      </c>
-      <c r="I9" s="12">
+      <c r="F9" s="7" t="inlineStr"/>
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n">
+        <v>981</v>
+      </c>
+      <c r="I9" s="11">
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 355 units, Block B: 334 units, Block C: 292 units</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -5926,7 +6008,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A2:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -5941,263 +6023,272 @@
     <col width="46" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>New tracker: the single column below is today's reading standing in for a weekly record, so it has no NEW SALES figure yet.</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="1" t="inlineStr">
         <is>
           <t>Report as at 03/09/2026</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="2" t="inlineStr">
         <is>
           <t>WEEKLY TEDUH SALES REPORT (MAXIM)</t>
         </is>
       </c>
-      <c r="G3" s="4" t="n">
-        <v>46262</v>
+      <c r="G3" s="3" t="n">
+        <v>46269</v>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>NO</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="4" t="inlineStr">
         <is>
           <t>PROJECT</t>
         </is>
       </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>APDL 
 DATE</t>
         </is>
       </c>
-      <c r="D4" s="5" t="inlineStr">
+      <c r="D4" s="4" t="inlineStr">
         <is>
           <t>TOTAL 
 UNIT</t>
         </is>
       </c>
-      <c r="E4" s="5" t="inlineStr">
+      <c r="E4" s="4" t="inlineStr">
         <is>
           <t>PROJECT 
 CODE</t>
         </is>
       </c>
-      <c r="F4" s="5" t="inlineStr">
+      <c r="F4" s="4" t="inlineStr">
         <is>
           <t>DEVELOPER</t>
         </is>
       </c>
-      <c r="G4" s="6" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>NEW SALES</t>
         </is>
       </c>
-      <c r="H4" s="6" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>TOTAL SOLD</t>
         </is>
       </c>
-      <c r="I4" s="6" t="inlineStr">
+      <c r="I4" s="5" t="inlineStr">
         <is>
           <t>TOTAL %</t>
         </is>
       </c>
-      <c r="J4" s="5" t="inlineStr">
+      <c r="J4" s="4" t="inlineStr">
         <is>
           <t>NOTES</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="n">
+      <c r="A5" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="8" t="inlineStr">
+      <c r="B5" s="7" t="inlineStr">
         <is>
           <t>Residensi Max II</t>
         </is>
       </c>
-      <c r="C5" s="9" t="n">
+      <c r="C5" s="8" t="n">
         <v>45103</v>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="9" t="n">
         <v>604</v>
       </c>
-      <c r="E5" s="7" t="inlineStr">
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>30267-1</t>
         </is>
       </c>
-      <c r="F5" s="8" t="inlineStr">
+      <c r="F5" s="7" t="inlineStr">
         <is>
           <t>PROMINENT MAXIM SDN. BHD.</t>
         </is>
       </c>
-      <c r="G5" s="11" t="n"/>
-      <c r="H5" s="11" t="n">
+      <c r="G5" s="10" t="n"/>
+      <c r="H5" s="10" t="n">
         <v>604</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <f>H5/$D$5</f>
         <v/>
       </c>
-      <c r="J5" s="8" t="inlineStr"/>
+      <c r="J5" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 302 units, Block B: 302 units</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="7" t="n">
+      <c r="A6" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B6" s="8" t="inlineStr">
+      <c r="B6" s="7" t="inlineStr">
         <is>
           <t>Residensi Maxim D’Parc</t>
         </is>
       </c>
-      <c r="C6" s="9" t="n">
+      <c r="C6" s="8" t="n">
         <v>46057</v>
       </c>
-      <c r="D6" s="10" t="n">
+      <c r="D6" s="9" t="n">
         <v>1116</v>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="E6" s="6" t="inlineStr">
         <is>
           <t>31046-1</t>
         </is>
       </c>
-      <c r="F6" s="8" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>MIZUMI MAXIM SDN. BHD.</t>
         </is>
       </c>
-      <c r="G6" s="11" t="n"/>
-      <c r="H6" s="11" t="n">
-        <v>321</v>
-      </c>
-      <c r="I6" s="12">
+      <c r="G6" s="10" t="n"/>
+      <c r="H6" s="10" t="n">
+        <v>325</v>
+      </c>
+      <c r="I6" s="11">
         <f>H6/$D$6</f>
         <v/>
       </c>
-      <c r="J6" s="8" t="inlineStr"/>
+      <c r="J6" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 111 units, Block B: 214 units</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="7" t="n">
+      <c r="A7" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B7" s="8" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>Residensi Maxim Pelangi</t>
         </is>
       </c>
-      <c r="C7" s="9" t="n">
+      <c r="C7" s="8" t="n">
         <v>45884</v>
       </c>
-      <c r="D7" s="10" t="n">
+      <c r="D7" s="9" t="n">
         <v>2743</v>
       </c>
-      <c r="E7" s="7" t="inlineStr">
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>31074-1</t>
         </is>
       </c>
-      <c r="F7" s="8" t="inlineStr">
+      <c r="F7" s="7" t="inlineStr">
         <is>
           <t>MAXIM PELANGI SDN. BHD.</t>
         </is>
       </c>
-      <c r="G7" s="11" t="n"/>
-      <c r="H7" s="11" t="n">
-        <v>1010</v>
-      </c>
-      <c r="I7" s="12">
+      <c r="G7" s="10" t="n"/>
+      <c r="H7" s="10" t="n">
+        <v>1011</v>
+      </c>
+      <c r="I7" s="11">
         <f>H7/$D$7</f>
         <v/>
       </c>
-      <c r="J7" s="8" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 403 units, Block B: 369 units, Block C: 234 units</t>
+      <c r="J7" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 403 units, Block B: 371 units, Block C: 237 units</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="n">
+      <c r="A8" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B8" s="8" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>Residensi Maxim Risen</t>
         </is>
       </c>
-      <c r="C8" s="9" t="n">
+      <c r="C8" s="8" t="n">
         <v>44733</v>
       </c>
-      <c r="D8" s="10" t="n">
+      <c r="D8" s="9" t="n">
         <v>1236</v>
       </c>
-      <c r="E8" s="7" t="inlineStr">
+      <c r="E8" s="6" t="inlineStr">
         <is>
           <t>30037-1</t>
         </is>
       </c>
-      <c r="F8" s="8" t="inlineStr">
+      <c r="F8" s="7" t="inlineStr">
         <is>
           <t>BUILTAMONT DEVELOPMENT SDN. BHD.</t>
         </is>
       </c>
-      <c r="G8" s="11" t="n"/>
-      <c r="H8" s="11" t="n">
+      <c r="G8" s="10" t="n"/>
+      <c r="H8" s="10" t="n">
         <v>1236</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="11">
         <f>H8/$D$8</f>
         <v/>
       </c>
-      <c r="J8" s="8" t="inlineStr"/>
+      <c r="J8" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 629 units, Block B: 607 units</t>
+        </is>
+      </c>
     </row>
     <row r="9">
-      <c r="A9" s="7" t="n">
+      <c r="A9" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B9" s="8" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>Residensi The Atas</t>
         </is>
       </c>
-      <c r="C9" s="9" t="n">
+      <c r="C9" s="8" t="n">
         <v>45412</v>
       </c>
-      <c r="D9" s="10" t="n">
+      <c r="D9" s="9" t="n">
         <v>624</v>
       </c>
-      <c r="E9" s="7" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>19088-3</t>
         </is>
       </c>
-      <c r="F9" s="8" t="inlineStr">
+      <c r="F9" s="7" t="inlineStr">
         <is>
           <t>KAISAR MAXIM SDN. BHD.</t>
         </is>
       </c>
-      <c r="G9" s="11" t="n"/>
-      <c r="H9" s="11" t="n">
+      <c r="G9" s="10" t="n"/>
+      <c r="H9" s="10" t="n">
         <v>523</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="11">
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="8" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 178 units, Block B: 164 units, Block C: 181 units</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/09/2026</t>
+          <t>Report as at 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/09/2026</t>
+          <t>Report as at 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/09/2026</t>
+          <t>Report as at 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/09/2026</t>
+          <t>Report as at 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/09/2026</t>
+          <t>Report as at 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/09/2026</t>
+          <t>Report as at 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -2658,7 +2658,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:J12"/>
+  <dimension ref="A2:J13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2676,7 +2676,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/09/2026</t>
+          <t>Report as at 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -3001,7 +3001,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Aetas Taman Desa</t>
+          <t>Aetas Damansara</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
@@ -3027,6 +3027,30 @@
       <c r="J12" s="7" t="inlineStr">
         <is>
           <t>Latest sales - Block A: 144 units, Block B: 77 units</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Aetas Taman Desa</t>
+        </is>
+      </c>
+      <c r="C13" s="8" t="n"/>
+      <c r="D13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr"/>
+      <c r="F13" s="7" t="inlineStr"/>
+      <c r="G13" s="10" t="n"/>
+      <c r="H13" s="10" t="n"/>
+      <c r="I13" s="11" t="n"/>
+      <c r="J13" s="7" t="inlineStr">
+        <is>
+          <t>Not yet launched</t>
         </is>
       </c>
     </row>
@@ -3062,7 +3086,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/09/2026</t>
+          <t>Report as at 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -3254,7 +3278,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/09/2026</t>
+          <t>Report as at 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -3721,7 +3745,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/09/2026</t>
+          <t>Report as at 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -4554,7 +4578,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/09/2026</t>
+          <t>Report as at 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5337,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/09/2026</t>
+          <t>Report as at 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -5742,7 +5766,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/09/2026</t>
+          <t>Report as at 04/09/2026</t>
         </is>
       </c>
     </row>
@@ -6026,7 +6050,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 03/09/2026</t>
+          <t>Report as at 04/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/09/2026</t>
+          <t>Report as at 05/09/2026</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/09/2026</t>
+          <t>Report as at 05/09/2026</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/09/2026</t>
+          <t>Report as at 05/09/2026</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/09/2026</t>
+          <t>Report as at 05/09/2026</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/09/2026</t>
+          <t>Report as at 05/09/2026</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/09/2026</t>
+          <t>Report as at 05/09/2026</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/09/2026</t>
+          <t>Report as at 05/09/2026</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/09/2026</t>
+          <t>Report as at 05/09/2026</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/09/2026</t>
+          <t>Report as at 05/09/2026</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/09/2026</t>
+          <t>Report as at 05/09/2026</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/09/2026</t>
+          <t>Report as at 05/09/2026</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/09/2026</t>
+          <t>Report as at 05/09/2026</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/09/2026</t>
+          <t>Report as at 05/09/2026</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 04/09/2026</t>
+          <t>Report as at 05/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/09/2026</t>
+          <t>Report as at 06/09/2026</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/09/2026</t>
+          <t>Report as at 06/09/2026</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/09/2026</t>
+          <t>Report as at 06/09/2026</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/09/2026</t>
+          <t>Report as at 06/09/2026</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/09/2026</t>
+          <t>Report as at 06/09/2026</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/09/2026</t>
+          <t>Report as at 06/09/2026</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/09/2026</t>
+          <t>Report as at 06/09/2026</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/09/2026</t>
+          <t>Report as at 06/09/2026</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/09/2026</t>
+          <t>Report as at 06/09/2026</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/09/2026</t>
+          <t>Report as at 06/09/2026</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/09/2026</t>
+          <t>Report as at 06/09/2026</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/09/2026</t>
+          <t>Report as at 06/09/2026</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/09/2026</t>
+          <t>Report as at 06/09/2026</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 05/09/2026</t>
+          <t>Report as at 06/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/09/2026</t>
+          <t>Report as at 07/09/2026</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/09/2026</t>
+          <t>Report as at 07/09/2026</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/09/2026</t>
+          <t>Report as at 07/09/2026</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/09/2026</t>
+          <t>Report as at 07/09/2026</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/09/2026</t>
+          <t>Report as at 07/09/2026</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/09/2026</t>
+          <t>Report as at 07/09/2026</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/09/2026</t>
+          <t>Report as at 07/09/2026</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/09/2026</t>
+          <t>Report as at 07/09/2026</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/09/2026</t>
+          <t>Report as at 07/09/2026</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/09/2026</t>
+          <t>Report as at 07/09/2026</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/09/2026</t>
+          <t>Report as at 07/09/2026</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/09/2026</t>
+          <t>Report as at 07/09/2026</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/09/2026</t>
+          <t>Report as at 07/09/2026</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 06/09/2026</t>
+          <t>Report as at 07/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/09/2026</t>
+          <t>Report as at 08/09/2026</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/09/2026</t>
+          <t>Report as at 08/09/2026</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/09/2026</t>
+          <t>Report as at 08/09/2026</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/09/2026</t>
+          <t>Report as at 08/09/2026</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/09/2026</t>
+          <t>Report as at 08/09/2026</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/09/2026</t>
+          <t>Report as at 08/09/2026</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/09/2026</t>
+          <t>Report as at 08/09/2026</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/09/2026</t>
+          <t>Report as at 08/09/2026</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/09/2026</t>
+          <t>Report as at 08/09/2026</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/09/2026</t>
+          <t>Report as at 08/09/2026</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/09/2026</t>
+          <t>Report as at 08/09/2026</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/09/2026</t>
+          <t>Report as at 08/09/2026</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/09/2026</t>
+          <t>Report as at 08/09/2026</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 07/09/2026</t>
+          <t>Report as at 08/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -513,7 +513,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/09/2026</t>
+          <t>Report as at 09/09/2026</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/09/2026</t>
+          <t>Report as at 09/09/2026</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/09/2026</t>
+          <t>Report as at 09/09/2026</t>
         </is>
       </c>
     </row>
@@ -1777,7 +1777,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/09/2026</t>
+          <t>Report as at 09/09/2026</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/09/2026</t>
+          <t>Report as at 09/09/2026</t>
         </is>
       </c>
     </row>
@@ -2407,7 +2407,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/09/2026</t>
+          <t>Report as at 09/09/2026</t>
         </is>
       </c>
     </row>
@@ -2676,7 +2676,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/09/2026</t>
+          <t>Report as at 09/09/2026</t>
         </is>
       </c>
     </row>
@@ -3086,7 +3086,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/09/2026</t>
+          <t>Report as at 09/09/2026</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/09/2026</t>
+          <t>Report as at 09/09/2026</t>
         </is>
       </c>
     </row>
@@ -3745,7 +3745,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/09/2026</t>
+          <t>Report as at 09/09/2026</t>
         </is>
       </c>
     </row>
@@ -4578,7 +4578,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/09/2026</t>
+          <t>Report as at 09/09/2026</t>
         </is>
       </c>
     </row>
@@ -5337,7 +5337,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/09/2026</t>
+          <t>Report as at 09/09/2026</t>
         </is>
       </c>
     </row>
@@ -5766,7 +5766,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/09/2026</t>
+          <t>Report as at 09/09/2026</t>
         </is>
       </c>
     </row>
@@ -6050,7 +6050,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 08/09/2026</t>
+          <t>Report as at 09/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -2691,7 +2691,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3354,24 +3354,24 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Kita Bestari</t>
+          <t>Corallia @ D'Island</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>44999</v>
+        <v>42196</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>817</v>
+        <v>56</v>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>19533-5</t>
+          <t>11482-8</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr"/>
       <c r="G22" s="10" t="n"/>
       <c r="H22" s="10" t="n">
-        <v>812</v>
+        <v>52</v>
       </c>
       <c r="I22" s="11">
         <f>H22/$D$22</f>
@@ -3385,24 +3385,24 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Corallia @ D'Island</t>
+          <t>SkyVilla @ D'Island</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>42196</v>
+        <v>42152</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>56</v>
+        <v>352</v>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>11482-8</t>
+          <t>11482-7</t>
         </is>
       </c>
       <c r="F23" s="7" t="inlineStr"/>
       <c r="G23" s="10" t="n"/>
       <c r="H23" s="10" t="n">
-        <v>52</v>
+        <v>314</v>
       </c>
       <c r="I23" s="11">
         <f>H23/$D$23</f>
@@ -3416,24 +3416,24 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>SkyVilla @ D'Island</t>
+          <t>Nautilus @ D'Island</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>42152</v>
+        <v>40886</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>352</v>
+        <v>115</v>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>11482-7</t>
+          <t>11482-5</t>
         </is>
       </c>
       <c r="F24" s="7" t="inlineStr"/>
       <c r="G24" s="10" t="n"/>
       <c r="H24" s="10" t="n">
-        <v>314</v>
+        <v>84</v>
       </c>
       <c r="I24" s="11">
         <f>H24/$D$24</f>
@@ -3447,24 +3447,24 @@
       </c>
       <c r="B25" s="7" t="inlineStr">
         <is>
-          <t>Nautilus @ D'Island</t>
+          <t>Skylake @ D'Island</t>
         </is>
       </c>
       <c r="C25" s="8" t="n">
-        <v>40886</v>
+        <v>42965</v>
       </c>
       <c r="D25" s="9" t="n">
-        <v>115</v>
+        <v>746</v>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>11482-5</t>
+          <t>11482-9</t>
         </is>
       </c>
       <c r="F25" s="7" t="inlineStr"/>
       <c r="G25" s="10" t="n"/>
       <c r="H25" s="10" t="n">
-        <v>84</v>
+        <v>454</v>
       </c>
       <c r="I25" s="11">
         <f>H25/$D$25</f>
@@ -3478,24 +3478,24 @@
       </c>
       <c r="B26" s="7" t="inlineStr">
         <is>
-          <t>Skylake @ D'Island</t>
+          <t>Ritma Perdana</t>
         </is>
       </c>
       <c r="C26" s="8" t="n">
-        <v>42965</v>
+        <v>44029</v>
       </c>
       <c r="D26" s="9" t="n">
-        <v>746</v>
+        <v>1151</v>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>11482-9</t>
+          <t>19183-11</t>
         </is>
       </c>
       <c r="F26" s="7" t="inlineStr"/>
       <c r="G26" s="10" t="n"/>
       <c r="H26" s="10" t="n">
-        <v>454</v>
+        <v>446</v>
       </c>
       <c r="I26" s="11">
         <f>H26/$D$26</f>
@@ -3509,24 +3509,24 @@
       </c>
       <c r="B27" s="7" t="inlineStr">
         <is>
-          <t>Ritma Perdana</t>
+          <t>Emerald Garden 3</t>
         </is>
       </c>
       <c r="C27" s="8" t="n">
-        <v>44029</v>
+        <v>44259</v>
       </c>
       <c r="D27" s="9" t="n">
-        <v>1151</v>
+        <v>155</v>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>19183-11</t>
+          <t>7702-44,7702-45,7702-46,7702-47,7702-48</t>
         </is>
       </c>
       <c r="F27" s="7" t="inlineStr"/>
       <c r="G27" s="10" t="n"/>
       <c r="H27" s="10" t="n">
-        <v>446</v>
+        <v>150</v>
       </c>
       <c r="I27" s="11">
         <f>H27/$D$27</f>
@@ -3540,24 +3540,24 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>Emerald Garden 3</t>
+          <t>BSP21</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>44259</v>
+        <v>41976</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>155</v>
+        <v>2602</v>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>7702-44,7702-45,7702-46,7702-47,7702-48</t>
+          <t>8945-4,8945-5,8945-6,8945-7</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr"/>
       <c r="G28" s="10" t="n"/>
       <c r="H28" s="10" t="n">
-        <v>150</v>
+        <v>2149</v>
       </c>
       <c r="I28" s="11">
         <f>H28/$D$28</f>
@@ -3571,24 +3571,24 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>BSP21</t>
+          <t>BSP Skypark</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
-        <v>41976</v>
+        <v>41627</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>2602</v>
+        <v>689</v>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>8945-4,8945-5,8945-6,8945-7</t>
+          <t>8945-3</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr"/>
       <c r="G29" s="10" t="n"/>
       <c r="H29" s="10" t="n">
-        <v>2149</v>
+        <v>491</v>
       </c>
       <c r="I29" s="11">
         <f>H29/$D$29</f>
@@ -3602,30 +3602,23 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>BSP Skypark</t>
-        </is>
-      </c>
-      <c r="C30" s="8" t="n">
-        <v>41627</v>
-      </c>
+          <t>Sherwood Residence</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="n"/>
       <c r="D30" s="9" t="n">
-        <v>689</v>
-      </c>
-      <c r="E30" s="6" t="inlineStr">
-        <is>
-          <t>8945-3</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E30" s="6" t="inlineStr"/>
       <c r="F30" s="7" t="inlineStr"/>
       <c r="G30" s="10" t="n"/>
-      <c r="H30" s="10" t="n">
-        <v>491</v>
-      </c>
-      <c r="I30" s="11">
-        <f>H30/$D$30</f>
-        <v/>
-      </c>
-      <c r="J30" s="7" t="inlineStr"/>
+      <c r="H30" s="10" t="n"/>
+      <c r="I30" s="11" t="n"/>
+      <c r="J30" s="7" t="inlineStr">
+        <is>
+          <t>Not launched yet.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="n">
@@ -3633,7 +3626,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Sherwood Residence</t>
+          <t>Amira Residences</t>
         </is>
       </c>
       <c r="C31" s="8" t="n"/>
@@ -3646,30 +3639,6 @@
       <c r="H31" s="10" t="n"/>
       <c r="I31" s="11" t="n"/>
       <c r="J31" s="7" t="inlineStr">
-        <is>
-          <t>Not launched yet.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="n">
-        <v>28</v>
-      </c>
-      <c r="B32" s="7" t="inlineStr">
-        <is>
-          <t>Amira Residences</t>
-        </is>
-      </c>
-      <c r="C32" s="8" t="n"/>
-      <c r="D32" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="6" t="inlineStr"/>
-      <c r="F32" s="7" t="inlineStr"/>
-      <c r="G32" s="10" t="n"/>
-      <c r="H32" s="10" t="n"/>
-      <c r="I32" s="11" t="n"/>
-      <c r="J32" s="7" t="inlineStr">
         <is>
           <t>Not launched yet.</t>
         </is>
@@ -7836,7 +7805,7 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>Aster (SM1D)? site shows 181u for SM1D</t>
+          <t>Aster (SM1D)</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
@@ -9084,18 +9053,18 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Scientex Durian Tunggal 2 (5 licences)</t>
+          <t>Scientex Durian Tunggal 2</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
         <v>44016</v>
       </c>
       <c r="D74" s="9" t="n">
-        <v>1187</v>
+        <v>757</v>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>6575-18,6575-19,6575-20,6575-21,6575-22</t>
+          <t>6575-18,6575-19,6575-21</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr">
@@ -9105,7 +9074,7 @@
       </c>
       <c r="G74" s="10" t="n"/>
       <c r="H74" s="10" t="n">
-        <v>1147</v>
+        <v>730</v>
       </c>
       <c r="I74" s="11">
         <f>H74/$D$74</f>
@@ -11831,28 +11800,28 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>The Ophera</t>
+          <t>Tiara Residences 2</t>
         </is>
       </c>
       <c r="C28" s="8" t="n">
-        <v>45218</v>
+        <v>46274</v>
       </c>
       <c r="D28" s="9" t="n">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>30500-1</t>
+          <t>20171-3</t>
         </is>
       </c>
       <c r="F28" s="7" t="inlineStr">
         <is>
-          <t>SIME DARBY PROPERTY (GOLFHOME) SDN. BHD.</t>
+          <t>SIME DARBY PROPERTY (BUKIT JELUTONG)  SDN. BHD.</t>
         </is>
       </c>
       <c r="G28" s="10" t="n"/>
       <c r="H28" s="10" t="n">
-        <v>134</v>
+        <v>0</v>
       </c>
       <c r="I28" s="11">
         <f>H28/$D$28</f>
@@ -11866,28 +11835,28 @@
       </c>
       <c r="B29" s="7" t="inlineStr">
         <is>
-          <t>Hype Residences (tentative)</t>
+          <t>The Ophera</t>
         </is>
       </c>
       <c r="C29" s="8" t="n">
         <v>45218</v>
       </c>
       <c r="D29" s="9" t="n">
-        <v>961</v>
+        <v>150</v>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>3780-6</t>
+          <t>30500-1</t>
         </is>
       </c>
       <c r="F29" s="7" t="inlineStr">
         <is>
-          <t>SIME DARBY PROPERTY (SJ7) SDN. BHD.</t>
+          <t>SIME DARBY PROPERTY (GOLFHOME) SDN. BHD.</t>
         </is>
       </c>
       <c r="G29" s="10" t="n"/>
       <c r="H29" s="10" t="n">
-        <v>956</v>
+        <v>134</v>
       </c>
       <c r="I29" s="11">
         <f>H29/$D$29</f>
@@ -11905,14 +11874,14 @@
         </is>
       </c>
       <c r="C30" s="8" t="n">
-        <v>46206</v>
+        <v>45218</v>
       </c>
       <c r="D30" s="9" t="n">
-        <v>998</v>
+        <v>961</v>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>3780-7</t>
+          <t>3780-6</t>
         </is>
       </c>
       <c r="F30" s="7" t="inlineStr">
@@ -11922,7 +11891,7 @@
       </c>
       <c r="G30" s="10" t="n"/>
       <c r="H30" s="10" t="n">
-        <v>0</v>
+        <v>956</v>
       </c>
       <c r="I30" s="11">
         <f>H30/$D$30</f>
@@ -11936,28 +11905,28 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>The Glades</t>
+          <t>Hype Residences (tentative)</t>
         </is>
       </c>
       <c r="C31" s="8" t="n">
-        <v>44817</v>
+        <v>46206</v>
       </c>
       <c r="D31" s="9" t="n">
-        <v>122</v>
+        <v>998</v>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>3927-154</t>
+          <t>3780-7</t>
         </is>
       </c>
       <c r="F31" s="7" t="inlineStr">
         <is>
-          <t>SIME DARBY PROPERTY (BUKIT RAJA) SDN. BHD.</t>
+          <t>SIME DARBY PROPERTY (SJ7) SDN. BHD.</t>
         </is>
       </c>
       <c r="G31" s="10" t="n"/>
       <c r="H31" s="10" t="n">
-        <v>122</v>
+        <v>0</v>
       </c>
       <c r="I31" s="11">
         <f>H31/$D$31</f>
@@ -11971,18 +11940,18 @@
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>Serasi Residences</t>
+          <t>The Glades</t>
         </is>
       </c>
       <c r="C32" s="8" t="n">
-        <v>44917</v>
+        <v>44817</v>
       </c>
       <c r="D32" s="9" t="n">
-        <v>1428</v>
+        <v>122</v>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>3927-155</t>
+          <t>3927-154</t>
         </is>
       </c>
       <c r="F32" s="7" t="inlineStr">
@@ -11992,7 +11961,7 @@
       </c>
       <c r="G32" s="10" t="n"/>
       <c r="H32" s="10" t="n">
-        <v>1420</v>
+        <v>122</v>
       </c>
       <c r="I32" s="11">
         <f>H32/$D$32</f>
@@ -12006,18 +11975,18 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>Damayan Residences</t>
+          <t>Serasi Residences</t>
         </is>
       </c>
       <c r="C33" s="8" t="n">
-        <v>45350</v>
+        <v>44917</v>
       </c>
       <c r="D33" s="9" t="n">
-        <v>308</v>
+        <v>1428</v>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>3927-160</t>
+          <t>3927-155</t>
         </is>
       </c>
       <c r="F33" s="7" t="inlineStr">
@@ -12027,7 +11996,7 @@
       </c>
       <c r="G33" s="10" t="n"/>
       <c r="H33" s="10" t="n">
-        <v>166</v>
+        <v>1420</v>
       </c>
       <c r="I33" s="11">
         <f>H33/$D$33</f>
@@ -12041,18 +12010,18 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Adira</t>
+          <t>Damayan Residences</t>
         </is>
       </c>
       <c r="C34" s="8" t="n">
-        <v>45427</v>
+        <v>45350</v>
       </c>
       <c r="D34" s="9" t="n">
-        <v>138</v>
+        <v>308</v>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>3927-161</t>
+          <t>3927-160</t>
         </is>
       </c>
       <c r="F34" s="7" t="inlineStr">
@@ -12062,7 +12031,7 @@
       </c>
       <c r="G34" s="10" t="n"/>
       <c r="H34" s="10" t="n">
-        <v>58</v>
+        <v>166</v>
       </c>
       <c r="I34" s="11">
         <f>H34/$D$34</f>
@@ -12083,11 +12052,11 @@
         <v>45427</v>
       </c>
       <c r="D35" s="9" t="n">
-        <v>82</v>
+        <v>138</v>
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>3927-162</t>
+          <t>3927-161</t>
         </is>
       </c>
       <c r="F35" s="7" t="inlineStr">
@@ -12097,7 +12066,7 @@
       </c>
       <c r="G35" s="10" t="n"/>
       <c r="H35" s="10" t="n">
-        <v>24</v>
+        <v>58</v>
       </c>
       <c r="I35" s="11">
         <f>H35/$D$35</f>
@@ -12118,11 +12087,11 @@
         <v>45427</v>
       </c>
       <c r="D36" s="9" t="n">
-        <v>109</v>
+        <v>82</v>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>3927-163</t>
+          <t>3927-162</t>
         </is>
       </c>
       <c r="F36" s="7" t="inlineStr">
@@ -12132,7 +12101,7 @@
       </c>
       <c r="G36" s="10" t="n"/>
       <c r="H36" s="10" t="n">
-        <v>104</v>
+        <v>24</v>
       </c>
       <c r="I36" s="11">
         <f>H36/$D$36</f>
@@ -12146,18 +12115,18 @@
       </c>
       <c r="B37" s="7" t="inlineStr">
         <is>
-          <t>Lanai Lakeside</t>
+          <t>Adira</t>
         </is>
       </c>
       <c r="C37" s="8" t="n">
-        <v>45624</v>
+        <v>45427</v>
       </c>
       <c r="D37" s="9" t="n">
-        <v>72</v>
+        <v>109</v>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>3927-164</t>
+          <t>3927-163</t>
         </is>
       </c>
       <c r="F37" s="7" t="inlineStr">
@@ -12167,7 +12136,7 @@
       </c>
       <c r="G37" s="10" t="n"/>
       <c r="H37" s="10" t="n">
-        <v>44</v>
+        <v>104</v>
       </c>
       <c r="I37" s="11">
         <f>H37/$D$37</f>
@@ -12181,18 +12150,18 @@
       </c>
       <c r="B38" s="7" t="inlineStr">
         <is>
-          <t>The Straits</t>
+          <t>Lanai Lakeside</t>
         </is>
       </c>
       <c r="C38" s="8" t="n">
-        <v>45946</v>
+        <v>45624</v>
       </c>
       <c r="D38" s="9" t="n">
-        <v>146</v>
+        <v>72</v>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>3927-165</t>
+          <t>3927-164</t>
         </is>
       </c>
       <c r="F38" s="7" t="inlineStr">
@@ -12202,7 +12171,7 @@
       </c>
       <c r="G38" s="10" t="n"/>
       <c r="H38" s="10" t="n">
-        <v>29</v>
+        <v>44</v>
       </c>
       <c r="I38" s="11">
         <f>H38/$D$38</f>
@@ -12216,18 +12185,18 @@
       </c>
       <c r="B39" s="7" t="inlineStr">
         <is>
-          <t>The Glades</t>
+          <t>The Straits</t>
         </is>
       </c>
       <c r="C39" s="8" t="n">
-        <v>45951</v>
+        <v>45946</v>
       </c>
       <c r="D39" s="9" t="n">
-        <v>25</v>
+        <v>146</v>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>3927-166</t>
+          <t>3927-165</t>
         </is>
       </c>
       <c r="F39" s="7" t="inlineStr">
@@ -12237,7 +12206,7 @@
       </c>
       <c r="G39" s="10" t="n"/>
       <c r="H39" s="10" t="n">
-        <v>24</v>
+        <v>29</v>
       </c>
       <c r="I39" s="11">
         <f>H39/$D$39</f>
@@ -12251,18 +12220,18 @@
       </c>
       <c r="B40" s="7" t="inlineStr">
         <is>
-          <t>The Straits</t>
+          <t>The Glades</t>
         </is>
       </c>
       <c r="C40" s="8" t="n">
-        <v>45952</v>
+        <v>45951</v>
       </c>
       <c r="D40" s="9" t="n">
-        <v>142</v>
+        <v>25</v>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>3927-167</t>
+          <t>3927-166</t>
         </is>
       </c>
       <c r="F40" s="7" t="inlineStr">
@@ -12272,7 +12241,7 @@
       </c>
       <c r="G40" s="10" t="n"/>
       <c r="H40" s="10" t="n">
-        <v>106</v>
+        <v>24</v>
       </c>
       <c r="I40" s="11">
         <f>H40/$D$40</f>
@@ -12286,28 +12255,28 @@
       </c>
       <c r="B41" s="7" t="inlineStr">
         <is>
-          <t>Park One</t>
+          <t>The Straits</t>
         </is>
       </c>
       <c r="C41" s="8" t="n">
-        <v>44841</v>
+        <v>45952</v>
       </c>
       <c r="D41" s="9" t="n">
-        <v>234</v>
+        <v>142</v>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>597-13</t>
+          <t>3927-167</t>
         </is>
       </c>
       <c r="F41" s="7" t="inlineStr">
         <is>
-          <t>SIME DARBY PROPERTY (KL EAST) SDN. BHD.</t>
+          <t>SIME DARBY PROPERTY (BUKIT RAJA) SDN. BHD.</t>
         </is>
       </c>
       <c r="G41" s="10" t="n"/>
       <c r="H41" s="10" t="n">
-        <v>228</v>
+        <v>106</v>
       </c>
       <c r="I41" s="11">
         <f>H41/$D$41</f>
@@ -12321,28 +12290,28 @@
       </c>
       <c r="B42" s="7" t="inlineStr">
         <is>
-          <t>Emilia Lakeside 1</t>
+          <t>Park One</t>
         </is>
       </c>
       <c r="C42" s="8" t="n">
-        <v>45586</v>
+        <v>44841</v>
       </c>
       <c r="D42" s="9" t="n">
-        <v>100</v>
+        <v>234</v>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>6755-11</t>
+          <t>597-13</t>
         </is>
       </c>
       <c r="F42" s="7" t="inlineStr">
         <is>
-          <t>SIME DARBY PROPERTY (NILAI) SDN. BHD.</t>
+          <t>SIME DARBY PROPERTY (KL EAST) SDN. BHD.</t>
         </is>
       </c>
       <c r="G42" s="10" t="n"/>
       <c r="H42" s="10" t="n">
-        <v>84</v>
+        <v>228</v>
       </c>
       <c r="I42" s="11">
         <f>H42/$D$42</f>
@@ -12356,18 +12325,18 @@
       </c>
       <c r="B43" s="7" t="inlineStr">
         <is>
-          <t>Emilia Lakeside 3</t>
+          <t>Emilia Lakeside 1</t>
         </is>
       </c>
       <c r="C43" s="8" t="n">
-        <v>45694</v>
+        <v>45586</v>
       </c>
       <c r="D43" s="9" t="n">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>6755-12</t>
+          <t>6755-11</t>
         </is>
       </c>
       <c r="F43" s="7" t="inlineStr">
@@ -12377,7 +12346,7 @@
       </c>
       <c r="G43" s="10" t="n"/>
       <c r="H43" s="10" t="n">
-        <v>34</v>
+        <v>84</v>
       </c>
       <c r="I43" s="11">
         <f>H43/$D$43</f>
@@ -12391,18 +12360,18 @@
       </c>
       <c r="B44" s="7" t="inlineStr">
         <is>
-          <t>Emilia Lakeside 2</t>
+          <t>Emilia Lakeside 3</t>
         </is>
       </c>
       <c r="C44" s="8" t="n">
-        <v>45743</v>
+        <v>45694</v>
       </c>
       <c r="D44" s="9" t="n">
-        <v>65</v>
+        <v>45</v>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>6755-13</t>
+          <t>6755-12</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -12412,7 +12381,7 @@
       </c>
       <c r="G44" s="10" t="n"/>
       <c r="H44" s="10" t="n">
-        <v>50</v>
+        <v>34</v>
       </c>
       <c r="I44" s="11">
         <f>H44/$D$44</f>
@@ -12426,28 +12395,28 @@
       </c>
       <c r="B45" s="7" t="inlineStr">
         <is>
-          <t>Serenia Amalia 5</t>
+          <t>Emilia Lakeside 2</t>
         </is>
       </c>
       <c r="C45" s="8" t="n">
-        <v>45191</v>
+        <v>45743</v>
       </c>
       <c r="D45" s="9" t="n">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>6785-27</t>
+          <t>6755-13</t>
         </is>
       </c>
       <c r="F45" s="7" t="inlineStr">
         <is>
-          <t>SIME DARBY PROPERTY (SERENIA CITY) SDN. BHD.</t>
+          <t>SIME DARBY PROPERTY (NILAI) SDN. BHD.</t>
         </is>
       </c>
       <c r="G45" s="10" t="n"/>
       <c r="H45" s="10" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="I45" s="11">
         <f>H45/$D$45</f>
@@ -12461,18 +12430,18 @@
       </c>
       <c r="B46" s="7" t="inlineStr">
         <is>
-          <t>Serenia Amalia 7</t>
+          <t>Serenia Amalia 5</t>
         </is>
       </c>
       <c r="C46" s="8" t="n">
-        <v>45595</v>
+        <v>45191</v>
       </c>
       <c r="D46" s="9" t="n">
-        <v>40</v>
+        <v>68</v>
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>6785-28</t>
+          <t>6785-27</t>
         </is>
       </c>
       <c r="F46" s="7" t="inlineStr">
@@ -12482,7 +12451,7 @@
       </c>
       <c r="G46" s="10" t="n"/>
       <c r="H46" s="10" t="n">
-        <v>32</v>
+        <v>55</v>
       </c>
       <c r="I46" s="11">
         <f>H46/$D$46</f>
@@ -12496,18 +12465,18 @@
       </c>
       <c r="B47" s="7" t="inlineStr">
         <is>
-          <t>Serenia Amalia 6</t>
+          <t>Serenia Amalia 7</t>
         </is>
       </c>
       <c r="C47" s="8" t="n">
-        <v>45790</v>
+        <v>45595</v>
       </c>
       <c r="D47" s="9" t="n">
-        <v>84</v>
+        <v>40</v>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>6785-29</t>
+          <t>6785-28</t>
         </is>
       </c>
       <c r="F47" s="7" t="inlineStr">
@@ -12517,7 +12486,7 @@
       </c>
       <c r="G47" s="10" t="n"/>
       <c r="H47" s="10" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="I47" s="11">
         <f>H47/$D$47</f>
@@ -12531,18 +12500,18 @@
       </c>
       <c r="B48" s="7" t="inlineStr">
         <is>
-          <t>Serenia Baleria 1</t>
+          <t>Serenia Amalia 6</t>
         </is>
       </c>
       <c r="C48" s="8" t="n">
-        <v>45798</v>
+        <v>45790</v>
       </c>
       <c r="D48" s="9" t="n">
-        <v>211</v>
+        <v>84</v>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>6785-30</t>
+          <t>6785-29</t>
         </is>
       </c>
       <c r="F48" s="7" t="inlineStr">
@@ -12552,7 +12521,7 @@
       </c>
       <c r="G48" s="10" t="n"/>
       <c r="H48" s="10" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="I48" s="11">
         <f>H48/$D$48</f>
@@ -12566,18 +12535,18 @@
       </c>
       <c r="B49" s="7" t="inlineStr">
         <is>
-          <t>Serenia Baleria 2</t>
+          <t>Serenia Baleria 1</t>
         </is>
       </c>
       <c r="C49" s="8" t="n">
-        <v>45820</v>
+        <v>45798</v>
       </c>
       <c r="D49" s="9" t="n">
-        <v>174</v>
+        <v>211</v>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>6785-31</t>
+          <t>6785-30</t>
         </is>
       </c>
       <c r="F49" s="7" t="inlineStr">
@@ -12587,7 +12556,7 @@
       </c>
       <c r="G49" s="10" t="n"/>
       <c r="H49" s="10" t="n">
-        <v>27</v>
+        <v>160</v>
       </c>
       <c r="I49" s="11">
         <f>H49/$D$49</f>
@@ -12601,28 +12570,28 @@
       </c>
       <c r="B50" s="7" t="inlineStr">
         <is>
-          <t>Triara Residences</t>
+          <t>Serenia Baleria 2</t>
         </is>
       </c>
       <c r="C50" s="8" t="n">
-        <v>45114</v>
+        <v>45820</v>
       </c>
       <c r="D50" s="9" t="n">
-        <v>450</v>
+        <v>174</v>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>7277-27</t>
+          <t>6785-31</t>
         </is>
       </c>
       <c r="F50" s="7" t="inlineStr">
         <is>
-          <t>SIME DARBY PROPERTY (ARA DAMANSARA)  SDN. BHD.</t>
+          <t>SIME DARBY PROPERTY (SERENIA CITY) SDN. BHD.</t>
         </is>
       </c>
       <c r="G50" s="10" t="n"/>
       <c r="H50" s="10" t="n">
-        <v>436</v>
+        <v>27</v>
       </c>
       <c r="I50" s="11">
         <f>H50/$D$50</f>
@@ -12636,18 +12605,18 @@
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>Andara</t>
+          <t>Triara Residences</t>
         </is>
       </c>
       <c r="C51" s="8" t="n">
-        <v>45722</v>
+        <v>45114</v>
       </c>
       <c r="D51" s="9" t="n">
-        <v>20</v>
+        <v>450</v>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>7277-28</t>
+          <t>7277-27</t>
         </is>
       </c>
       <c r="F51" s="7" t="inlineStr">
@@ -12657,7 +12626,7 @@
       </c>
       <c r="G51" s="10" t="n"/>
       <c r="H51" s="10" t="n">
-        <v>18</v>
+        <v>436</v>
       </c>
       <c r="I51" s="11">
         <f>H51/$D$51</f>
@@ -12671,28 +12640,28 @@
       </c>
       <c r="B52" s="7" t="inlineStr">
         <is>
-          <t>Nadira 3</t>
+          <t>Andara</t>
         </is>
       </c>
       <c r="C52" s="8" t="n">
-        <v>45000</v>
+        <v>45722</v>
       </c>
       <c r="D52" s="9" t="n">
-        <v>139</v>
+        <v>20</v>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>3927-156</t>
+          <t>7277-28</t>
         </is>
       </c>
       <c r="F52" s="7" t="inlineStr">
         <is>
-          <t>SIME DARBY PROPERTY (BUKIT RAJA) SDN. BHD.</t>
+          <t>SIME DARBY PROPERTY (ARA DAMANSARA)  SDN. BHD.</t>
         </is>
       </c>
       <c r="G52" s="10" t="n"/>
       <c r="H52" s="10" t="n">
-        <v>128</v>
+        <v>18</v>
       </c>
       <c r="I52" s="11">
         <f>H52/$D$52</f>
@@ -12706,18 +12675,18 @@
       </c>
       <c r="B53" s="7" t="inlineStr">
         <is>
-          <t>Casira 3</t>
+          <t>Nadira 3</t>
         </is>
       </c>
       <c r="C53" s="8" t="n">
-        <v>45029</v>
+        <v>45000</v>
       </c>
       <c r="D53" s="9" t="n">
-        <v>346</v>
+        <v>139</v>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>3927-157,3927-158,3927-159</t>
+          <t>3927-156</t>
         </is>
       </c>
       <c r="F53" s="7" t="inlineStr">
@@ -12727,7 +12696,7 @@
       </c>
       <c r="G53" s="10" t="n"/>
       <c r="H53" s="10" t="n">
-        <v>300</v>
+        <v>128</v>
       </c>
       <c r="I53" s="11">
         <f>H53/$D$53</f>
@@ -12741,23 +12710,34 @@
       </c>
       <c r="B54" s="7" t="inlineStr">
         <is>
-          <t>Seroja Gardens</t>
-        </is>
-      </c>
-      <c r="C54" s="8" t="n"/>
+          <t>Casira 3</t>
+        </is>
+      </c>
+      <c r="C54" s="8" t="n">
+        <v>45029</v>
+      </c>
       <c r="D54" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="6" t="inlineStr"/>
-      <c r="F54" s="7" t="inlineStr"/>
+        <v>346</v>
+      </c>
+      <c r="E54" s="6" t="inlineStr">
+        <is>
+          <t>3927-157,3927-158,3927-159</t>
+        </is>
+      </c>
+      <c r="F54" s="7" t="inlineStr">
+        <is>
+          <t>SIME DARBY PROPERTY (BUKIT RAJA) SDN. BHD.</t>
+        </is>
+      </c>
       <c r="G54" s="10" t="n"/>
-      <c r="H54" s="10" t="n"/>
-      <c r="I54" s="11" t="n"/>
-      <c r="J54" s="7" t="inlineStr">
-        <is>
-          <t>Not launched yet.</t>
-        </is>
-      </c>
+      <c r="H54" s="10" t="n">
+        <v>300</v>
+      </c>
+      <c r="I54" s="11">
+        <f>H54/$D$54</f>
+        <v/>
+      </c>
+      <c r="J54" s="7" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="n">
@@ -12765,34 +12745,23 @@
       </c>
       <c r="B55" s="7" t="inlineStr">
         <is>
-          <t>Emilia</t>
-        </is>
-      </c>
-      <c r="C55" s="8" t="n">
-        <v>44979</v>
-      </c>
+          <t>Seroja Gardens</t>
+        </is>
+      </c>
+      <c r="C55" s="8" t="n"/>
       <c r="D55" s="9" t="n">
-        <v>24</v>
-      </c>
-      <c r="E55" s="6" t="inlineStr">
-        <is>
-          <t>6755-7,6755-9</t>
-        </is>
-      </c>
-      <c r="F55" s="7" t="inlineStr">
-        <is>
-          <t>SIME DARBY PROPERTY (NILAI) SDN. BHD.</t>
-        </is>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E55" s="6" t="inlineStr"/>
+      <c r="F55" s="7" t="inlineStr"/>
       <c r="G55" s="10" t="n"/>
-      <c r="H55" s="10" t="n">
-        <v>80</v>
-      </c>
-      <c r="I55" s="11">
-        <f>H55/$D$55</f>
-        <v/>
-      </c>
-      <c r="J55" s="7" t="inlineStr"/>
+      <c r="H55" s="10" t="n"/>
+      <c r="I55" s="11" t="n"/>
+      <c r="J55" s="7" t="inlineStr">
+        <is>
+          <t>Not launched yet.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="6" t="n">
@@ -12800,24 +12769,28 @@
       </c>
       <c r="B56" s="7" t="inlineStr">
         <is>
-          <t>Ara Bloc</t>
+          <t>Emilia</t>
         </is>
       </c>
       <c r="C56" s="8" t="n">
-        <v>46126</v>
+        <v>44979</v>
       </c>
       <c r="D56" s="9" t="n">
-        <v>998</v>
+        <v>24</v>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>7277-30</t>
-        </is>
-      </c>
-      <c r="F56" s="7" t="inlineStr"/>
+          <t>6755-7,6755-9</t>
+        </is>
+      </c>
+      <c r="F56" s="7" t="inlineStr">
+        <is>
+          <t>SIME DARBY PROPERTY (NILAI) SDN. BHD.</t>
+        </is>
+      </c>
       <c r="G56" s="10" t="n"/>
       <c r="H56" s="10" t="n">
-        <v>157</v>
+        <v>80</v>
       </c>
       <c r="I56" s="11">
         <f>H56/$D$56</f>
@@ -12831,28 +12804,24 @@
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>Senada Residences</t>
+          <t>Ara Bloc</t>
         </is>
       </c>
       <c r="C57" s="8" t="n">
-        <v>42510</v>
+        <v>46126</v>
       </c>
       <c r="D57" s="9" t="n">
-        <v>429</v>
+        <v>998</v>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>14350-1</t>
-        </is>
-      </c>
-      <c r="F57" s="7" t="inlineStr">
-        <is>
-          <t>SIME DARBY PROPERTY (SENADA) SDN. BHD.</t>
-        </is>
-      </c>
+          <t>7277-30</t>
+        </is>
+      </c>
+      <c r="F57" s="7" t="inlineStr"/>
       <c r="G57" s="10" t="n"/>
       <c r="H57" s="10" t="n">
-        <v>275</v>
+        <v>157</v>
       </c>
       <c r="I57" s="11">
         <f>H57/$D$57</f>
@@ -12866,24 +12835,28 @@
       </c>
       <c r="B58" s="7" t="inlineStr">
         <is>
-          <t>Elmina Green (Eg1A)</t>
+          <t>Senada Residences</t>
         </is>
       </c>
       <c r="C58" s="8" t="n">
-        <v>43005</v>
+        <v>42510</v>
       </c>
       <c r="D58" s="9" t="n">
-        <v>187</v>
+        <v>429</v>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>13017-19</t>
-        </is>
-      </c>
-      <c r="F58" s="7" t="inlineStr"/>
+          <t>14350-1</t>
+        </is>
+      </c>
+      <c r="F58" s="7" t="inlineStr">
+        <is>
+          <t>SIME DARBY PROPERTY (SENADA) SDN. BHD.</t>
+        </is>
+      </c>
       <c r="G58" s="10" t="n"/>
       <c r="H58" s="10" t="n">
-        <v>183</v>
+        <v>275</v>
       </c>
       <c r="I58" s="11">
         <f>H58/$D$58</f>
@@ -12897,24 +12870,24 @@
       </c>
       <c r="B59" s="7" t="inlineStr">
         <is>
-          <t>Elmina Green (Eg1B)</t>
+          <t>Elmina Green (Eg1A)</t>
         </is>
       </c>
       <c r="C59" s="8" t="n">
-        <v>43021</v>
+        <v>43005</v>
       </c>
       <c r="D59" s="9" t="n">
-        <v>211</v>
+        <v>187</v>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>13017-20</t>
+          <t>13017-19</t>
         </is>
       </c>
       <c r="F59" s="7" t="inlineStr"/>
       <c r="G59" s="10" t="n"/>
       <c r="H59" s="10" t="n">
-        <v>205</v>
+        <v>183</v>
       </c>
       <c r="I59" s="11">
         <f>H59/$D$59</f>
@@ -12928,24 +12901,24 @@
       </c>
       <c r="B60" s="7" t="inlineStr">
         <is>
-          <t>Elmina East - (Phase G3C)</t>
+          <t>Elmina Green (Eg1B)</t>
         </is>
       </c>
       <c r="C60" s="8" t="n">
-        <v>43035</v>
+        <v>43021</v>
       </c>
       <c r="D60" s="9" t="n">
-        <v>72</v>
+        <v>211</v>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>13017-21</t>
+          <t>13017-20</t>
         </is>
       </c>
       <c r="F60" s="7" t="inlineStr"/>
       <c r="G60" s="10" t="n"/>
       <c r="H60" s="10" t="n">
-        <v>72</v>
+        <v>205</v>
       </c>
       <c r="I60" s="11">
         <f>H60/$D$60</f>
@@ -12959,24 +12932,24 @@
       </c>
       <c r="B61" s="7" t="inlineStr">
         <is>
-          <t>Phase Eg1C</t>
+          <t>Elmina East - (Phase G3C)</t>
         </is>
       </c>
       <c r="C61" s="8" t="n">
-        <v>43349</v>
+        <v>43035</v>
       </c>
       <c r="D61" s="9" t="n">
-        <v>181</v>
+        <v>72</v>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>13017-22</t>
+          <t>13017-21</t>
         </is>
       </c>
       <c r="F61" s="7" t="inlineStr"/>
       <c r="G61" s="10" t="n"/>
       <c r="H61" s="10" t="n">
-        <v>181</v>
+        <v>72</v>
       </c>
       <c r="I61" s="11">
         <f>H61/$D$61</f>
@@ -12990,24 +12963,24 @@
       </c>
       <c r="B62" s="7" t="inlineStr">
         <is>
-          <t>Phase G5</t>
+          <t>Phase Eg1C</t>
         </is>
       </c>
       <c r="C62" s="8" t="n">
-        <v>43439</v>
+        <v>43349</v>
       </c>
       <c r="D62" s="9" t="n">
-        <v>90</v>
+        <v>181</v>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>13017-23</t>
+          <t>13017-22</t>
         </is>
       </c>
       <c r="F62" s="7" t="inlineStr"/>
       <c r="G62" s="10" t="n"/>
       <c r="H62" s="10" t="n">
-        <v>47</v>
+        <v>181</v>
       </c>
       <c r="I62" s="11">
         <f>H62/$D$62</f>
@@ -13021,24 +12994,24 @@
       </c>
       <c r="B63" s="7" t="inlineStr">
         <is>
-          <t>Phase Eg2 (Rumah Selangorku)</t>
+          <t>Phase G5</t>
         </is>
       </c>
       <c r="C63" s="8" t="n">
-        <v>43539</v>
+        <v>43439</v>
       </c>
       <c r="D63" s="9" t="n">
-        <v>562</v>
+        <v>90</v>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>13017-24</t>
+          <t>13017-23</t>
         </is>
       </c>
       <c r="F63" s="7" t="inlineStr"/>
       <c r="G63" s="10" t="n"/>
       <c r="H63" s="10" t="n">
-        <v>348</v>
+        <v>47</v>
       </c>
       <c r="I63" s="11">
         <f>H63/$D$63</f>
@@ -13052,24 +13025,24 @@
       </c>
       <c r="B64" s="7" t="inlineStr">
         <is>
-          <t>Phase Ev5A</t>
+          <t>Phase Eg2 (Rumah Selangorku)</t>
         </is>
       </c>
       <c r="C64" s="8" t="n">
-        <v>43540</v>
+        <v>43539</v>
       </c>
       <c r="D64" s="9" t="n">
-        <v>168</v>
+        <v>562</v>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>13017-25</t>
+          <t>13017-24</t>
         </is>
       </c>
       <c r="F64" s="7" t="inlineStr"/>
       <c r="G64" s="10" t="n"/>
       <c r="H64" s="10" t="n">
-        <v>168</v>
+        <v>348</v>
       </c>
       <c r="I64" s="11">
         <f>H64/$D$64</f>
@@ -13083,24 +13056,24 @@
       </c>
       <c r="B65" s="7" t="inlineStr">
         <is>
-          <t>Phase Ev5B</t>
+          <t>Phase Ev5A</t>
         </is>
       </c>
       <c r="C65" s="8" t="n">
-        <v>43544</v>
+        <v>43540</v>
       </c>
       <c r="D65" s="9" t="n">
-        <v>205</v>
+        <v>168</v>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>13017-26</t>
+          <t>13017-25</t>
         </is>
       </c>
       <c r="F65" s="7" t="inlineStr"/>
       <c r="G65" s="10" t="n"/>
       <c r="H65" s="10" t="n">
-        <v>204</v>
+        <v>168</v>
       </c>
       <c r="I65" s="11">
         <f>H65/$D$65</f>
@@ -13114,24 +13087,24 @@
       </c>
       <c r="B66" s="7" t="inlineStr">
         <is>
-          <t>Elmina Ilham</t>
+          <t>Phase Ev5B</t>
         </is>
       </c>
       <c r="C66" s="8" t="n">
-        <v>43861</v>
+        <v>43544</v>
       </c>
       <c r="D66" s="9" t="n">
-        <v>513</v>
+        <v>205</v>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>13017-27</t>
+          <t>13017-26</t>
         </is>
       </c>
       <c r="F66" s="7" t="inlineStr"/>
       <c r="G66" s="10" t="n"/>
       <c r="H66" s="10" t="n">
-        <v>300</v>
+        <v>204</v>
       </c>
       <c r="I66" s="11">
         <f>H66/$D$66</f>
@@ -13145,24 +13118,24 @@
       </c>
       <c r="B67" s="7" t="inlineStr">
         <is>
-          <t>Elmina Hijauan Dua (Fasa A)</t>
+          <t>Elmina Ilham</t>
         </is>
       </c>
       <c r="C67" s="8" t="n">
-        <v>43867</v>
+        <v>43861</v>
       </c>
       <c r="D67" s="9" t="n">
-        <v>218</v>
+        <v>513</v>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>13017-28</t>
+          <t>13017-27</t>
         </is>
       </c>
       <c r="F67" s="7" t="inlineStr"/>
       <c r="G67" s="10" t="n"/>
       <c r="H67" s="10" t="n">
-        <v>49</v>
+        <v>300</v>
       </c>
       <c r="I67" s="11">
         <f>H67/$D$67</f>
@@ -13176,24 +13149,24 @@
       </c>
       <c r="B68" s="7" t="inlineStr">
         <is>
-          <t>Elmina Hijauan Dua (Fasa B)</t>
+          <t>Elmina Hijauan Dua (Fasa A)</t>
         </is>
       </c>
       <c r="C68" s="8" t="n">
-        <v>43880</v>
+        <v>43867</v>
       </c>
       <c r="D68" s="9" t="n">
-        <v>194</v>
+        <v>218</v>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>13017-29</t>
+          <t>13017-28</t>
         </is>
       </c>
       <c r="F68" s="7" t="inlineStr"/>
       <c r="G68" s="10" t="n"/>
       <c r="H68" s="10" t="n">
-        <v>31</v>
+        <v>49</v>
       </c>
       <c r="I68" s="11">
         <f>H68/$D$68</f>
@@ -13207,24 +13180,24 @@
       </c>
       <c r="B69" s="7" t="inlineStr">
         <is>
-          <t>Hevea (Fasa B)</t>
+          <t>Elmina Hijauan Dua (Fasa B)</t>
         </is>
       </c>
       <c r="C69" s="8" t="n">
-        <v>44183</v>
+        <v>43880</v>
       </c>
       <c r="D69" s="9" t="n">
-        <v>57</v>
+        <v>194</v>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>13017-30</t>
+          <t>13017-29</t>
         </is>
       </c>
       <c r="F69" s="7" t="inlineStr"/>
       <c r="G69" s="10" t="n"/>
       <c r="H69" s="10" t="n">
-        <v>14</v>
+        <v>31</v>
       </c>
       <c r="I69" s="11">
         <f>H69/$D$69</f>
@@ -13238,24 +13211,24 @@
       </c>
       <c r="B70" s="7" t="inlineStr">
         <is>
-          <t>Hevea (Fasa A)</t>
+          <t>Hevea (Fasa B)</t>
         </is>
       </c>
       <c r="C70" s="8" t="n">
-        <v>44184</v>
+        <v>44183</v>
       </c>
       <c r="D70" s="9" t="n">
-        <v>69</v>
+        <v>57</v>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>13017-31</t>
+          <t>13017-30</t>
         </is>
       </c>
       <c r="F70" s="7" t="inlineStr"/>
       <c r="G70" s="10" t="n"/>
       <c r="H70" s="10" t="n">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="I70" s="11">
         <f>H70/$D$70</f>
@@ -13269,24 +13242,24 @@
       </c>
       <c r="B71" s="7" t="inlineStr">
         <is>
-          <t>Elmina Hijauan Empat (Fasa A)</t>
+          <t>Hevea (Fasa A)</t>
         </is>
       </c>
       <c r="C71" s="8" t="n">
-        <v>44257</v>
+        <v>44184</v>
       </c>
       <c r="D71" s="9" t="n">
-        <v>189</v>
+        <v>69</v>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>13017-32</t>
+          <t>13017-31</t>
         </is>
       </c>
       <c r="F71" s="7" t="inlineStr"/>
       <c r="G71" s="10" t="n"/>
       <c r="H71" s="10" t="n">
-        <v>1</v>
+        <v>66</v>
       </c>
       <c r="I71" s="11">
         <f>H71/$D$71</f>
@@ -13300,24 +13273,24 @@
       </c>
       <c r="B72" s="7" t="inlineStr">
         <is>
-          <t>Elmina Hijauan Empat (Fasa B)</t>
+          <t>Elmina Hijauan Empat (Fasa A)</t>
         </is>
       </c>
       <c r="C72" s="8" t="n">
-        <v>44256</v>
+        <v>44257</v>
       </c>
       <c r="D72" s="9" t="n">
-        <v>160</v>
+        <v>189</v>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>13017-33</t>
+          <t>13017-32</t>
         </is>
       </c>
       <c r="F72" s="7" t="inlineStr"/>
       <c r="G72" s="10" t="n"/>
       <c r="H72" s="10" t="n">
-        <v>16</v>
+        <v>1</v>
       </c>
       <c r="I72" s="11">
         <f>H72/$D$72</f>
@@ -13331,24 +13304,24 @@
       </c>
       <c r="B73" s="7" t="inlineStr">
         <is>
-          <t>Elmina Hijauan Lima</t>
+          <t>Elmina Hijauan Empat (Fasa B)</t>
         </is>
       </c>
       <c r="C73" s="8" t="n">
-        <v>44428</v>
+        <v>44256</v>
       </c>
       <c r="D73" s="9" t="n">
-        <v>208</v>
+        <v>160</v>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>13017-34</t>
+          <t>13017-33</t>
         </is>
       </c>
       <c r="F73" s="7" t="inlineStr"/>
       <c r="G73" s="10" t="n"/>
       <c r="H73" s="10" t="n">
-        <v>117</v>
+        <v>16</v>
       </c>
       <c r="I73" s="11">
         <f>H73/$D$73</f>
@@ -13362,24 +13335,24 @@
       </c>
       <c r="B74" s="7" t="inlineStr">
         <is>
-          <t>Ilham Residence 2</t>
+          <t>Elmina Hijauan Lima</t>
         </is>
       </c>
       <c r="C74" s="8" t="n">
-        <v>44638</v>
+        <v>44428</v>
       </c>
       <c r="D74" s="9" t="n">
-        <v>277</v>
+        <v>208</v>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>13017-35</t>
+          <t>13017-34</t>
         </is>
       </c>
       <c r="F74" s="7" t="inlineStr"/>
       <c r="G74" s="10" t="n"/>
       <c r="H74" s="10" t="n">
-        <v>277</v>
+        <v>117</v>
       </c>
       <c r="I74" s="11">
         <f>H74/$D$74</f>
@@ -13393,24 +13366,24 @@
       </c>
       <c r="B75" s="7" t="inlineStr">
         <is>
-          <t>Elmina Hijauan Enam (Fasa A)</t>
+          <t>Ilham Residence 2</t>
         </is>
       </c>
       <c r="C75" s="8" t="n">
-        <v>44705</v>
+        <v>44638</v>
       </c>
       <c r="D75" s="9" t="n">
-        <v>116</v>
+        <v>277</v>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>13017-36</t>
+          <t>13017-35</t>
         </is>
       </c>
       <c r="F75" s="7" t="inlineStr"/>
       <c r="G75" s="10" t="n"/>
       <c r="H75" s="10" t="n">
-        <v>113</v>
+        <v>277</v>
       </c>
       <c r="I75" s="11">
         <f>H75/$D$75</f>
@@ -13424,24 +13397,24 @@
       </c>
       <c r="B76" s="7" t="inlineStr">
         <is>
-          <t>Elmina Hijauan Enam (Fasa B)</t>
+          <t>Elmina Hijauan Enam (Fasa A)</t>
         </is>
       </c>
       <c r="C76" s="8" t="n">
-        <v>44767</v>
+        <v>44705</v>
       </c>
       <c r="D76" s="9" t="n">
-        <v>139</v>
+        <v>116</v>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>13017-37</t>
+          <t>13017-36</t>
         </is>
       </c>
       <c r="F76" s="7" t="inlineStr"/>
       <c r="G76" s="10" t="n"/>
       <c r="H76" s="10" t="n">
-        <v>138</v>
+        <v>113</v>
       </c>
       <c r="I76" s="11">
         <f>H76/$D$76</f>
@@ -13455,24 +13428,24 @@
       </c>
       <c r="B77" s="7" t="inlineStr">
         <is>
-          <t>Elmina Hijauan Tujuh (Fasa B)</t>
+          <t>Elmina Hijauan Enam (Fasa B)</t>
         </is>
       </c>
       <c r="C77" s="8" t="n">
-        <v>44854</v>
+        <v>44767</v>
       </c>
       <c r="D77" s="9" t="n">
-        <v>185</v>
+        <v>139</v>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>13017-38</t>
+          <t>13017-37</t>
         </is>
       </c>
       <c r="F77" s="7" t="inlineStr"/>
       <c r="G77" s="10" t="n"/>
       <c r="H77" s="10" t="n">
-        <v>180</v>
+        <v>138</v>
       </c>
       <c r="I77" s="11">
         <f>H77/$D$77</f>
@@ -13486,24 +13459,24 @@
       </c>
       <c r="B78" s="7" t="inlineStr">
         <is>
-          <t>Elmina Hijauan Tujuh (Fasa A)</t>
+          <t>Elmina Hijauan Tujuh (Fasa B)</t>
         </is>
       </c>
       <c r="C78" s="8" t="n">
         <v>44854</v>
       </c>
       <c r="D78" s="9" t="n">
-        <v>131</v>
+        <v>185</v>
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>13017-39</t>
+          <t>13017-38</t>
         </is>
       </c>
       <c r="F78" s="7" t="inlineStr"/>
       <c r="G78" s="10" t="n"/>
       <c r="H78" s="10" t="n">
-        <v>130</v>
+        <v>180</v>
       </c>
       <c r="I78" s="11">
         <f>H78/$D$78</f>
@@ -13517,24 +13490,24 @@
       </c>
       <c r="B79" s="7" t="inlineStr">
         <is>
-          <t>Elmina Ilham Tiga</t>
+          <t>Elmina Hijauan Tujuh (Fasa A)</t>
         </is>
       </c>
       <c r="C79" s="8" t="n">
-        <v>44998</v>
+        <v>44854</v>
       </c>
       <c r="D79" s="9" t="n">
-        <v>303</v>
+        <v>131</v>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>13017-40</t>
+          <t>13017-39</t>
         </is>
       </c>
       <c r="F79" s="7" t="inlineStr"/>
       <c r="G79" s="10" t="n"/>
       <c r="H79" s="10" t="n">
-        <v>302</v>
+        <v>130</v>
       </c>
       <c r="I79" s="11">
         <f>H79/$D$79</f>
@@ -13548,24 +13521,24 @@
       </c>
       <c r="B80" s="7" t="inlineStr">
         <is>
-          <t>Elmina Hijauan Lapan (Fasa B)</t>
+          <t>Elmina Ilham Tiga</t>
         </is>
       </c>
       <c r="C80" s="8" t="n">
-        <v>45006</v>
+        <v>44998</v>
       </c>
       <c r="D80" s="9" t="n">
-        <v>80</v>
+        <v>303</v>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>13017-41</t>
+          <t>13017-40</t>
         </is>
       </c>
       <c r="F80" s="7" t="inlineStr"/>
       <c r="G80" s="10" t="n"/>
       <c r="H80" s="10" t="n">
-        <v>79</v>
+        <v>302</v>
       </c>
       <c r="I80" s="11">
         <f>H80/$D$80</f>
@@ -13579,24 +13552,24 @@
       </c>
       <c r="B81" s="7" t="inlineStr">
         <is>
-          <t>Elmina Hijauan Lapan (Fasa A)</t>
+          <t>Elmina Hijauan Lapan (Fasa B)</t>
         </is>
       </c>
       <c r="C81" s="8" t="n">
-        <v>45018</v>
+        <v>45006</v>
       </c>
       <c r="D81" s="9" t="n">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>13017-42</t>
+          <t>13017-41</t>
         </is>
       </c>
       <c r="F81" s="7" t="inlineStr"/>
       <c r="G81" s="10" t="n"/>
       <c r="H81" s="10" t="n">
-        <v>88</v>
+        <v>79</v>
       </c>
       <c r="I81" s="11">
         <f>H81/$D$81</f>
@@ -13610,24 +13583,24 @@
       </c>
       <c r="B82" s="7" t="inlineStr">
         <is>
-          <t>Embun</t>
+          <t>Elmina Hijauan Lapan (Fasa A)</t>
         </is>
       </c>
       <c r="C82" s="8" t="n">
-        <v>43823</v>
+        <v>45018</v>
       </c>
       <c r="D82" s="9" t="n">
-        <v>189</v>
+        <v>88</v>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>12408-11</t>
+          <t>13017-42</t>
         </is>
       </c>
       <c r="F82" s="7" t="inlineStr"/>
       <c r="G82" s="10" t="n"/>
       <c r="H82" s="10" t="n">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="I82" s="11">
         <f>H82/$D$82</f>
@@ -13641,24 +13614,24 @@
       </c>
       <c r="B83" s="7" t="inlineStr">
         <is>
-          <t>Anggun (Fasa 1)</t>
+          <t>Embun</t>
         </is>
       </c>
       <c r="C83" s="8" t="n">
-        <v>44328</v>
+        <v>43823</v>
       </c>
       <c r="D83" s="9" t="n">
-        <v>59</v>
+        <v>189</v>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>12408-12</t>
+          <t>12408-11</t>
         </is>
       </c>
       <c r="F83" s="7" t="inlineStr"/>
       <c r="G83" s="10" t="n"/>
       <c r="H83" s="10" t="n">
-        <v>12</v>
+        <v>125</v>
       </c>
       <c r="I83" s="11">
         <f>H83/$D$83</f>
@@ -13672,24 +13645,24 @@
       </c>
       <c r="B84" s="7" t="inlineStr">
         <is>
-          <t>Anggun (Fasa 2)</t>
+          <t>Anggun (Fasa 1)</t>
         </is>
       </c>
       <c r="C84" s="8" t="n">
-        <v>44393</v>
+        <v>44328</v>
       </c>
       <c r="D84" s="9" t="n">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>12408-13</t>
+          <t>12408-12</t>
         </is>
       </c>
       <c r="F84" s="7" t="inlineStr"/>
       <c r="G84" s="10" t="n"/>
       <c r="H84" s="10" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="I84" s="11">
         <f>H84/$D$84</f>
@@ -13703,24 +13676,24 @@
       </c>
       <c r="B85" s="7" t="inlineStr">
         <is>
-          <t>Suasana Ainsdale (Fasa 1)</t>
+          <t>Anggun (Fasa 2)</t>
         </is>
       </c>
       <c r="C85" s="8" t="n">
-        <v>44932</v>
+        <v>44393</v>
       </c>
       <c r="D85" s="9" t="n">
-        <v>50</v>
+        <v>86</v>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>12408-14</t>
+          <t>12408-13</t>
         </is>
       </c>
       <c r="F85" s="7" t="inlineStr"/>
       <c r="G85" s="10" t="n"/>
       <c r="H85" s="10" t="n">
-        <v>43</v>
+        <v>10</v>
       </c>
       <c r="I85" s="11">
         <f>H85/$D$85</f>
@@ -13734,24 +13707,24 @@
       </c>
       <c r="B86" s="7" t="inlineStr">
         <is>
-          <t>Suasana Ainsdale (Fasa 2)</t>
+          <t>Suasana Ainsdale (Fasa 1)</t>
         </is>
       </c>
       <c r="C86" s="8" t="n">
         <v>44932</v>
       </c>
       <c r="D86" s="9" t="n">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>12408-15</t>
+          <t>12408-14</t>
         </is>
       </c>
       <c r="F86" s="7" t="inlineStr"/>
       <c r="G86" s="10" t="n"/>
       <c r="H86" s="10" t="n">
-        <v>23</v>
+        <v>43</v>
       </c>
       <c r="I86" s="11">
         <f>H86/$D$86</f>
@@ -13765,24 +13738,24 @@
       </c>
       <c r="B87" s="7" t="inlineStr">
         <is>
-          <t>Phase A2</t>
+          <t>Suasana Ainsdale (Fasa 2)</t>
         </is>
       </c>
       <c r="C87" s="8" t="n">
-        <v>43168</v>
+        <v>44932</v>
       </c>
       <c r="D87" s="9" t="n">
-        <v>302</v>
+        <v>65</v>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>6785-7</t>
+          <t>12408-15</t>
         </is>
       </c>
       <c r="F87" s="7" t="inlineStr"/>
       <c r="G87" s="10" t="n"/>
       <c r="H87" s="10" t="n">
-        <v>298</v>
+        <v>23</v>
       </c>
       <c r="I87" s="11">
         <f>H87/$D$87</f>
@@ -13796,24 +13769,24 @@
       </c>
       <c r="B88" s="7" t="inlineStr">
         <is>
-          <t>Phase A3-2</t>
+          <t>Phase A2</t>
         </is>
       </c>
       <c r="C88" s="8" t="n">
-        <v>43330</v>
+        <v>43168</v>
       </c>
       <c r="D88" s="9" t="n">
-        <v>226</v>
+        <v>302</v>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>6785-8</t>
+          <t>6785-7</t>
         </is>
       </c>
       <c r="F88" s="7" t="inlineStr"/>
       <c r="G88" s="10" t="n"/>
       <c r="H88" s="10" t="n">
-        <v>226</v>
+        <v>298</v>
       </c>
       <c r="I88" s="11">
         <f>H88/$D$88</f>
@@ -13827,24 +13800,24 @@
       </c>
       <c r="B89" s="7" t="inlineStr">
         <is>
-          <t>Phase A3-1</t>
+          <t>Phase A3-2</t>
         </is>
       </c>
       <c r="C89" s="8" t="n">
-        <v>43356</v>
+        <v>43330</v>
       </c>
       <c r="D89" s="9" t="n">
-        <v>176</v>
+        <v>226</v>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>6785-9</t>
+          <t>6785-8</t>
         </is>
       </c>
       <c r="F89" s="7" t="inlineStr"/>
       <c r="G89" s="10" t="n"/>
       <c r="H89" s="10" t="n">
-        <v>176</v>
+        <v>226</v>
       </c>
       <c r="I89" s="11">
         <f>H89/$D$89</f>
@@ -13858,24 +13831,24 @@
       </c>
       <c r="B90" s="7" t="inlineStr">
         <is>
-          <t>Phase A5-1</t>
+          <t>Phase A3-1</t>
         </is>
       </c>
       <c r="C90" s="8" t="n">
-        <v>43659</v>
+        <v>43356</v>
       </c>
       <c r="D90" s="9" t="n">
-        <v>100</v>
+        <v>176</v>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>6785-10</t>
+          <t>6785-9</t>
         </is>
       </c>
       <c r="F90" s="7" t="inlineStr"/>
       <c r="G90" s="10" t="n"/>
       <c r="H90" s="10" t="n">
-        <v>100</v>
+        <v>176</v>
       </c>
       <c r="I90" s="11">
         <f>H90/$D$90</f>
@@ -13889,18 +13862,18 @@
       </c>
       <c r="B91" s="7" t="inlineStr">
         <is>
-          <t>Phase A5-2</t>
+          <t>Phase A5-1</t>
         </is>
       </c>
       <c r="C91" s="8" t="n">
-        <v>43662</v>
+        <v>43659</v>
       </c>
       <c r="D91" s="9" t="n">
         <v>100</v>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>6785-11</t>
+          <t>6785-10</t>
         </is>
       </c>
       <c r="F91" s="7" t="inlineStr"/>
@@ -13920,24 +13893,24 @@
       </c>
       <c r="B92" s="7" t="inlineStr">
         <is>
-          <t>Serenia Ariya 3</t>
+          <t>Phase A5-2</t>
         </is>
       </c>
       <c r="C92" s="8" t="n">
-        <v>44066</v>
+        <v>43662</v>
       </c>
       <c r="D92" s="9" t="n">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>6785-12</t>
+          <t>6785-11</t>
         </is>
       </c>
       <c r="F92" s="7" t="inlineStr"/>
       <c r="G92" s="10" t="n"/>
       <c r="H92" s="10" t="n">
-        <v>122</v>
+        <v>100</v>
       </c>
       <c r="I92" s="11">
         <f>H92/$D$92</f>
@@ -13951,24 +13924,24 @@
       </c>
       <c r="B93" s="7" t="inlineStr">
         <is>
-          <t>Serenia Ariya</t>
+          <t>Serenia Ariya 3</t>
         </is>
       </c>
       <c r="C93" s="8" t="n">
-        <v>44065</v>
+        <v>44066</v>
       </c>
       <c r="D93" s="9" t="n">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>6785-13</t>
+          <t>6785-12</t>
         </is>
       </c>
       <c r="F93" s="7" t="inlineStr"/>
       <c r="G93" s="10" t="n"/>
       <c r="H93" s="10" t="n">
-        <v>87</v>
+        <v>122</v>
       </c>
       <c r="I93" s="11">
         <f>H93/$D$93</f>
@@ -13982,24 +13955,24 @@
       </c>
       <c r="B94" s="7" t="inlineStr">
         <is>
-          <t>Serenia Ariya 2</t>
+          <t>Serenia Ariya</t>
         </is>
       </c>
       <c r="C94" s="8" t="n">
-        <v>44068</v>
+        <v>44065</v>
       </c>
       <c r="D94" s="9" t="n">
-        <v>115</v>
+        <v>87</v>
       </c>
       <c r="E94" s="6" t="inlineStr">
         <is>
-          <t>6785-14</t>
+          <t>6785-13</t>
         </is>
       </c>
       <c r="F94" s="7" t="inlineStr"/>
       <c r="G94" s="10" t="n"/>
       <c r="H94" s="10" t="n">
-        <v>111</v>
+        <v>87</v>
       </c>
       <c r="I94" s="11">
         <f>H94/$D$94</f>
@@ -14013,24 +13986,24 @@
       </c>
       <c r="B95" s="7" t="inlineStr">
         <is>
-          <t>Serenia Amalia 2</t>
+          <t>Serenia Ariya 2</t>
         </is>
       </c>
       <c r="C95" s="8" t="n">
-        <v>44268</v>
+        <v>44068</v>
       </c>
       <c r="D95" s="9" t="n">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="E95" s="6" t="inlineStr">
         <is>
-          <t>6785-15</t>
+          <t>6785-14</t>
         </is>
       </c>
       <c r="F95" s="7" t="inlineStr"/>
       <c r="G95" s="10" t="n"/>
       <c r="H95" s="10" t="n">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="I95" s="11">
         <f>H95/$D$95</f>
@@ -14044,24 +14017,24 @@
       </c>
       <c r="B96" s="7" t="inlineStr">
         <is>
-          <t>Serenia Amalia 3</t>
+          <t>Serenia Amalia 2</t>
         </is>
       </c>
       <c r="C96" s="8" t="n">
-        <v>44270</v>
+        <v>44268</v>
       </c>
       <c r="D96" s="9" t="n">
-        <v>60</v>
+        <v>110</v>
       </c>
       <c r="E96" s="6" t="inlineStr">
         <is>
-          <t>6785-16</t>
+          <t>6785-15</t>
         </is>
       </c>
       <c r="F96" s="7" t="inlineStr"/>
       <c r="G96" s="10" t="n"/>
       <c r="H96" s="10" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="I96" s="11">
         <f>H96/$D$96</f>
@@ -14075,18 +14048,18 @@
       </c>
       <c r="B97" s="7" t="inlineStr">
         <is>
-          <t>Serenia Amalia 4</t>
+          <t>Serenia Amalia 3</t>
         </is>
       </c>
       <c r="C97" s="8" t="n">
-        <v>44279</v>
+        <v>44270</v>
       </c>
       <c r="D97" s="9" t="n">
-        <v>142</v>
+        <v>60</v>
       </c>
       <c r="E97" s="6" t="inlineStr">
         <is>
-          <t>6785-17</t>
+          <t>6785-16</t>
         </is>
       </c>
       <c r="F97" s="7" t="inlineStr"/>
@@ -14106,24 +14079,24 @@
       </c>
       <c r="B98" s="7" t="inlineStr">
         <is>
-          <t>Serenia Amalia 1</t>
+          <t>Serenia Amalia 4</t>
         </is>
       </c>
       <c r="C98" s="8" t="n">
-        <v>44278</v>
+        <v>44279</v>
       </c>
       <c r="D98" s="9" t="n">
-        <v>120</v>
+        <v>142</v>
       </c>
       <c r="E98" s="6" t="inlineStr">
         <is>
-          <t>6785-18</t>
+          <t>6785-17</t>
         </is>
       </c>
       <c r="F98" s="7" t="inlineStr"/>
       <c r="G98" s="10" t="n"/>
       <c r="H98" s="10" t="n">
-        <v>87</v>
+        <v>0</v>
       </c>
       <c r="I98" s="11">
         <f>H98/$D$98</f>
@@ -14137,24 +14110,24 @@
       </c>
       <c r="B99" s="7" t="inlineStr">
         <is>
-          <t>Serenia Aiora 1</t>
+          <t>Serenia Amalia 1</t>
         </is>
       </c>
       <c r="C99" s="8" t="n">
-        <v>44502</v>
+        <v>44278</v>
       </c>
       <c r="D99" s="9" t="n">
-        <v>144</v>
+        <v>120</v>
       </c>
       <c r="E99" s="6" t="inlineStr">
         <is>
-          <t>6785-19</t>
+          <t>6785-18</t>
         </is>
       </c>
       <c r="F99" s="7" t="inlineStr"/>
       <c r="G99" s="10" t="n"/>
       <c r="H99" s="10" t="n">
-        <v>144</v>
+        <v>87</v>
       </c>
       <c r="I99" s="11">
         <f>H99/$D$99</f>
@@ -14168,24 +14141,24 @@
       </c>
       <c r="B100" s="7" t="inlineStr">
         <is>
-          <t>Serenia Aiora 2</t>
+          <t>Serenia Aiora 1</t>
         </is>
       </c>
       <c r="C100" s="8" t="n">
-        <v>44520</v>
+        <v>44502</v>
       </c>
       <c r="D100" s="9" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="E100" s="6" t="inlineStr">
         <is>
-          <t>6785-20</t>
+          <t>6785-19</t>
         </is>
       </c>
       <c r="F100" s="7" t="inlineStr"/>
       <c r="G100" s="10" t="n"/>
       <c r="H100" s="10" t="n">
-        <v>138</v>
+        <v>144</v>
       </c>
       <c r="I100" s="11">
         <f>H100/$D$100</f>
@@ -14199,24 +14172,24 @@
       </c>
       <c r="B101" s="7" t="inlineStr">
         <is>
-          <t>Serenia Anira 1</t>
+          <t>Serenia Aiora 2</t>
         </is>
       </c>
       <c r="C101" s="8" t="n">
-        <v>44713</v>
+        <v>44520</v>
       </c>
       <c r="D101" s="9" t="n">
-        <v>84</v>
+        <v>138</v>
       </c>
       <c r="E101" s="6" t="inlineStr">
         <is>
-          <t>6785-21</t>
+          <t>6785-20</t>
         </is>
       </c>
       <c r="F101" s="7" t="inlineStr"/>
       <c r="G101" s="10" t="n"/>
       <c r="H101" s="10" t="n">
-        <v>57</v>
+        <v>138</v>
       </c>
       <c r="I101" s="11">
         <f>H101/$D$101</f>
@@ -14230,24 +14203,24 @@
       </c>
       <c r="B102" s="7" t="inlineStr">
         <is>
-          <t>Serenia Anira 3</t>
+          <t>Serenia Anira 1</t>
         </is>
       </c>
       <c r="C102" s="8" t="n">
-        <v>44763</v>
+        <v>44713</v>
       </c>
       <c r="D102" s="9" t="n">
-        <v>116</v>
+        <v>84</v>
       </c>
       <c r="E102" s="6" t="inlineStr">
         <is>
-          <t>6785-22</t>
+          <t>6785-21</t>
         </is>
       </c>
       <c r="F102" s="7" t="inlineStr"/>
       <c r="G102" s="10" t="n"/>
       <c r="H102" s="10" t="n">
-        <v>108</v>
+        <v>57</v>
       </c>
       <c r="I102" s="11">
         <f>H102/$D$102</f>
@@ -14261,24 +14234,24 @@
       </c>
       <c r="B103" s="7" t="inlineStr">
         <is>
-          <t>Serenia Anira 2</t>
+          <t>Serenia Anira 3</t>
         </is>
       </c>
       <c r="C103" s="8" t="n">
-        <v>44839</v>
+        <v>44763</v>
       </c>
       <c r="D103" s="9" t="n">
-        <v>96</v>
+        <v>116</v>
       </c>
       <c r="E103" s="6" t="inlineStr">
         <is>
-          <t>6785-23</t>
+          <t>6785-22</t>
         </is>
       </c>
       <c r="F103" s="7" t="inlineStr"/>
       <c r="G103" s="10" t="n"/>
       <c r="H103" s="10" t="n">
-        <v>86</v>
+        <v>108</v>
       </c>
       <c r="I103" s="11">
         <f>H103/$D$103</f>
@@ -14292,24 +14265,24 @@
       </c>
       <c r="B104" s="7" t="inlineStr">
         <is>
-          <t>Serenia Aqila</t>
+          <t>Serenia Anira 2</t>
         </is>
       </c>
       <c r="C104" s="8" t="n">
-        <v>44851</v>
+        <v>44839</v>
       </c>
       <c r="D104" s="9" t="n">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="E104" s="6" t="inlineStr">
         <is>
-          <t>6785-24</t>
+          <t>6785-23</t>
         </is>
       </c>
       <c r="F104" s="7" t="inlineStr"/>
       <c r="G104" s="10" t="n"/>
       <c r="H104" s="10" t="n">
-        <v>53</v>
+        <v>86</v>
       </c>
       <c r="I104" s="11">
         <f>H104/$D$104</f>
@@ -14323,24 +14296,24 @@
       </c>
       <c r="B105" s="7" t="inlineStr">
         <is>
-          <t>Serenia Anisa 2</t>
+          <t>Serenia Aqila</t>
         </is>
       </c>
       <c r="C105" s="8" t="n">
-        <v>44956</v>
+        <v>44851</v>
       </c>
       <c r="D105" s="9" t="n">
-        <v>202</v>
+        <v>72</v>
       </c>
       <c r="E105" s="6" t="inlineStr">
         <is>
-          <t>6785-25</t>
+          <t>6785-24</t>
         </is>
       </c>
       <c r="F105" s="7" t="inlineStr"/>
       <c r="G105" s="10" t="n"/>
       <c r="H105" s="10" t="n">
-        <v>191</v>
+        <v>53</v>
       </c>
       <c r="I105" s="11">
         <f>H105/$D$105</f>
@@ -14354,24 +14327,24 @@
       </c>
       <c r="B106" s="7" t="inlineStr">
         <is>
-          <t>Serenia Anisa 1</t>
+          <t>Serenia Anisa 2</t>
         </is>
       </c>
       <c r="C106" s="8" t="n">
-        <v>44974</v>
+        <v>44956</v>
       </c>
       <c r="D106" s="9" t="n">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="E106" s="6" t="inlineStr">
         <is>
-          <t>6785-26</t>
+          <t>6785-25</t>
         </is>
       </c>
       <c r="F106" s="7" t="inlineStr"/>
       <c r="G106" s="10" t="n"/>
       <c r="H106" s="10" t="n">
-        <v>203</v>
+        <v>191</v>
       </c>
       <c r="I106" s="11">
         <f>H106/$D$106</f>
@@ -14385,28 +14358,24 @@
       </c>
       <c r="B107" s="7" t="inlineStr">
         <is>
-          <t>Residensi Dian</t>
+          <t>Serenia Anisa 1</t>
         </is>
       </c>
       <c r="C107" s="8" t="n">
-        <v>45560</v>
+        <v>44974</v>
       </c>
       <c r="D107" s="9" t="n">
-        <v>480</v>
+        <v>206</v>
       </c>
       <c r="E107" s="6" t="inlineStr">
         <is>
-          <t>597-14</t>
-        </is>
-      </c>
-      <c r="F107" s="7" t="inlineStr">
-        <is>
-          <t>SIME DARBY PROPERTY (KL EAST) SDN. BHD.</t>
-        </is>
-      </c>
+          <t>6785-26</t>
+        </is>
+      </c>
+      <c r="F107" s="7" t="inlineStr"/>
       <c r="G107" s="10" t="n"/>
       <c r="H107" s="10" t="n">
-        <v>333</v>
+        <v>203</v>
       </c>
       <c r="I107" s="11">
         <f>H107/$D$107</f>
@@ -14420,18 +14389,18 @@
       </c>
       <c r="B108" s="7" t="inlineStr">
         <is>
-          <t>Residensi Vista Timur</t>
+          <t>Residensi Dian</t>
         </is>
       </c>
       <c r="C108" s="8" t="n">
-        <v>46150</v>
+        <v>45560</v>
       </c>
       <c r="D108" s="9" t="n">
-        <v>61</v>
+        <v>480</v>
       </c>
       <c r="E108" s="6" t="inlineStr">
         <is>
-          <t>597-15</t>
+          <t>597-14</t>
         </is>
       </c>
       <c r="F108" s="7" t="inlineStr">
@@ -14441,7 +14410,7 @@
       </c>
       <c r="G108" s="10" t="n"/>
       <c r="H108" s="10" t="n">
-        <v>6</v>
+        <v>333</v>
       </c>
       <c r="I108" s="11">
         <f>H108/$D$108</f>
@@ -14455,28 +14424,28 @@
       </c>
       <c r="B109" s="7" t="inlineStr">
         <is>
-          <t>TIARA RESIDENCES 2</t>
+          <t>Residensi Vista Timur</t>
         </is>
       </c>
       <c r="C109" s="8" t="n">
-        <v>46274</v>
+        <v>46150</v>
       </c>
       <c r="D109" s="9" t="n">
-        <v>112</v>
+        <v>61</v>
       </c>
       <c r="E109" s="6" t="inlineStr">
         <is>
-          <t>20171-3</t>
+          <t>597-15</t>
         </is>
       </c>
       <c r="F109" s="7" t="inlineStr">
         <is>
-          <t>SIME DARBY PROPERTY (BUKIT JELUTONG)  SDN. BHD.</t>
+          <t>SIME DARBY PROPERTY (KL EAST) SDN. BHD.</t>
         </is>
       </c>
       <c r="G109" s="10" t="n"/>
       <c r="H109" s="10" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I109" s="11">
         <f>H109/$D$109</f>
@@ -14498,7 +14467,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J16"/>
+  <dimension ref="A1:J15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -14773,18 +14742,18 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>TriTower Residence</t>
+          <t>Sky Habitat</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>41502</v>
+        <v>41898</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>360</v>
+        <v>184</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>12327-2</t>
+          <t>12327-4</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
@@ -14794,7 +14763,7 @@
       </c>
       <c r="G10" s="10" t="n"/>
       <c r="H10" s="10" t="n">
-        <v>224</v>
+        <v>175</v>
       </c>
       <c r="I10" s="11">
         <f>H10/$D$10</f>
@@ -14808,18 +14777,18 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Sky Habitat</t>
+          <t>Pandan Residence I</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>41898</v>
+        <v>41626</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>184</v>
+        <v>283</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>12327-4</t>
+          <t>12327-1</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
@@ -14829,7 +14798,7 @@
       </c>
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="10" t="n">
-        <v>175</v>
+        <v>282</v>
       </c>
       <c r="I11" s="11">
         <f>H11/$D$11</f>
@@ -14843,18 +14812,18 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Pandan Residence I</t>
+          <t>Pandan Residence II</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>41626</v>
+        <v>41514</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>283</v>
+        <v>182</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>12327-1</t>
+          <t>12327-3</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
@@ -14864,7 +14833,7 @@
       </c>
       <c r="G12" s="10" t="n"/>
       <c r="H12" s="10" t="n">
-        <v>282</v>
+        <v>180</v>
       </c>
       <c r="I12" s="11">
         <f>H12/$D$12</f>
@@ -14878,28 +14847,28 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Pandan Residence II</t>
+          <t>Escadia + Arcadia (Taman Desaru Utama)</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>41514</v>
+        <v>41984</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>182</v>
+        <v>507</v>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>12327-3</t>
+          <t>11786-2</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>SKS SOUTHERN SDN. BHD.</t>
+          <t>CONTINENTAL MANAGEMENT SDN. BHD.</t>
         </is>
       </c>
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="10" t="n">
-        <v>180</v>
+        <v>492</v>
       </c>
       <c r="I13" s="11">
         <f>H13/$D$13</f>
@@ -14913,28 +14882,28 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Escadia + Arcadia (Taman Desaru Utama)</t>
+          <t>Marinea (Taman Desaru Utama)</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>41984</v>
+        <v>41704</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>507</v>
+        <v>306</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>11786-2</t>
+          <t>9736-4</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>CONTINENTAL MANAGEMENT SDN. BHD.</t>
+          <t>TNC CONSOLIDATED SDN. BHD.</t>
         </is>
       </c>
       <c r="G14" s="10" t="n"/>
       <c r="H14" s="10" t="n">
-        <v>492</v>
+        <v>288</v>
       </c>
       <c r="I14" s="11">
         <f>H14/$D$14</f>
@@ -14948,69 +14917,34 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Marinea (Taman Desaru Utama)</t>
+          <t>Desaru Utama SSTH</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>41704</v>
+        <v>40869</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>306</v>
+        <v>985</v>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>9736-4</t>
+          <t>11786-1</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>TNC CONSOLIDATED SDN. BHD.</t>
+          <t>CONTINENTAL MANAGEMENT SDN. BHD.</t>
         </is>
       </c>
       <c r="G15" s="10" t="n"/>
       <c r="H15" s="10" t="n">
-        <v>288</v>
+        <v>938</v>
       </c>
       <c r="I15" s="11">
         <f>H15/$D$15</f>
         <v/>
       </c>
       <c r="J15" s="7" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Desaru Utama SSTH</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="n">
-        <v>40869</v>
-      </c>
-      <c r="D16" s="9" t="n">
-        <v>985</v>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
-        <is>
-          <t>11786-1</t>
-        </is>
-      </c>
-      <c r="F16" s="7" t="inlineStr">
-        <is>
-          <t>CONTINENTAL MANAGEMENT SDN. BHD.</t>
-        </is>
-      </c>
-      <c r="G16" s="10" t="n"/>
-      <c r="H16" s="10" t="n">
-        <v>938</v>
-      </c>
-      <c r="I16" s="11">
-        <f>H16/$D$16</f>
-        <v/>
-      </c>
-      <c r="J16" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -25789,7 +25723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:J24"/>
+  <dimension ref="A2:J26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -25960,38 +25894,29 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>D'Terra Residences</t>
+          <t>D'Evia Residences @ Kwasa Damansara</t>
         </is>
       </c>
       <c r="C7" s="8" t="n">
-        <v>44946</v>
+        <v>46177</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>767</v>
+        <v>440</v>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>20011-2</t>
+          <t>31064-1</t>
         </is>
       </c>
       <c r="F7" s="7" t="inlineStr">
         <is>
-          <t>MIGHTYPROP  SDN. BHD.</t>
+          <t>EXSIM MX4 SDN. BHD.</t>
         </is>
       </c>
       <c r="G7" s="10" t="n"/>
-      <c r="H7" s="10" t="n">
-        <v>767</v>
-      </c>
-      <c r="I7" s="11">
-        <f>H7/$D$7</f>
-        <v/>
-      </c>
-      <c r="J7" s="7" t="inlineStr">
-        <is>
-          <t>Latest sales - Block B: 767 units</t>
-        </is>
-      </c>
+      <c r="H7" s="10" t="n"/>
+      <c r="I7" s="11" t="n"/>
+      <c r="J7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="n">
@@ -25999,38 +25924,29 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>D'Tessera Residences</t>
+          <t>D'Nuri Residences @ Kwasa Damansara</t>
         </is>
       </c>
       <c r="C8" s="8" t="n">
-        <v>45033</v>
+        <v>46261</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>671</v>
+        <v>492</v>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>20011-4</t>
+          <t>31064-2</t>
         </is>
       </c>
       <c r="F8" s="7" t="inlineStr">
         <is>
-          <t>MIGHTYPROP  SDN. BHD.</t>
+          <t>EXSIM MX4 SDN. BHD.</t>
         </is>
       </c>
       <c r="G8" s="10" t="n"/>
-      <c r="H8" s="10" t="n">
-        <v>664</v>
-      </c>
-      <c r="I8" s="11">
-        <f>H8/$D$8</f>
-        <v/>
-      </c>
-      <c r="J8" s="7" t="inlineStr">
-        <is>
-          <t>Latest sales - Block C: 664 units</t>
-        </is>
-      </c>
+      <c r="H8" s="10" t="n"/>
+      <c r="I8" s="11" t="n"/>
+      <c r="J8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
@@ -26038,34 +25954,38 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Hanaz Suites</t>
+          <t>D'Terra Residences</t>
         </is>
       </c>
       <c r="C9" s="8" t="n">
-        <v>45659</v>
+        <v>44946</v>
       </c>
       <c r="D9" s="9" t="n">
-        <v>98</v>
+        <v>767</v>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>13666-2</t>
+          <t>20011-2</t>
         </is>
       </c>
       <c r="F9" s="7" t="inlineStr">
         <is>
-          <t>SUNRISE CHARM SDN. BHD.</t>
+          <t>MIGHTYPROP  SDN. BHD.</t>
         </is>
       </c>
       <c r="G9" s="10" t="n"/>
       <c r="H9" s="10" t="n">
-        <v>98</v>
+        <v>767</v>
       </c>
       <c r="I9" s="11">
         <f>H9/$D$9</f>
         <v/>
       </c>
-      <c r="J9" s="7" t="inlineStr"/>
+      <c r="J9" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block B: 767 units</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
@@ -26073,34 +25993,38 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>Hugoz Suites</t>
+          <t>D'Tessera Residences</t>
         </is>
       </c>
       <c r="C10" s="8" t="n">
-        <v>45184</v>
+        <v>45033</v>
       </c>
       <c r="D10" s="9" t="n">
-        <v>320</v>
+        <v>671</v>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>30370-1</t>
+          <t>20011-4</t>
         </is>
       </c>
       <c r="F10" s="7" t="inlineStr">
         <is>
-          <t>ARMADA ISTIMEWA SDN. BHD.</t>
+          <t>MIGHTYPROP  SDN. BHD.</t>
         </is>
       </c>
       <c r="G10" s="10" t="n"/>
       <c r="H10" s="10" t="n">
-        <v>319</v>
+        <v>664</v>
       </c>
       <c r="I10" s="11">
         <f>H10/$D$10</f>
         <v/>
       </c>
-      <c r="J10" s="7" t="inlineStr"/>
+      <c r="J10" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block C: 664 units</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
@@ -26108,28 +26032,28 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Kyliez Suites</t>
+          <t>Hanaz Suites</t>
         </is>
       </c>
       <c r="C11" s="8" t="n">
-        <v>45511</v>
+        <v>45659</v>
       </c>
       <c r="D11" s="9" t="n">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>30789-1</t>
+          <t>13666-2</t>
         </is>
       </c>
       <c r="F11" s="7" t="inlineStr">
         <is>
-          <t>EXSIM AVENUE SDN. BHD.</t>
+          <t>SUNRISE CHARM SDN. BHD.</t>
         </is>
       </c>
       <c r="G11" s="10" t="n"/>
       <c r="H11" s="10" t="n">
-        <v>126</v>
+        <v>98</v>
       </c>
       <c r="I11" s="11">
         <f>H11/$D$11</f>
@@ -26143,28 +26067,28 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Noordinz Suites</t>
+          <t>Hugoz Suites</t>
         </is>
       </c>
       <c r="C12" s="8" t="n">
-        <v>45251</v>
+        <v>45184</v>
       </c>
       <c r="D12" s="9" t="n">
-        <v>603</v>
+        <v>320</v>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>30571-1</t>
+          <t>30370-1</t>
         </is>
       </c>
       <c r="F12" s="7" t="inlineStr">
         <is>
-          <t>EXSIM NOORDIN SDN. BHD.</t>
+          <t>ARMADA ISTIMEWA SDN. BHD.</t>
         </is>
       </c>
       <c r="G12" s="10" t="n"/>
       <c r="H12" s="10" t="n">
-        <v>602</v>
+        <v>319</v>
       </c>
       <c r="I12" s="11">
         <f>H12/$D$12</f>
@@ -26178,28 +26102,28 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Qubaz Suites</t>
+          <t>Kyliez Suites</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
-        <v>45716</v>
+        <v>45511</v>
       </c>
       <c r="D13" s="9" t="n">
-        <v>759</v>
+        <v>126</v>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>30914-1</t>
+          <t>30789-1</t>
         </is>
       </c>
       <c r="F13" s="7" t="inlineStr">
         <is>
-          <t>EXSIM KG TIONG (KT)  SDN. BHD.</t>
+          <t>EXSIM AVENUE SDN. BHD.</t>
         </is>
       </c>
       <c r="G13" s="10" t="n"/>
       <c r="H13" s="10" t="n">
-        <v>625</v>
+        <v>126</v>
       </c>
       <c r="I13" s="11">
         <f>H13/$D$13</f>
@@ -26213,28 +26137,28 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Sea Crestz</t>
+          <t>Noordinz Suites</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
-        <v>45736</v>
+        <v>45251</v>
       </c>
       <c r="D14" s="9" t="n">
-        <v>456</v>
+        <v>603</v>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>30830-1</t>
+          <t>30571-1</t>
         </is>
       </c>
       <c r="F14" s="7" t="inlineStr">
         <is>
-          <t>KUANTAN WATERFRONT RESORT CITY SDN. BHD.</t>
+          <t>EXSIM NOORDIN SDN. BHD.</t>
         </is>
       </c>
       <c r="G14" s="10" t="n"/>
       <c r="H14" s="10" t="n">
-        <v>317</v>
+        <v>602</v>
       </c>
       <c r="I14" s="11">
         <f>H14/$D$14</f>
@@ -26248,28 +26172,28 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>The Aldenz</t>
+          <t>Qubaz Suites</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
-        <v>45839</v>
+        <v>45716</v>
       </c>
       <c r="D15" s="9" t="n">
-        <v>662</v>
+        <v>759</v>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>20011-5</t>
+          <t>30914-1</t>
         </is>
       </c>
       <c r="F15" s="7" t="inlineStr">
         <is>
-          <t>MIGHTYPROP  SDN. BHD.</t>
+          <t>EXSIM KG TIONG (KT)  SDN. BHD.</t>
         </is>
       </c>
       <c r="G15" s="10" t="n"/>
       <c r="H15" s="10" t="n">
-        <v>181</v>
+        <v>625</v>
       </c>
       <c r="I15" s="11">
         <f>H15/$D$15</f>
@@ -26283,38 +26207,34 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>The Asteriaz</t>
+          <t>Sea Crestz</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
-        <v>45856</v>
+        <v>45736</v>
       </c>
       <c r="D16" s="9" t="n">
-        <v>848</v>
+        <v>456</v>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>31007-1</t>
+          <t>30830-1</t>
         </is>
       </c>
       <c r="F16" s="7" t="inlineStr">
         <is>
-          <t>EXSIM KEBUN TEH SDN. BHD.</t>
+          <t>KUANTAN WATERFRONT RESORT CITY SDN. BHD.</t>
         </is>
       </c>
       <c r="G16" s="10" t="n"/>
       <c r="H16" s="10" t="n">
-        <v>845</v>
+        <v>317</v>
       </c>
       <c r="I16" s="11">
         <f>H16/$D$16</f>
         <v/>
       </c>
-      <c r="J16" s="7" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
+      <c r="J16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="n">
@@ -26322,38 +26242,34 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>The Fiddlewoodz</t>
+          <t>The Aldenz</t>
         </is>
       </c>
       <c r="C17" s="8" t="n">
-        <v>44282</v>
+        <v>45839</v>
       </c>
       <c r="D17" s="9" t="n">
-        <v>679</v>
+        <v>662</v>
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>20084-1</t>
+          <t>20011-5</t>
         </is>
       </c>
       <c r="F17" s="7" t="inlineStr">
         <is>
-          <t>IVORY INTERPOINT SDN. BHD.</t>
+          <t>MIGHTYPROP  SDN. BHD.</t>
         </is>
       </c>
       <c r="G17" s="10" t="n"/>
       <c r="H17" s="10" t="n">
-        <v>339</v>
+        <v>181</v>
       </c>
       <c r="I17" s="11">
         <f>H17/$D$17</f>
         <v/>
       </c>
-      <c r="J17" s="7" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 312 units, Block B: 27 units</t>
-        </is>
-      </c>
+      <c r="J17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="n">
@@ -26361,28 +26277,28 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>The Kingswoodz</t>
+          <t>The Asteriaz</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
-        <v>45516</v>
+        <v>45856</v>
       </c>
       <c r="D18" s="9" t="n">
-        <v>1558</v>
+        <v>848</v>
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>30741-1</t>
+          <t>31007-1</t>
         </is>
       </c>
       <c r="F18" s="7" t="inlineStr">
         <is>
-          <t>EXSIM JALIL LINK   SDN. BHD.</t>
+          <t>EXSIM KEBUN TEH SDN. BHD.</t>
         </is>
       </c>
       <c r="G18" s="10" t="n"/>
       <c r="H18" s="10" t="n">
-        <v>1552</v>
+        <v>845</v>
       </c>
       <c r="I18" s="11">
         <f>H18/$D$18</f>
@@ -26390,7 +26306,7 @@
       </c>
       <c r="J18" s="7" t="inlineStr">
         <is>
-          <t>Latest sales - Block A: 457 units, Block B: 505 units, Block C: 590 units</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -26400,34 +26316,38 @@
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>The Lighthauz</t>
+          <t>The Fiddlewoodz</t>
         </is>
       </c>
       <c r="C19" s="8" t="n">
-        <v>45952</v>
+        <v>44282</v>
       </c>
       <c r="D19" s="9" t="n">
-        <v>671</v>
+        <v>679</v>
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>31088-1</t>
+          <t>20084-1</t>
         </is>
       </c>
       <c r="F19" s="7" t="inlineStr">
         <is>
-          <t>EXSIM WATERFRONT SDN. BHD.</t>
+          <t>IVORY INTERPOINT SDN. BHD.</t>
         </is>
       </c>
       <c r="G19" s="10" t="n"/>
       <c r="H19" s="10" t="n">
-        <v>553</v>
+        <v>339</v>
       </c>
       <c r="I19" s="11">
         <f>H19/$D$19</f>
         <v/>
       </c>
-      <c r="J19" s="7" t="inlineStr"/>
+      <c r="J19" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 312 units, Block B: 27 units</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="6" t="n">
@@ -26435,18 +26355,18 @@
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>The Queenswoodz</t>
+          <t>The Kingswoodz</t>
         </is>
       </c>
       <c r="C20" s="8" t="n">
-        <v>46099</v>
+        <v>45516</v>
       </c>
       <c r="D20" s="9" t="n">
-        <v>1004</v>
+        <v>1558</v>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>30741-2</t>
+          <t>30741-1</t>
         </is>
       </c>
       <c r="F20" s="7" t="inlineStr">
@@ -26456,7 +26376,7 @@
       </c>
       <c r="G20" s="10" t="n"/>
       <c r="H20" s="10" t="n">
-        <v>438</v>
+        <v>1552</v>
       </c>
       <c r="I20" s="11">
         <f>H20/$D$20</f>
@@ -26464,7 +26384,7 @@
       </c>
       <c r="J20" s="7" t="inlineStr">
         <is>
-          <t>Latest sales - Block A: 193 units, Block B: 245 units</t>
+          <t>Latest sales - Block A: 457 units, Block B: 505 units, Block C: 590 units</t>
         </is>
       </c>
     </row>
@@ -26474,38 +26394,34 @@
       </c>
       <c r="B21" s="7" t="inlineStr">
         <is>
-          <t>The Vividz</t>
+          <t>The Lighthauz</t>
         </is>
       </c>
       <c r="C21" s="8" t="n">
-        <v>45806</v>
+        <v>45952</v>
       </c>
       <c r="D21" s="9" t="n">
-        <v>1138</v>
+        <v>671</v>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>30357-2</t>
+          <t>31088-1</t>
         </is>
       </c>
       <c r="F21" s="7" t="inlineStr">
         <is>
-          <t>EXSIM BUKIT JALIL CITY SDN. BHD.</t>
+          <t>EXSIM WATERFRONT SDN. BHD.</t>
         </is>
       </c>
       <c r="G21" s="10" t="n"/>
       <c r="H21" s="10" t="n">
-        <v>658</v>
+        <v>553</v>
       </c>
       <c r="I21" s="11">
         <f>H21/$D$21</f>
         <v/>
       </c>
-      <c r="J21" s="7" t="inlineStr">
-        <is>
-          <t>Latest sales - Block A: 358 units, Block B: 300 units</t>
-        </is>
-      </c>
+      <c r="J21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="n">
@@ -26513,34 +26429,38 @@
       </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>Veladaz Residences</t>
+          <t>The Queenswoodz</t>
         </is>
       </c>
       <c r="C22" s="8" t="n">
-        <v>45218</v>
+        <v>46099</v>
       </c>
       <c r="D22" s="9" t="n">
-        <v>508</v>
+        <v>1004</v>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>30357-1</t>
+          <t>30741-2</t>
         </is>
       </c>
       <c r="F22" s="7" t="inlineStr">
         <is>
-          <t>EXSIM BUKIT JALIL CITY SDN. BHD.</t>
+          <t>EXSIM JALIL LINK   SDN. BHD.</t>
         </is>
       </c>
       <c r="G22" s="10" t="n"/>
       <c r="H22" s="10" t="n">
-        <v>507</v>
+        <v>438</v>
       </c>
       <c r="I22" s="11">
         <f>H22/$D$22</f>
         <v/>
       </c>
-      <c r="J22" s="7" t="inlineStr"/>
+      <c r="J22" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 193 units, Block B: 245 units</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="6" t="n">
@@ -26548,24 +26468,28 @@
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>Causewayz Square @ JBCC</t>
+          <t>The Vividz</t>
         </is>
       </c>
       <c r="C23" s="8" t="n">
-        <v>45966</v>
+        <v>45806</v>
       </c>
       <c r="D23" s="9" t="n">
-        <v>4525</v>
+        <v>1138</v>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>31100-1,31100-2,31100-3,31100-4</t>
-        </is>
-      </c>
-      <c r="F23" s="7" t="inlineStr"/>
+          <t>30357-2</t>
+        </is>
+      </c>
+      <c r="F23" s="7" t="inlineStr">
+        <is>
+          <t>EXSIM BUKIT JALIL CITY SDN. BHD.</t>
+        </is>
+      </c>
       <c r="G23" s="10" t="n"/>
       <c r="H23" s="10" t="n">
-        <v>1503</v>
+        <v>658</v>
       </c>
       <c r="I23" s="11">
         <f>H23/$D$23</f>
@@ -26573,7 +26497,7 @@
       </c>
       <c r="J23" s="7" t="inlineStr">
         <is>
-          <t>Latest sales - Block A: 497 units, Block B: 531 units, Block D: 475 units</t>
+          <t>Latest sales - Block A: 358 units, Block B: 300 units</t>
         </is>
       </c>
     </row>
@@ -26583,30 +26507,100 @@
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>The Stallionz</t>
+          <t>Veladaz Residences</t>
         </is>
       </c>
       <c r="C24" s="8" t="n">
-        <v>44840</v>
+        <v>45218</v>
       </c>
       <c r="D24" s="9" t="n">
-        <v>424</v>
+        <v>508</v>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>30131-1</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr"/>
+          <t>30357-1</t>
+        </is>
+      </c>
+      <c r="F24" s="7" t="inlineStr">
+        <is>
+          <t>EXSIM BUKIT JALIL CITY SDN. BHD.</t>
+        </is>
+      </c>
       <c r="G24" s="10" t="n"/>
       <c r="H24" s="10" t="n">
-        <v>424</v>
+        <v>507</v>
       </c>
       <c r="I24" s="11">
         <f>H24/$D$24</f>
         <v/>
       </c>
       <c r="J24" s="7" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="n">
+        <v>21</v>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>Causewayz Square @ JBCC</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>45966</v>
+      </c>
+      <c r="D25" s="9" t="n">
+        <v>4525</v>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>31100-1,31100-2,31100-3,31100-4</t>
+        </is>
+      </c>
+      <c r="F25" s="7" t="inlineStr"/>
+      <c r="G25" s="10" t="n"/>
+      <c r="H25" s="10" t="n">
+        <v>1503</v>
+      </c>
+      <c r="I25" s="11">
+        <f>H25/$D$25</f>
+        <v/>
+      </c>
+      <c r="J25" s="7" t="inlineStr">
+        <is>
+          <t>Latest sales - Block A: 497 units, Block B: 531 units, Block D: 475 units</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>The Stallionz</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>44840</v>
+      </c>
+      <c r="D26" s="9" t="n">
+        <v>424</v>
+      </c>
+      <c r="E26" s="6" t="inlineStr">
+        <is>
+          <t>30131-1</t>
+        </is>
+      </c>
+      <c r="F26" s="7" t="inlineStr"/>
+      <c r="G26" s="10" t="n"/>
+      <c r="H26" s="10" t="n">
+        <v>424</v>
+      </c>
+      <c r="I26" s="11">
+        <f>H26/$D$26</f>
+        <v/>
+      </c>
+      <c r="J26" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -26988,7 +26982,7 @@
       </c>
       <c r="G12" s="10" t="n"/>
       <c r="H12" s="10" t="n">
-        <v>592</v>
+        <v>62</v>
       </c>
       <c r="I12" s="11">
         <f>H12/$D$12</f>
@@ -27002,7 +26996,7 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
-          <t>Riveria Aluna @ Wawari (530 total)</t>
+          <t>Riveria Aluna @ Wawari</t>
         </is>
       </c>
       <c r="C13" s="8" t="n">
@@ -27037,7 +27031,7 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Riveria Aluna @ Wawari Ph2 (530 total)</t>
+          <t>Riveria Aluna @ Wawari Ph2</t>
         </is>
       </c>
       <c r="C14" s="8" t="n">
@@ -27072,7 +27066,7 @@
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
-          <t>Riverhaus @ Wawari (2160 total)</t>
+          <t>Riverhaus @ Wawari</t>
         </is>
       </c>
       <c r="C15" s="8" t="n">
@@ -27107,7 +27101,7 @@
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
-          <t>Riverhaus @ Wawari Ph2 (2160 total)</t>
+          <t>Riverhaus @ Wawari Ph2</t>
         </is>
       </c>
       <c r="C16" s="8" t="n">
@@ -27177,7 +27171,7 @@
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>D'Secret Garden 2 @ Kempas Indah (3389 total)</t>
+          <t>D'Secret Garden 2 @ Kempas Indah</t>
         </is>
       </c>
       <c r="C18" s="8" t="n">
@@ -27950,31 +27944,24 @@
           <t>Riveria Avenia @ Wawari</t>
         </is>
       </c>
-      <c r="C40" s="8" t="n">
-        <v>46087</v>
-      </c>
+      <c r="C40" s="8" t="n"/>
       <c r="D40" s="9" t="n">
         <v>440</v>
       </c>
-      <c r="E40" s="6" t="inlineStr">
-        <is>
-          <t>31063-1,31063-2,31063-3</t>
-        </is>
-      </c>
+      <c r="E40" s="6" t="inlineStr"/>
       <c r="F40" s="7" t="inlineStr">
         <is>
           <t>WAWARI SDN. BHD.</t>
         </is>
       </c>
       <c r="G40" s="10" t="n"/>
-      <c r="H40" s="10" t="n">
-        <v>592</v>
-      </c>
-      <c r="I40" s="11">
-        <f>H40/$D$40</f>
-        <v/>
-      </c>
-      <c r="J40" s="7" t="inlineStr"/>
+      <c r="H40" s="10" t="n"/>
+      <c r="I40" s="11" t="n"/>
+      <c r="J40" s="7" t="inlineStr">
+        <is>
+          <t>Not launched yet.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="n">

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -535,7 +535,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5811,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -10876,7 +10876,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -11388,7 +11388,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -15652,7 +15652,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -16169,7 +16169,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -16515,7 +16515,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -20581,7 +20581,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -21012,7 +21012,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -22420,7 +22420,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -22648,7 +22648,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -23543,7 +23543,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -24139,7 +24139,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -24619,7 +24619,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -27406,7 +27406,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>
@@ -28554,7 +28554,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 11/09/2026</t>
+          <t>Report as at 12/09/2026</t>
         </is>
       </c>
     </row>

--- a/docs/downloads/TEDUH_Competitor_Trackers.xlsx
+++ b/docs/downloads/TEDUH_Competitor_Trackers.xlsx
@@ -535,7 +535,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -1391,7 +1391,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -2907,7 +2907,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -3926,7 +3926,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -4905,7 +4905,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -5811,7 +5811,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -6181,7 +6181,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -6726,7 +6726,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -7129,7 +7129,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -7491,7 +7491,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -10876,7 +10876,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -11388,7 +11388,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -12003,7 +12003,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -15652,7 +15652,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -16169,7 +16169,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -16515,7 +16515,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -20581,7 +20581,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -21012,7 +21012,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -21374,7 +21374,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -22420,7 +22420,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -22648,7 +22648,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -23543,7 +23543,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -24139,7 +24139,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -24619,7 +24619,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -27406,7 +27406,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
@@ -28554,7 +28554,7 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Report as at 12/09/2026</t>
+          <t>Report as at 13/09/2026</t>
         </is>
       </c>
     </row>
